--- a/30_table/01_테스트버전/Table_Data_Npc.xlsx
+++ b/30_table/01_테스트버전/Table_Data_Npc.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="45" windowWidth="19215" windowHeight="12135" activeTab="2"/>
+    <workbookView xWindow="-15" yWindow="105" windowWidth="19215" windowHeight="12075" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="DOC History" sheetId="6" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="319">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1047,6 +1047,107 @@
   <si>
     <t>mob_n_0003</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개발자_50046</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개발자_50047</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_0010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_NPC_N_0022</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_n_0022</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_n_0023</t>
+  </si>
+  <si>
+    <t>npc_n_0024</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20022_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20023_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20024_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개발자_50051</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개발자_50048</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_n_0025</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20025_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20022_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20022_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20022_04</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20023_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20023_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20023_04</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20023_05</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20023_06</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20023_07</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20024_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20024_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20024_04</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20025_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20025_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20025_04</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20025_05</t>
   </si>
 </sst>
 </file>
@@ -5044,7 +5145,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" style="36" bestFit="1" customWidth="1"/>
@@ -6534,278 +6635,300 @@
       <c r="AC22" s="33"/>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A23" s="40">
-        <v>22000</v>
-      </c>
-      <c r="B23" s="41" t="s">
-        <v>249</v>
-      </c>
-      <c r="C23" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="D23" s="40" t="str">
-        <f t="shared" ref="D23:D24" si="9">"STR_"&amp;UPPER(C23)</f>
-        <v>STR_MOB_N_0001</v>
-      </c>
-      <c r="E23" s="40" t="str">
-        <f t="shared" ref="E23:E35" si="10">D23&amp;"_DESC"</f>
-        <v>STR_MOB_N_0001_DESC</v>
-      </c>
-      <c r="F23" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G23" s="40">
-        <v>10</v>
-      </c>
-      <c r="H23" s="40">
+      <c r="A23" s="33">
+        <v>20021</v>
+      </c>
+      <c r="B23" s="34" t="s">
+        <v>289</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>293</v>
+      </c>
+      <c r="D23" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="E23" s="33" t="str">
+        <f t="shared" ref="E23:E24" si="9">D23&amp;"_DESC"</f>
+        <v>STR_NPC_N_0022_DESC</v>
+      </c>
+      <c r="F23" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G23" s="33">
+        <v>0</v>
+      </c>
+      <c r="H23" s="33">
+        <v>0</v>
+      </c>
+      <c r="I23" s="33">
         <v>1</v>
       </c>
-      <c r="I23" s="40">
+      <c r="J23" s="33">
+        <v>0</v>
+      </c>
+      <c r="K23" s="33">
+        <v>0</v>
+      </c>
+      <c r="L23" s="33">
+        <v>0</v>
+      </c>
+      <c r="M23" s="33">
+        <v>0</v>
+      </c>
+      <c r="N23" s="33"/>
+      <c r="O23" s="33"/>
+      <c r="P23" s="33"/>
+      <c r="Q23" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="T23" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="U23" s="33" t="s">
+        <v>303</v>
+      </c>
+      <c r="V23" s="33" t="s">
+        <v>304</v>
+      </c>
+      <c r="W23" s="33" t="s">
+        <v>305</v>
+      </c>
+      <c r="X23" s="33"/>
+      <c r="Y23" s="33"/>
+      <c r="Z23" s="33"/>
+      <c r="AA23" s="33"/>
+      <c r="AB23" s="33"/>
+      <c r="AC23" s="33"/>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A24" s="33">
+        <v>20022</v>
+      </c>
+      <c r="B24" s="34" t="s">
+        <v>290</v>
+      </c>
+      <c r="C24" s="35" t="s">
+        <v>294</v>
+      </c>
+      <c r="D24" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="E24" s="33" t="str">
+        <f t="shared" si="9"/>
+        <v>STR_NPC_N_0022_DESC</v>
+      </c>
+      <c r="F24" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G24" s="33">
+        <v>0</v>
+      </c>
+      <c r="H24" s="33">
+        <v>0</v>
+      </c>
+      <c r="I24" s="33">
         <v>1</v>
       </c>
-      <c r="J23" s="40">
-        <v>0</v>
-      </c>
-      <c r="K23" s="40">
-        <v>1200</v>
-      </c>
-      <c r="L23" s="40">
-        <v>30</v>
-      </c>
-      <c r="M23" s="40">
-        <v>20</v>
-      </c>
-      <c r="N23" s="40" t="s">
-        <v>227</v>
-      </c>
-      <c r="O23" s="40"/>
-      <c r="P23" s="40"/>
-      <c r="Q23" s="40" t="s">
-        <v>228</v>
-      </c>
-      <c r="R23" s="40"/>
-      <c r="S23" s="40"/>
-      <c r="T23" s="40"/>
-      <c r="U23" s="40"/>
-      <c r="V23" s="40"/>
-      <c r="W23" s="40"/>
-      <c r="X23" s="40"/>
-      <c r="Y23" s="40"/>
-      <c r="Z23" s="40"/>
-      <c r="AA23" s="40"/>
-      <c r="AB23" s="40"/>
-      <c r="AC23" s="40"/>
-    </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A24" s="40">
-        <v>22001</v>
-      </c>
-      <c r="B24" s="40" t="s">
-        <v>137</v>
-      </c>
-      <c r="C24" s="41" t="s">
-        <v>138</v>
-      </c>
-      <c r="D24" s="40" t="str">
-        <f t="shared" si="9"/>
-        <v>STR_MOB_N_0002</v>
-      </c>
-      <c r="E24" s="40" t="str">
-        <f t="shared" si="10"/>
-        <v>STR_MOB_N_0002_DESC</v>
-      </c>
-      <c r="F24" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G24" s="40">
-        <v>0</v>
-      </c>
-      <c r="H24" s="40">
-        <v>0</v>
-      </c>
-      <c r="I24" s="40">
+      <c r="J24" s="33">
+        <v>0</v>
+      </c>
+      <c r="K24" s="33">
+        <v>0</v>
+      </c>
+      <c r="L24" s="33">
+        <v>0</v>
+      </c>
+      <c r="M24" s="33">
+        <v>0</v>
+      </c>
+      <c r="N24" s="33"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="33"/>
+      <c r="Q24" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="T24" s="33" t="s">
+        <v>297</v>
+      </c>
+      <c r="U24" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="V24" s="33" t="s">
+        <v>307</v>
+      </c>
+      <c r="W24" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="X24" s="33" t="s">
+        <v>309</v>
+      </c>
+      <c r="Y24" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="Z24" s="33" t="s">
+        <v>311</v>
+      </c>
+      <c r="AA24" s="33"/>
+      <c r="AB24" s="33"/>
+      <c r="AC24" s="33"/>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A25" s="33">
+        <v>20023</v>
+      </c>
+      <c r="B25" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="C25" s="35" t="s">
+        <v>295</v>
+      </c>
+      <c r="D25" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="E25" s="33" t="str">
+        <f t="shared" ref="E25" si="10">D25&amp;"_DESC"</f>
+        <v>STR_NPC_N_0022_DESC</v>
+      </c>
+      <c r="F25" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G25" s="33">
+        <v>0</v>
+      </c>
+      <c r="H25" s="33">
+        <v>0</v>
+      </c>
+      <c r="I25" s="33">
         <v>1</v>
       </c>
-      <c r="J24" s="40">
-        <v>0</v>
-      </c>
-      <c r="K24" s="40">
-        <v>0</v>
-      </c>
-      <c r="L24" s="40">
-        <v>0</v>
-      </c>
-      <c r="M24" s="40">
-        <v>10</v>
-      </c>
-      <c r="N24" s="40"/>
-      <c r="O24" s="40"/>
-      <c r="P24" s="40"/>
-      <c r="Q24" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="R24" s="40"/>
-      <c r="S24" s="40"/>
-      <c r="T24" s="40"/>
-      <c r="U24" s="40"/>
-      <c r="V24" s="40"/>
-      <c r="W24" s="40"/>
-      <c r="X24" s="40"/>
-      <c r="Y24" s="40"/>
-      <c r="Z24" s="40"/>
-      <c r="AA24" s="40"/>
-      <c r="AB24" s="40"/>
-      <c r="AC24" s="40"/>
-    </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A25" s="40">
-        <v>22002</v>
-      </c>
-      <c r="B25" s="41" t="s">
-        <v>251</v>
-      </c>
-      <c r="C25" s="42" t="s">
-        <v>288</v>
-      </c>
-      <c r="D25" s="40" t="str">
-        <f t="shared" ref="D25" si="11">"STR_"&amp;UPPER(C25)</f>
-        <v>STR_MOB_N_0003</v>
-      </c>
-      <c r="E25" s="40" t="str">
-        <f t="shared" ref="E25" si="12">D25&amp;"_DESC"</f>
-        <v>STR_MOB_N_0003_DESC</v>
-      </c>
-      <c r="F25" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G25" s="40">
-        <v>60</v>
-      </c>
-      <c r="H25" s="40">
+      <c r="J25" s="33">
+        <v>0</v>
+      </c>
+      <c r="K25" s="33">
+        <v>0</v>
+      </c>
+      <c r="L25" s="33">
+        <v>0</v>
+      </c>
+      <c r="M25" s="33">
+        <v>0</v>
+      </c>
+      <c r="N25" s="33"/>
+      <c r="O25" s="33"/>
+      <c r="P25" s="33"/>
+      <c r="Q25" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="T25" s="33" t="s">
+        <v>298</v>
+      </c>
+      <c r="U25" s="33" t="s">
+        <v>312</v>
+      </c>
+      <c r="V25" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="W25" s="33" t="s">
+        <v>314</v>
+      </c>
+      <c r="X25" s="33"/>
+      <c r="Y25" s="33"/>
+      <c r="Z25" s="33"/>
+      <c r="AA25" s="33"/>
+      <c r="AB25" s="33"/>
+      <c r="AC25" s="33"/>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A26" s="33">
+        <v>20024</v>
+      </c>
+      <c r="B26" s="34" t="s">
+        <v>299</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>301</v>
+      </c>
+      <c r="D26" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="E26" s="33" t="str">
+        <f t="shared" ref="E26" si="11">D26&amp;"_DESC"</f>
+        <v>STR_NPC_N_0022_DESC</v>
+      </c>
+      <c r="F26" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G26" s="33">
+        <v>0</v>
+      </c>
+      <c r="H26" s="33">
+        <v>0</v>
+      </c>
+      <c r="I26" s="33">
         <v>1</v>
       </c>
-      <c r="I25" s="40">
-        <v>1</v>
-      </c>
-      <c r="J25" s="40">
-        <v>0</v>
-      </c>
-      <c r="K25" s="40">
-        <v>1500</v>
-      </c>
-      <c r="L25" s="40">
-        <v>15</v>
-      </c>
-      <c r="M25" s="40">
-        <v>30</v>
-      </c>
-      <c r="N25" s="40" t="s">
-        <v>226</v>
-      </c>
-      <c r="O25" s="40"/>
-      <c r="P25" s="40"/>
-      <c r="Q25" s="40" t="s">
-        <v>102</v>
-      </c>
-      <c r="R25" s="40"/>
-      <c r="S25" s="40"/>
-      <c r="T25" s="40"/>
-      <c r="U25" s="40"/>
-      <c r="V25" s="40"/>
-      <c r="W25" s="40"/>
-      <c r="X25" s="40"/>
-      <c r="Y25" s="40"/>
-      <c r="Z25" s="40"/>
-      <c r="AA25" s="40"/>
-      <c r="AB25" s="40"/>
-      <c r="AC25" s="40"/>
-    </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A26" s="40">
-        <v>22003</v>
-      </c>
-      <c r="B26" s="41" t="s">
-        <v>245</v>
-      </c>
-      <c r="C26" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="D26" s="40" t="str">
-        <f t="shared" ref="D26" si="13">"STR_"&amp;UPPER(C26)</f>
-        <v>STR_MOB_N_0004</v>
-      </c>
-      <c r="E26" s="40" t="str">
-        <f t="shared" ref="E26" si="14">D26&amp;"_DESC"</f>
-        <v>STR_MOB_N_0004_DESC</v>
-      </c>
-      <c r="F26" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G26" s="40">
-        <v>25</v>
-      </c>
-      <c r="H26" s="40">
-        <v>1</v>
-      </c>
-      <c r="I26" s="40">
-        <v>1</v>
-      </c>
-      <c r="J26" s="40">
-        <v>0</v>
-      </c>
-      <c r="K26" s="40">
-        <v>1500</v>
-      </c>
-      <c r="L26" s="40">
-        <v>20</v>
-      </c>
-      <c r="M26" s="40">
-        <v>50</v>
-      </c>
-      <c r="N26" s="40" t="s">
-        <v>226</v>
-      </c>
-      <c r="O26" s="40"/>
-      <c r="P26" s="40"/>
-      <c r="Q26" s="40" t="s">
-        <v>246</v>
-      </c>
-      <c r="R26" s="40"/>
-      <c r="S26" s="40"/>
-      <c r="T26" s="40"/>
-      <c r="U26" s="40"/>
-      <c r="V26" s="40"/>
-      <c r="W26" s="40"/>
-      <c r="X26" s="40"/>
-      <c r="Y26" s="40"/>
-      <c r="Z26" s="40"/>
-      <c r="AA26" s="40"/>
-      <c r="AB26" s="40"/>
-      <c r="AC26" s="40"/>
+      <c r="J26" s="33">
+        <v>0</v>
+      </c>
+      <c r="K26" s="33">
+        <v>0</v>
+      </c>
+      <c r="L26" s="33">
+        <v>0</v>
+      </c>
+      <c r="M26" s="33">
+        <v>0</v>
+      </c>
+      <c r="N26" s="33"/>
+      <c r="O26" s="33"/>
+      <c r="P26" s="33"/>
+      <c r="Q26" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="T26" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="U26" s="33" t="s">
+        <v>315</v>
+      </c>
+      <c r="V26" s="33" t="s">
+        <v>316</v>
+      </c>
+      <c r="W26" s="33" t="s">
+        <v>317</v>
+      </c>
+      <c r="X26" s="33" t="s">
+        <v>318</v>
+      </c>
+      <c r="Y26" s="33"/>
+      <c r="Z26" s="33"/>
+      <c r="AA26" s="33"/>
+      <c r="AB26" s="33"/>
+      <c r="AC26" s="33"/>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A27" s="40">
-        <v>22004</v>
+        <v>22000</v>
       </c>
       <c r="B27" s="41" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C27" s="42" t="s">
-        <v>237</v>
+        <v>100</v>
       </c>
       <c r="D27" s="40" t="str">
-        <f t="shared" ref="D27:D34" si="15">"STR_"&amp;UPPER(C27)</f>
-        <v>STR_MOB_N_0005</v>
+        <f t="shared" ref="D27:D28" si="12">"STR_"&amp;UPPER(C27)</f>
+        <v>STR_MOB_N_0001</v>
       </c>
       <c r="E27" s="40" t="str">
-        <f t="shared" ref="E27:E34" si="16">D27&amp;"_DESC"</f>
-        <v>STR_MOB_N_0005_DESC</v>
+        <f t="shared" ref="E27:E39" si="13">D27&amp;"_DESC"</f>
+        <v>STR_MOB_N_0001_DESC</v>
       </c>
       <c r="F27" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G27" s="40">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H27" s="40">
         <v>1</v>
@@ -6820,18 +6943,18 @@
         <v>1200</v>
       </c>
       <c r="L27" s="40">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="M27" s="40">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N27" s="40" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O27" s="40"/>
       <c r="P27" s="40"/>
       <c r="Q27" s="40" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="R27" s="40"/>
       <c r="S27" s="40"/>
@@ -6848,30 +6971,30 @@
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A28" s="40">
-        <v>22005</v>
-      </c>
-      <c r="B28" s="41" t="s">
-        <v>250</v>
-      </c>
-      <c r="C28" s="42" t="s">
-        <v>238</v>
+        <v>22001</v>
+      </c>
+      <c r="B28" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="C28" s="41" t="s">
+        <v>138</v>
       </c>
       <c r="D28" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v>STR_MOB_N_0006</v>
+        <f t="shared" si="12"/>
+        <v>STR_MOB_N_0002</v>
       </c>
       <c r="E28" s="40" t="str">
-        <f t="shared" si="16"/>
-        <v>STR_MOB_N_0006_DESC</v>
+        <f t="shared" si="13"/>
+        <v>STR_MOB_N_0002_DESC</v>
       </c>
       <c r="F28" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G28" s="40">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H28" s="40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" s="40">
         <v>1</v>
@@ -6880,21 +7003,19 @@
         <v>0</v>
       </c>
       <c r="K28" s="40">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L28" s="40">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M28" s="40">
-        <v>25</v>
-      </c>
-      <c r="N28" s="40" t="s">
-        <v>226</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="N28" s="40"/>
       <c r="O28" s="40"/>
       <c r="P28" s="40"/>
       <c r="Q28" s="40" t="s">
-        <v>253</v>
+        <v>139</v>
       </c>
       <c r="R28" s="40"/>
       <c r="S28" s="40"/>
@@ -6911,21 +7032,21 @@
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A29" s="40">
-        <v>22006</v>
+        <v>22002</v>
       </c>
       <c r="B29" s="41" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C29" s="42" t="s">
-        <v>239</v>
+        <v>288</v>
       </c>
       <c r="D29" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v>STR_MOB_N_0007</v>
+        <f t="shared" ref="D29" si="14">"STR_"&amp;UPPER(C29)</f>
+        <v>STR_MOB_N_0003</v>
       </c>
       <c r="E29" s="40" t="str">
-        <f t="shared" si="16"/>
-        <v>STR_MOB_N_0007_DESC</v>
+        <f t="shared" ref="E29" si="15">D29&amp;"_DESC"</f>
+        <v>STR_MOB_N_0003_DESC</v>
       </c>
       <c r="F29" s="40" t="s">
         <v>101</v>
@@ -6943,13 +7064,13 @@
         <v>0</v>
       </c>
       <c r="K29" s="40">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="L29" s="40">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="M29" s="40">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="N29" s="40" t="s">
         <v>226</v>
@@ -6957,7 +7078,7 @@
       <c r="O29" s="40"/>
       <c r="P29" s="40"/>
       <c r="Q29" s="40" t="s">
-        <v>254</v>
+        <v>102</v>
       </c>
       <c r="R29" s="40"/>
       <c r="S29" s="40"/>
@@ -6974,27 +7095,27 @@
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A30" s="40">
-        <v>22007</v>
+        <v>22003</v>
       </c>
       <c r="B30" s="41" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="C30" s="42" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D30" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v>STR_MOB_N_0008</v>
+        <f t="shared" ref="D30" si="16">"STR_"&amp;UPPER(C30)</f>
+        <v>STR_MOB_N_0004</v>
       </c>
       <c r="E30" s="40" t="str">
-        <f t="shared" si="16"/>
-        <v>STR_MOB_N_0008_DESC</v>
+        <f t="shared" ref="E30" si="17">D30&amp;"_DESC"</f>
+        <v>STR_MOB_N_0004_DESC</v>
       </c>
       <c r="F30" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G30" s="40">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="H30" s="40">
         <v>1</v>
@@ -7006,13 +7127,13 @@
         <v>0</v>
       </c>
       <c r="K30" s="40">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="L30" s="40">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="M30" s="40">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="N30" s="40" t="s">
         <v>226</v>
@@ -7020,7 +7141,7 @@
       <c r="O30" s="40"/>
       <c r="P30" s="40"/>
       <c r="Q30" s="40" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="R30" s="40"/>
       <c r="S30" s="40"/>
@@ -7037,21 +7158,21 @@
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A31" s="40">
-        <v>22008</v>
+        <v>22004</v>
       </c>
       <c r="B31" s="41" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="C31" s="42" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D31" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v>STR_MOB_N_0009</v>
+        <f t="shared" ref="D31:D38" si="18">"STR_"&amp;UPPER(C31)</f>
+        <v>STR_MOB_N_0005</v>
       </c>
       <c r="E31" s="40" t="str">
-        <f t="shared" si="16"/>
-        <v>STR_MOB_N_0009_DESC</v>
+        <f t="shared" ref="E31:E38" si="19">D31&amp;"_DESC"</f>
+        <v>STR_MOB_N_0005_DESC</v>
       </c>
       <c r="F31" s="40" t="s">
         <v>101</v>
@@ -7069,13 +7190,13 @@
         <v>0</v>
       </c>
       <c r="K31" s="40">
-        <v>1800</v>
+        <v>1200</v>
       </c>
       <c r="L31" s="40">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M31" s="40">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N31" s="40" t="s">
         <v>226</v>
@@ -7083,7 +7204,7 @@
       <c r="O31" s="40"/>
       <c r="P31" s="40"/>
       <c r="Q31" s="40" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="R31" s="40"/>
       <c r="S31" s="40"/>
@@ -7100,45 +7221,45 @@
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A32" s="40">
-        <v>22009</v>
+        <v>22005</v>
       </c>
       <c r="B32" s="41" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="C32" s="42" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D32" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v>STR_MOB_N_0010</v>
+        <f t="shared" si="18"/>
+        <v>STR_MOB_N_0006</v>
       </c>
       <c r="E32" s="40" t="str">
-        <f t="shared" si="16"/>
-        <v>STR_MOB_N_0010_DESC</v>
+        <f t="shared" si="19"/>
+        <v>STR_MOB_N_0006_DESC</v>
       </c>
       <c r="F32" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G32" s="40">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H32" s="40">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I32" s="40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J32" s="40">
         <v>0</v>
       </c>
       <c r="K32" s="40">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="L32" s="40">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M32" s="40">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="N32" s="40" t="s">
         <v>226</v>
@@ -7146,12 +7267,10 @@
       <c r="O32" s="40"/>
       <c r="P32" s="40"/>
       <c r="Q32" s="40" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="R32" s="40"/>
-      <c r="S32" s="40" t="s">
-        <v>287</v>
-      </c>
+      <c r="S32" s="40"/>
       <c r="T32" s="40"/>
       <c r="U32" s="40"/>
       <c r="V32" s="40"/>
@@ -7165,45 +7284,45 @@
     </row>
     <row r="33" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A33" s="40">
-        <v>22010</v>
+        <v>22006</v>
       </c>
       <c r="B33" s="41" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C33" s="42" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D33" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v>STR_MOB_N_0011</v>
+        <f t="shared" si="18"/>
+        <v>STR_MOB_N_0007</v>
       </c>
       <c r="E33" s="40" t="str">
-        <f t="shared" si="16"/>
-        <v>STR_MOB_N_0011_DESC</v>
+        <f t="shared" si="19"/>
+        <v>STR_MOB_N_0007_DESC</v>
       </c>
       <c r="F33" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G33" s="40">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H33" s="40">
+        <v>1</v>
+      </c>
+      <c r="I33" s="40">
+        <v>1</v>
+      </c>
+      <c r="J33" s="40">
+        <v>0</v>
+      </c>
+      <c r="K33" s="40">
+        <v>900</v>
+      </c>
+      <c r="L33" s="40">
         <v>70</v>
       </c>
-      <c r="I33" s="40">
-        <v>5</v>
-      </c>
-      <c r="J33" s="40">
-        <v>0</v>
-      </c>
-      <c r="K33" s="40">
-        <v>1200</v>
-      </c>
-      <c r="L33" s="40">
-        <v>45</v>
-      </c>
       <c r="M33" s="40">
-        <v>250</v>
+        <v>35</v>
       </c>
       <c r="N33" s="40" t="s">
         <v>226</v>
@@ -7211,12 +7330,10 @@
       <c r="O33" s="40"/>
       <c r="P33" s="40"/>
       <c r="Q33" s="40" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="R33" s="40"/>
-      <c r="S33" s="40" t="s">
-        <v>287</v>
-      </c>
+      <c r="S33" s="40"/>
       <c r="T33" s="40"/>
       <c r="U33" s="40"/>
       <c r="V33" s="40"/>
@@ -7230,45 +7347,45 @@
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A34" s="40">
-        <v>22011</v>
+        <v>22007</v>
       </c>
       <c r="B34" s="41" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C34" s="42" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D34" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v>STR_MOB_N_0012</v>
+        <f t="shared" si="18"/>
+        <v>STR_MOB_N_0008</v>
       </c>
       <c r="E34" s="40" t="str">
-        <f t="shared" si="16"/>
-        <v>STR_MOB_N_0012_DESC</v>
+        <f t="shared" si="19"/>
+        <v>STR_MOB_N_0008_DESC</v>
       </c>
       <c r="F34" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G34" s="40">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="H34" s="40">
+        <v>1</v>
+      </c>
+      <c r="I34" s="40">
+        <v>1</v>
+      </c>
+      <c r="J34" s="40">
+        <v>0</v>
+      </c>
+      <c r="K34" s="40">
+        <v>800</v>
+      </c>
+      <c r="L34" s="40">
         <v>80</v>
       </c>
-      <c r="I34" s="40">
-        <v>4</v>
-      </c>
-      <c r="J34" s="40">
-        <v>0</v>
-      </c>
-      <c r="K34" s="40">
-        <v>1000</v>
-      </c>
-      <c r="L34" s="40">
-        <v>60</v>
-      </c>
       <c r="M34" s="40">
-        <v>200</v>
+        <v>45</v>
       </c>
       <c r="N34" s="40" t="s">
         <v>226</v>
@@ -7276,12 +7393,10 @@
       <c r="O34" s="40"/>
       <c r="P34" s="40"/>
       <c r="Q34" s="40" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="R34" s="40"/>
-      <c r="S34" s="40" t="s">
-        <v>287</v>
-      </c>
+      <c r="S34" s="40"/>
       <c r="T34" s="40"/>
       <c r="U34" s="40"/>
       <c r="V34" s="40"/>
@@ -7294,131 +7409,312 @@
       <c r="AC34" s="40"/>
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A35" s="33">
+      <c r="A35" s="40">
+        <v>22008</v>
+      </c>
+      <c r="B35" s="41" t="s">
+        <v>261</v>
+      </c>
+      <c r="C35" s="42" t="s">
+        <v>241</v>
+      </c>
+      <c r="D35" s="40" t="str">
+        <f t="shared" si="18"/>
+        <v>STR_MOB_N_0009</v>
+      </c>
+      <c r="E35" s="40" t="str">
+        <f t="shared" si="19"/>
+        <v>STR_MOB_N_0009_DESC</v>
+      </c>
+      <c r="F35" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G35" s="40">
+        <v>1</v>
+      </c>
+      <c r="H35" s="40">
+        <v>1</v>
+      </c>
+      <c r="I35" s="40">
+        <v>1</v>
+      </c>
+      <c r="J35" s="40">
+        <v>0</v>
+      </c>
+      <c r="K35" s="40">
+        <v>1800</v>
+      </c>
+      <c r="L35" s="40">
+        <v>20</v>
+      </c>
+      <c r="M35" s="40">
+        <v>5</v>
+      </c>
+      <c r="N35" s="40" t="s">
+        <v>226</v>
+      </c>
+      <c r="O35" s="40"/>
+      <c r="P35" s="40"/>
+      <c r="Q35" s="40" t="s">
+        <v>256</v>
+      </c>
+      <c r="R35" s="40"/>
+      <c r="S35" s="40"/>
+      <c r="T35" s="40"/>
+      <c r="U35" s="40"/>
+      <c r="V35" s="40"/>
+      <c r="W35" s="40"/>
+      <c r="X35" s="40"/>
+      <c r="Y35" s="40"/>
+      <c r="Z35" s="40"/>
+      <c r="AA35" s="40"/>
+      <c r="AB35" s="40"/>
+      <c r="AC35" s="40"/>
+    </row>
+    <row r="36" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A36" s="40">
+        <v>22009</v>
+      </c>
+      <c r="B36" s="41" t="s">
+        <v>264</v>
+      </c>
+      <c r="C36" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="D36" s="40" t="str">
+        <f t="shared" si="18"/>
+        <v>STR_MOB_N_0010</v>
+      </c>
+      <c r="E36" s="40" t="str">
+        <f t="shared" si="19"/>
+        <v>STR_MOB_N_0010_DESC</v>
+      </c>
+      <c r="F36" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G36" s="40">
+        <v>50</v>
+      </c>
+      <c r="H36" s="40">
+        <v>50</v>
+      </c>
+      <c r="I36" s="40">
+        <v>3</v>
+      </c>
+      <c r="J36" s="40">
+        <v>0</v>
+      </c>
+      <c r="K36" s="40">
+        <v>1500</v>
+      </c>
+      <c r="L36" s="40">
+        <v>0</v>
+      </c>
+      <c r="M36" s="40">
+        <v>70</v>
+      </c>
+      <c r="N36" s="40" t="s">
+        <v>226</v>
+      </c>
+      <c r="O36" s="40"/>
+      <c r="P36" s="40"/>
+      <c r="Q36" s="40" t="s">
+        <v>257</v>
+      </c>
+      <c r="R36" s="40"/>
+      <c r="S36" s="40" t="s">
+        <v>287</v>
+      </c>
+      <c r="T36" s="40"/>
+      <c r="U36" s="40"/>
+      <c r="V36" s="40"/>
+      <c r="W36" s="40"/>
+      <c r="X36" s="40"/>
+      <c r="Y36" s="40"/>
+      <c r="Z36" s="40"/>
+      <c r="AA36" s="40"/>
+      <c r="AB36" s="40"/>
+      <c r="AC36" s="40"/>
+    </row>
+    <row r="37" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A37" s="40">
+        <v>22010</v>
+      </c>
+      <c r="B37" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="C37" s="42" t="s">
+        <v>243</v>
+      </c>
+      <c r="D37" s="40" t="str">
+        <f t="shared" si="18"/>
+        <v>STR_MOB_N_0011</v>
+      </c>
+      <c r="E37" s="40" t="str">
+        <f t="shared" si="19"/>
+        <v>STR_MOB_N_0011_DESC</v>
+      </c>
+      <c r="F37" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G37" s="40">
+        <v>100</v>
+      </c>
+      <c r="H37" s="40">
+        <v>70</v>
+      </c>
+      <c r="I37" s="40">
+        <v>5</v>
+      </c>
+      <c r="J37" s="40">
+        <v>0</v>
+      </c>
+      <c r="K37" s="40">
+        <v>1200</v>
+      </c>
+      <c r="L37" s="40">
+        <v>45</v>
+      </c>
+      <c r="M37" s="40">
+        <v>250</v>
+      </c>
+      <c r="N37" s="40" t="s">
+        <v>226</v>
+      </c>
+      <c r="O37" s="40"/>
+      <c r="P37" s="40"/>
+      <c r="Q37" s="40" t="s">
+        <v>258</v>
+      </c>
+      <c r="R37" s="40"/>
+      <c r="S37" s="40" t="s">
+        <v>287</v>
+      </c>
+      <c r="T37" s="40"/>
+      <c r="U37" s="40"/>
+      <c r="V37" s="40"/>
+      <c r="W37" s="40"/>
+      <c r="X37" s="40"/>
+      <c r="Y37" s="40"/>
+      <c r="Z37" s="40"/>
+      <c r="AA37" s="40"/>
+      <c r="AB37" s="40"/>
+      <c r="AC37" s="40"/>
+    </row>
+    <row r="38" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A38" s="40">
+        <v>22011</v>
+      </c>
+      <c r="B38" s="41" t="s">
+        <v>263</v>
+      </c>
+      <c r="C38" s="42" t="s">
+        <v>244</v>
+      </c>
+      <c r="D38" s="40" t="str">
+        <f t="shared" si="18"/>
+        <v>STR_MOB_N_0012</v>
+      </c>
+      <c r="E38" s="40" t="str">
+        <f t="shared" si="19"/>
+        <v>STR_MOB_N_0012_DESC</v>
+      </c>
+      <c r="F38" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G38" s="40">
+        <v>120</v>
+      </c>
+      <c r="H38" s="40">
+        <v>80</v>
+      </c>
+      <c r="I38" s="40">
+        <v>4</v>
+      </c>
+      <c r="J38" s="40">
+        <v>0</v>
+      </c>
+      <c r="K38" s="40">
+        <v>1000</v>
+      </c>
+      <c r="L38" s="40">
+        <v>60</v>
+      </c>
+      <c r="M38" s="40">
+        <v>200</v>
+      </c>
+      <c r="N38" s="40" t="s">
+        <v>226</v>
+      </c>
+      <c r="O38" s="40"/>
+      <c r="P38" s="40"/>
+      <c r="Q38" s="40" t="s">
+        <v>259</v>
+      </c>
+      <c r="R38" s="40"/>
+      <c r="S38" s="40" t="s">
+        <v>287</v>
+      </c>
+      <c r="T38" s="40"/>
+      <c r="U38" s="40"/>
+      <c r="V38" s="40"/>
+      <c r="W38" s="40"/>
+      <c r="X38" s="40"/>
+      <c r="Y38" s="40"/>
+      <c r="Z38" s="40"/>
+      <c r="AA38" s="40"/>
+      <c r="AB38" s="40"/>
+      <c r="AC38" s="40"/>
+    </row>
+    <row r="39" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A39" s="33">
         <v>25000</v>
       </c>
-      <c r="B35" s="34" t="s">
+      <c r="B39" s="34" t="s">
         <v>204</v>
       </c>
-      <c r="C35" s="35" t="s">
+      <c r="C39" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="D35" s="33" t="s">
+      <c r="D39" s="33" t="s">
         <v>225</v>
       </c>
-      <c r="E35" s="33" t="str">
-        <f t="shared" si="10"/>
+      <c r="E39" s="33" t="str">
+        <f t="shared" si="13"/>
         <v>STR_BOX_N_0001_DESC</v>
       </c>
-      <c r="F35" s="33" t="s">
+      <c r="F39" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="G35" s="33">
-        <v>0</v>
-      </c>
-      <c r="H35" s="33">
-        <v>0</v>
-      </c>
-      <c r="I35" s="33">
+      <c r="G39" s="33">
+        <v>0</v>
+      </c>
+      <c r="H39" s="33">
+        <v>0</v>
+      </c>
+      <c r="I39" s="33">
         <v>1</v>
       </c>
-      <c r="J35" s="33">
-        <v>0</v>
-      </c>
-      <c r="K35" s="33">
-        <v>0</v>
-      </c>
-      <c r="L35" s="33">
-        <v>0</v>
-      </c>
-      <c r="M35" s="33">
-        <v>0</v>
-      </c>
-      <c r="N35" s="33" t="s">
+      <c r="J39" s="33">
+        <v>0</v>
+      </c>
+      <c r="K39" s="33">
+        <v>0</v>
+      </c>
+      <c r="L39" s="33">
+        <v>0</v>
+      </c>
+      <c r="M39" s="33">
+        <v>0</v>
+      </c>
+      <c r="N39" s="33" t="s">
         <v>207</v>
       </c>
-      <c r="O35" s="33"/>
-      <c r="P35" s="33"/>
-      <c r="Q35" s="36" t="s">
-        <v>206</v>
-      </c>
-      <c r="T35" s="33"/>
-      <c r="U35" s="33"/>
-      <c r="V35" s="33"/>
-      <c r="W35" s="33"/>
-      <c r="X35" s="33"/>
-      <c r="Y35" s="33"/>
-      <c r="Z35" s="33"/>
-      <c r="AA35" s="33"/>
-      <c r="AB35" s="33"/>
-      <c r="AC35" s="33"/>
-    </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A36" s="33"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
-      <c r="M36" s="33"/>
-      <c r="N36" s="33"/>
-      <c r="O36" s="33"/>
-      <c r="P36" s="33"/>
-      <c r="T36" s="33"/>
-      <c r="U36" s="33"/>
-      <c r="V36" s="33"/>
-      <c r="W36" s="33"/>
-      <c r="X36" s="33"/>
-      <c r="Y36" s="33"/>
-      <c r="Z36" s="33"/>
-      <c r="AA36" s="33"/>
-      <c r="AB36" s="33"/>
-      <c r="AC36" s="33"/>
-    </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A37" s="33"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33"/>
-      <c r="M37" s="33"/>
-      <c r="N37" s="33"/>
-      <c r="O37" s="33"/>
-      <c r="P37" s="33"/>
-      <c r="T37" s="33"/>
-      <c r="U37" s="33"/>
-      <c r="V37" s="33"/>
-      <c r="W37" s="33"/>
-      <c r="X37" s="33"/>
-      <c r="Y37" s="33"/>
-      <c r="Z37" s="33"/>
-      <c r="AA37" s="33"/>
-      <c r="AB37" s="33"/>
-      <c r="AC37" s="33"/>
-    </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A38" s="33"/>
-      <c r="B38" s="34"/>
-      <c r="D38" s="33"/>
-      <c r="E38" s="33"/>
-      <c r="M38" s="33"/>
-      <c r="N38" s="33"/>
-      <c r="O38" s="33"/>
-      <c r="P38" s="33"/>
-      <c r="T38" s="33"/>
-      <c r="U38" s="33"/>
-      <c r="V38" s="33"/>
-      <c r="W38" s="33"/>
-      <c r="X38" s="33"/>
-      <c r="Y38" s="33"/>
-      <c r="Z38" s="33"/>
-      <c r="AA38" s="33"/>
-      <c r="AB38" s="33"/>
-      <c r="AC38" s="33"/>
-    </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A39" s="33"/>
-      <c r="D39" s="33"/>
-      <c r="E39" s="33"/>
-      <c r="M39" s="33"/>
-      <c r="N39" s="33"/>
       <c r="O39" s="33"/>
       <c r="P39" s="33"/>
+      <c r="Q39" s="36" t="s">
+        <v>206</v>
+      </c>
       <c r="T39" s="33"/>
       <c r="U39" s="33"/>
       <c r="V39" s="33"/>
@@ -7470,6 +7766,7 @@
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A42" s="33"/>
+      <c r="B42" s="34"/>
       <c r="D42" s="33"/>
       <c r="E42" s="33"/>
       <c r="M42" s="33"/>
@@ -7489,7 +7786,6 @@
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A43" s="33"/>
-      <c r="B43" s="34"/>
       <c r="D43" s="33"/>
       <c r="E43" s="33"/>
       <c r="M43" s="33"/>
@@ -7566,6 +7862,7 @@
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A47" s="33"/>
+      <c r="B47" s="34"/>
       <c r="D47" s="33"/>
       <c r="E47" s="33"/>
       <c r="M47" s="33"/>
@@ -7583,6 +7880,82 @@
       <c r="AB47" s="33"/>
       <c r="AC47" s="33"/>
     </row>
+    <row r="48" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A48" s="33"/>
+      <c r="D48" s="33"/>
+      <c r="E48" s="33"/>
+      <c r="M48" s="33"/>
+      <c r="N48" s="33"/>
+      <c r="O48" s="33"/>
+      <c r="P48" s="33"/>
+      <c r="T48" s="33"/>
+      <c r="U48" s="33"/>
+      <c r="V48" s="33"/>
+      <c r="W48" s="33"/>
+      <c r="X48" s="33"/>
+      <c r="Y48" s="33"/>
+      <c r="Z48" s="33"/>
+      <c r="AA48" s="33"/>
+      <c r="AB48" s="33"/>
+      <c r="AC48" s="33"/>
+    </row>
+    <row r="49" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A49" s="33"/>
+      <c r="D49" s="33"/>
+      <c r="E49" s="33"/>
+      <c r="M49" s="33"/>
+      <c r="N49" s="33"/>
+      <c r="O49" s="33"/>
+      <c r="P49" s="33"/>
+      <c r="T49" s="33"/>
+      <c r="U49" s="33"/>
+      <c r="V49" s="33"/>
+      <c r="W49" s="33"/>
+      <c r="X49" s="33"/>
+      <c r="Y49" s="33"/>
+      <c r="Z49" s="33"/>
+      <c r="AA49" s="33"/>
+      <c r="AB49" s="33"/>
+      <c r="AC49" s="33"/>
+    </row>
+    <row r="50" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A50" s="33"/>
+      <c r="D50" s="33"/>
+      <c r="E50" s="33"/>
+      <c r="M50" s="33"/>
+      <c r="N50" s="33"/>
+      <c r="O50" s="33"/>
+      <c r="P50" s="33"/>
+      <c r="T50" s="33"/>
+      <c r="U50" s="33"/>
+      <c r="V50" s="33"/>
+      <c r="W50" s="33"/>
+      <c r="X50" s="33"/>
+      <c r="Y50" s="33"/>
+      <c r="Z50" s="33"/>
+      <c r="AA50" s="33"/>
+      <c r="AB50" s="33"/>
+      <c r="AC50" s="33"/>
+    </row>
+    <row r="51" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A51" s="33"/>
+      <c r="D51" s="33"/>
+      <c r="E51" s="33"/>
+      <c r="M51" s="33"/>
+      <c r="N51" s="33"/>
+      <c r="O51" s="33"/>
+      <c r="P51" s="33"/>
+      <c r="T51" s="33"/>
+      <c r="U51" s="33"/>
+      <c r="V51" s="33"/>
+      <c r="W51" s="33"/>
+      <c r="X51" s="33"/>
+      <c r="Y51" s="33"/>
+      <c r="Z51" s="33"/>
+      <c r="AA51" s="33"/>
+      <c r="AB51" s="33"/>
+      <c r="AC51" s="33"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:U2"/>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7595,7 +7968,7 @@
           <x14:formula1>
             <xm:f>Type!$A$2:$A$20</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F35</xm:sqref>
+          <xm:sqref>F2:F39</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/30_table/01_테스트버전/Table_Data_Npc.xlsx
+++ b/30_table/01_테스트버전/Table_Data_Npc.xlsx
@@ -6991,10 +6991,10 @@
         <v>101</v>
       </c>
       <c r="G28" s="40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" s="40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="40">
         <v>1</v>
@@ -7003,7 +7003,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="40">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="L28" s="40">
         <v>0</v>

--- a/30_table/01_테스트버전/Table_Data_Npc.xlsx
+++ b/30_table/01_테스트버전/Table_Data_Npc.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="344">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -751,18 +751,10 @@
     <t>STR_STORY_NPC_20016_06</t>
   </si>
   <si>
-    <t>보물상자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>box_n_0001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>npc_0008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>drop_0007</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1148,6 +1140,104 @@
   </si>
   <si>
     <t>STR_STORY_NPC_20025_05</t>
+  </si>
+  <si>
+    <t>박쥐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mob_n_0013</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mob_0014</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구울</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mob_n_0014</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mob_0013</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보물상자 01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보물상자 02</t>
+  </si>
+  <si>
+    <t>box_n_0002</t>
+  </si>
+  <si>
+    <t>STR_BOX_N_0002</t>
+  </si>
+  <si>
+    <t>보물상자 03</t>
+  </si>
+  <si>
+    <t>box_n_0003</t>
+  </si>
+  <si>
+    <t>STR_BOX_N_0003</t>
+  </si>
+  <si>
+    <t>chest_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chest_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지 상자 01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>damagn_box_n_0001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT</t>
+  </si>
+  <si>
+    <t>chest_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지 필드 01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trap_n_0001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_TRAP_N_0001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지 필드 02</t>
+  </si>
+  <si>
+    <t>trap_n_0002</t>
+  </si>
+  <si>
+    <t>STR_TRAP_N_0002</t>
+  </si>
+  <si>
+    <t>trap_03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trap_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4038,13 +4128,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="25" t="s">
+        <v>263</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="D10" s="20" t="s">
         <v>265</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>266</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>267</v>
       </c>
       <c r="E10" s="20">
         <v>0</v>
@@ -4056,7 +4146,7 @@
         <v>100</v>
       </c>
       <c r="H10" s="26" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -4376,13 +4466,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>282</v>
+      </c>
+      <c r="D20" s="25" t="s">
         <v>283</v>
-      </c>
-      <c r="C20" s="25" t="s">
-        <v>284</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>285</v>
       </c>
       <c r="E20" s="25" t="s">
         <v>43</v>
@@ -4394,7 +4484,7 @@
         <v>32</v>
       </c>
       <c r="H20" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -5145,7 +5235,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AC53"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" style="36" bestFit="1" customWidth="1"/>
@@ -5191,7 +5281,7 @@
         <v>73</v>
       </c>
       <c r="I1" s="39" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="J1" s="39" t="s">
         <v>75</v>
@@ -5221,7 +5311,7 @@
         <v>37</v>
       </c>
       <c r="S1" s="38" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="T1" s="38" t="s">
         <v>105</v>
@@ -5430,19 +5520,19 @@
         <v>131</v>
       </c>
       <c r="U4" s="33" t="s">
+        <v>206</v>
+      </c>
+      <c r="V4" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="W4" s="33" t="s">
         <v>208</v>
       </c>
-      <c r="V4" s="33" t="s">
+      <c r="X4" s="33" t="s">
         <v>209</v>
       </c>
-      <c r="W4" s="33" t="s">
+      <c r="Y4" s="33" t="s">
         <v>210</v>
-      </c>
-      <c r="X4" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y4" s="33" t="s">
-        <v>212</v>
       </c>
       <c r="Z4" s="33"/>
       <c r="AA4" s="33"/>
@@ -6309,13 +6399,13 @@
         <v>20016</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C18" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="D18" s="33" t="s">
         <v>214</v>
-      </c>
-      <c r="D18" s="33" t="s">
-        <v>216</v>
       </c>
       <c r="E18" s="33" t="str">
         <f t="shared" si="6"/>
@@ -6352,7 +6442,7 @@
         <v>99</v>
       </c>
       <c r="T18" s="33" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="U18" s="33"/>
       <c r="V18" s="33"/>
@@ -6369,13 +6459,13 @@
         <v>20017</v>
       </c>
       <c r="B19" s="34" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E19" s="33" t="str">
         <f t="shared" si="6"/>
@@ -6412,19 +6502,19 @@
         <v>125</v>
       </c>
       <c r="T19" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="U19" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="V19" s="33" t="s">
         <v>220</v>
       </c>
-      <c r="U19" s="33" t="s">
+      <c r="W19" s="33" t="s">
         <v>221</v>
       </c>
-      <c r="V19" s="33" t="s">
+      <c r="X19" s="33" t="s">
         <v>222</v>
-      </c>
-      <c r="W19" s="33" t="s">
-        <v>223</v>
-      </c>
-      <c r="X19" s="33" t="s">
-        <v>224</v>
       </c>
       <c r="Y19" s="33"/>
       <c r="Z19" s="33"/>
@@ -6437,13 +6527,13 @@
         <v>20018</v>
       </c>
       <c r="B20" s="34" t="s">
+        <v>227</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>228</v>
+      </c>
+      <c r="D20" s="33" t="s">
         <v>229</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>230</v>
-      </c>
-      <c r="D20" s="33" t="s">
-        <v>231</v>
       </c>
       <c r="E20" s="33" t="str">
         <f t="shared" ref="E20:E22" si="7">D20&amp;"_DESC"</f>
@@ -6480,16 +6570,16 @@
         <v>125</v>
       </c>
       <c r="T20" s="33" t="s">
+        <v>230</v>
+      </c>
+      <c r="U20" s="33" t="s">
+        <v>231</v>
+      </c>
+      <c r="V20" s="33" t="s">
         <v>232</v>
       </c>
-      <c r="U20" s="33" t="s">
+      <c r="W20" s="33" t="s">
         <v>233</v>
-      </c>
-      <c r="V20" s="33" t="s">
-        <v>234</v>
-      </c>
-      <c r="W20" s="33" t="s">
-        <v>235</v>
       </c>
       <c r="X20" s="33"/>
       <c r="Y20" s="33"/>
@@ -6503,13 +6593,13 @@
         <v>20019</v>
       </c>
       <c r="B21" s="34" t="s">
+        <v>215</v>
+      </c>
+      <c r="C21" s="35" t="s">
+        <v>268</v>
+      </c>
+      <c r="D21" s="33" t="s">
         <v>217</v>
-      </c>
-      <c r="C21" s="35" t="s">
-        <v>270</v>
-      </c>
-      <c r="D21" s="33" t="s">
-        <v>219</v>
       </c>
       <c r="E21" s="33" t="str">
         <f t="shared" ref="E21" si="8">D21&amp;"_DESC"</f>
@@ -6546,16 +6636,16 @@
         <v>125</v>
       </c>
       <c r="T21" s="33" t="s">
+        <v>270</v>
+      </c>
+      <c r="U21" s="33" t="s">
         <v>272</v>
       </c>
-      <c r="U21" s="33" t="s">
+      <c r="V21" s="33" t="s">
+        <v>273</v>
+      </c>
+      <c r="W21" s="33" t="s">
         <v>274</v>
-      </c>
-      <c r="V21" s="33" t="s">
-        <v>275</v>
-      </c>
-      <c r="W21" s="33" t="s">
-        <v>276</v>
       </c>
       <c r="X21" s="33"/>
       <c r="Y21" s="33"/>
@@ -6569,13 +6659,13 @@
         <v>20020</v>
       </c>
       <c r="B22" s="34" t="s">
+        <v>215</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="D22" s="33" t="s">
         <v>217</v>
-      </c>
-      <c r="C22" s="35" t="s">
-        <v>271</v>
-      </c>
-      <c r="D22" s="33" t="s">
-        <v>219</v>
       </c>
       <c r="E22" s="33" t="str">
         <f t="shared" si="7"/>
@@ -6612,22 +6702,22 @@
         <v>125</v>
       </c>
       <c r="T22" s="33" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="U22" s="33" t="s">
+        <v>275</v>
+      </c>
+      <c r="V22" s="33" t="s">
+        <v>276</v>
+      </c>
+      <c r="W22" s="33" t="s">
         <v>277</v>
       </c>
-      <c r="V22" s="33" t="s">
+      <c r="X22" s="33" t="s">
         <v>278</v>
       </c>
-      <c r="W22" s="33" t="s">
+      <c r="Y22" s="33" t="s">
         <v>279</v>
-      </c>
-      <c r="X22" s="33" t="s">
-        <v>280</v>
-      </c>
-      <c r="Y22" s="33" t="s">
-        <v>281</v>
       </c>
       <c r="Z22" s="33"/>
       <c r="AA22" s="33"/>
@@ -6639,13 +6729,13 @@
         <v>20021</v>
       </c>
       <c r="B23" s="34" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E23" s="33" t="str">
         <f t="shared" ref="E23:E24" si="9">D23&amp;"_DESC"</f>
@@ -6679,19 +6769,19 @@
       <c r="O23" s="33"/>
       <c r="P23" s="33"/>
       <c r="Q23" s="36" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="T23" s="33" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="U23" s="33" t="s">
+        <v>301</v>
+      </c>
+      <c r="V23" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="W23" s="33" t="s">
         <v>303</v>
-      </c>
-      <c r="V23" s="33" t="s">
-        <v>304</v>
-      </c>
-      <c r="W23" s="33" t="s">
-        <v>305</v>
       </c>
       <c r="X23" s="33"/>
       <c r="Y23" s="33"/>
@@ -6705,13 +6795,13 @@
         <v>20022</v>
       </c>
       <c r="B24" s="34" t="s">
+        <v>288</v>
+      </c>
+      <c r="C24" s="35" t="s">
+        <v>292</v>
+      </c>
+      <c r="D24" s="33" t="s">
         <v>290</v>
-      </c>
-      <c r="C24" s="35" t="s">
-        <v>294</v>
-      </c>
-      <c r="D24" s="33" t="s">
-        <v>292</v>
       </c>
       <c r="E24" s="33" t="str">
         <f t="shared" si="9"/>
@@ -6745,28 +6835,28 @@
       <c r="O24" s="33"/>
       <c r="P24" s="33"/>
       <c r="Q24" s="36" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="T24" s="33" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="U24" s="33" t="s">
+        <v>304</v>
+      </c>
+      <c r="V24" s="33" t="s">
+        <v>305</v>
+      </c>
+      <c r="W24" s="33" t="s">
         <v>306</v>
       </c>
-      <c r="V24" s="33" t="s">
+      <c r="X24" s="33" t="s">
         <v>307</v>
       </c>
-      <c r="W24" s="33" t="s">
+      <c r="Y24" s="33" t="s">
         <v>308</v>
       </c>
-      <c r="X24" s="33" t="s">
+      <c r="Z24" s="33" t="s">
         <v>309</v>
-      </c>
-      <c r="Y24" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="Z24" s="33" t="s">
-        <v>311</v>
       </c>
       <c r="AA24" s="33"/>
       <c r="AB24" s="33"/>
@@ -6777,13 +6867,13 @@
         <v>20023</v>
       </c>
       <c r="B25" s="34" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E25" s="33" t="str">
         <f t="shared" ref="E25" si="10">D25&amp;"_DESC"</f>
@@ -6817,19 +6907,19 @@
       <c r="O25" s="33"/>
       <c r="P25" s="33"/>
       <c r="Q25" s="36" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="T25" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="U25" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="V25" s="33" t="s">
+        <v>311</v>
+      </c>
+      <c r="W25" s="33" t="s">
         <v>312</v>
-      </c>
-      <c r="V25" s="33" t="s">
-        <v>313</v>
-      </c>
-      <c r="W25" s="33" t="s">
-        <v>314</v>
       </c>
       <c r="X25" s="33"/>
       <c r="Y25" s="33"/>
@@ -6843,13 +6933,13 @@
         <v>20024</v>
       </c>
       <c r="B26" s="34" t="s">
+        <v>297</v>
+      </c>
+      <c r="C26" s="35" t="s">
         <v>299</v>
       </c>
-      <c r="C26" s="35" t="s">
-        <v>301</v>
-      </c>
       <c r="D26" s="33" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E26" s="33" t="str">
         <f t="shared" ref="E26" si="11">D26&amp;"_DESC"</f>
@@ -6883,22 +6973,22 @@
       <c r="O26" s="33"/>
       <c r="P26" s="33"/>
       <c r="Q26" s="36" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="T26" s="33" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="U26" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="V26" s="33" t="s">
+        <v>314</v>
+      </c>
+      <c r="W26" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="V26" s="33" t="s">
+      <c r="X26" s="33" t="s">
         <v>316</v>
-      </c>
-      <c r="W26" s="33" t="s">
-        <v>317</v>
-      </c>
-      <c r="X26" s="33" t="s">
-        <v>318</v>
       </c>
       <c r="Y26" s="33"/>
       <c r="Z26" s="33"/>
@@ -6911,7 +7001,7 @@
         <v>22000</v>
       </c>
       <c r="B27" s="41" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C27" s="42" t="s">
         <v>100</v>
@@ -6921,7 +7011,7 @@
         <v>STR_MOB_N_0001</v>
       </c>
       <c r="E27" s="40" t="str">
-        <f t="shared" ref="E27:E39" si="13">D27&amp;"_DESC"</f>
+        <f t="shared" ref="E27:E41" si="13">D27&amp;"_DESC"</f>
         <v>STR_MOB_N_0001_DESC</v>
       </c>
       <c r="F27" s="40" t="s">
@@ -6949,12 +7039,12 @@
         <v>20</v>
       </c>
       <c r="N27" s="40" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O27" s="40"/>
       <c r="P27" s="40"/>
       <c r="Q27" s="40" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="R27" s="40"/>
       <c r="S27" s="40"/>
@@ -7035,10 +7125,10 @@
         <v>22002</v>
       </c>
       <c r="B29" s="41" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C29" s="42" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D29" s="40" t="str">
         <f t="shared" ref="D29" si="14">"STR_"&amp;UPPER(C29)</f>
@@ -7073,7 +7163,7 @@
         <v>30</v>
       </c>
       <c r="N29" s="40" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O29" s="40"/>
       <c r="P29" s="40"/>
@@ -7098,10 +7188,10 @@
         <v>22003</v>
       </c>
       <c r="B30" s="41" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C30" s="42" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D30" s="40" t="str">
         <f t="shared" ref="D30" si="16">"STR_"&amp;UPPER(C30)</f>
@@ -7136,12 +7226,12 @@
         <v>50</v>
       </c>
       <c r="N30" s="40" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O30" s="40"/>
       <c r="P30" s="40"/>
       <c r="Q30" s="40" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="R30" s="40"/>
       <c r="S30" s="40"/>
@@ -7161,17 +7251,17 @@
         <v>22004</v>
       </c>
       <c r="B31" s="41" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C31" s="42" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D31" s="40" t="str">
-        <f t="shared" ref="D31:D38" si="18">"STR_"&amp;UPPER(C31)</f>
+        <f t="shared" ref="D31:D39" si="18">"STR_"&amp;UPPER(C31)</f>
         <v>STR_MOB_N_0005</v>
       </c>
       <c r="E31" s="40" t="str">
-        <f t="shared" ref="E31:E38" si="19">D31&amp;"_DESC"</f>
+        <f t="shared" ref="E31:E39" si="19">D31&amp;"_DESC"</f>
         <v>STR_MOB_N_0005_DESC</v>
       </c>
       <c r="F31" s="40" t="s">
@@ -7199,12 +7289,12 @@
         <v>10</v>
       </c>
       <c r="N31" s="40" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O31" s="40"/>
       <c r="P31" s="40"/>
       <c r="Q31" s="40" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="R31" s="40"/>
       <c r="S31" s="40"/>
@@ -7224,10 +7314,10 @@
         <v>22005</v>
       </c>
       <c r="B32" s="41" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C32" s="42" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D32" s="40" t="str">
         <f t="shared" si="18"/>
@@ -7262,12 +7352,12 @@
         <v>25</v>
       </c>
       <c r="N32" s="40" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O32" s="40"/>
       <c r="P32" s="40"/>
       <c r="Q32" s="40" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="R32" s="40"/>
       <c r="S32" s="40"/>
@@ -7287,10 +7377,10 @@
         <v>22006</v>
       </c>
       <c r="B33" s="41" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C33" s="42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D33" s="40" t="str">
         <f t="shared" si="18"/>
@@ -7325,12 +7415,12 @@
         <v>35</v>
       </c>
       <c r="N33" s="40" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O33" s="40"/>
       <c r="P33" s="40"/>
       <c r="Q33" s="40" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="R33" s="40"/>
       <c r="S33" s="40"/>
@@ -7350,10 +7440,10 @@
         <v>22007</v>
       </c>
       <c r="B34" s="41" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C34" s="42" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D34" s="40" t="str">
         <f t="shared" si="18"/>
@@ -7388,12 +7478,12 @@
         <v>45</v>
       </c>
       <c r="N34" s="40" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O34" s="40"/>
       <c r="P34" s="40"/>
       <c r="Q34" s="40" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="R34" s="40"/>
       <c r="S34" s="40"/>
@@ -7413,10 +7503,10 @@
         <v>22008</v>
       </c>
       <c r="B35" s="41" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C35" s="42" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D35" s="40" t="str">
         <f t="shared" si="18"/>
@@ -7451,12 +7541,12 @@
         <v>5</v>
       </c>
       <c r="N35" s="40" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O35" s="40"/>
       <c r="P35" s="40"/>
       <c r="Q35" s="40" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="R35" s="40"/>
       <c r="S35" s="40"/>
@@ -7476,10 +7566,10 @@
         <v>22009</v>
       </c>
       <c r="B36" s="41" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C36" s="42" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D36" s="40" t="str">
         <f t="shared" si="18"/>
@@ -7514,16 +7604,16 @@
         <v>70</v>
       </c>
       <c r="N36" s="40" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O36" s="40"/>
       <c r="P36" s="40"/>
       <c r="Q36" s="40" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="R36" s="40"/>
       <c r="S36" s="40" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="T36" s="40"/>
       <c r="U36" s="40"/>
@@ -7541,10 +7631,10 @@
         <v>22010</v>
       </c>
       <c r="B37" s="41" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C37" s="42" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D37" s="40" t="str">
         <f t="shared" si="18"/>
@@ -7579,16 +7669,16 @@
         <v>250</v>
       </c>
       <c r="N37" s="40" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O37" s="40"/>
       <c r="P37" s="40"/>
       <c r="Q37" s="40" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="R37" s="40"/>
       <c r="S37" s="40" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="T37" s="40"/>
       <c r="U37" s="40"/>
@@ -7606,10 +7696,10 @@
         <v>22011</v>
       </c>
       <c r="B38" s="41" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C38" s="42" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D38" s="40" t="str">
         <f t="shared" si="18"/>
@@ -7644,16 +7734,16 @@
         <v>200</v>
       </c>
       <c r="N38" s="40" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O38" s="40"/>
       <c r="P38" s="40"/>
       <c r="Q38" s="40" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="R38" s="40"/>
       <c r="S38" s="40" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="T38" s="40"/>
       <c r="U38" s="40"/>
@@ -7667,92 +7757,182 @@
       <c r="AC38" s="40"/>
     </row>
     <row r="39" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A39" s="33">
+      <c r="A39" s="40">
+        <v>22012</v>
+      </c>
+      <c r="B39" s="41" t="s">
+        <v>317</v>
+      </c>
+      <c r="C39" s="42" t="s">
+        <v>318</v>
+      </c>
+      <c r="D39" s="40" t="str">
+        <f t="shared" si="18"/>
+        <v>STR_MOB_N_0013</v>
+      </c>
+      <c r="E39" s="40" t="str">
+        <f t="shared" si="19"/>
+        <v>STR_MOB_N_0013_DESC</v>
+      </c>
+      <c r="F39" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G39" s="40">
+        <v>25</v>
+      </c>
+      <c r="H39" s="40">
+        <v>1</v>
+      </c>
+      <c r="I39" s="40">
+        <v>1</v>
+      </c>
+      <c r="J39" s="40">
+        <v>0</v>
+      </c>
+      <c r="K39" s="40">
+        <v>1500</v>
+      </c>
+      <c r="L39" s="40">
+        <v>20</v>
+      </c>
+      <c r="M39" s="40">
+        <v>1</v>
+      </c>
+      <c r="N39" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="O39" s="40"/>
+      <c r="P39" s="40"/>
+      <c r="Q39" s="40" t="s">
+        <v>319</v>
+      </c>
+      <c r="R39" s="40"/>
+      <c r="S39" s="40"/>
+      <c r="T39" s="40"/>
+      <c r="U39" s="40"/>
+      <c r="V39" s="40"/>
+      <c r="W39" s="40"/>
+      <c r="X39" s="40"/>
+      <c r="Y39" s="40"/>
+      <c r="Z39" s="40"/>
+      <c r="AA39" s="40"/>
+      <c r="AB39" s="40"/>
+      <c r="AC39" s="40"/>
+    </row>
+    <row r="40" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A40" s="40">
+        <v>22013</v>
+      </c>
+      <c r="B40" s="41" t="s">
+        <v>320</v>
+      </c>
+      <c r="C40" s="42" t="s">
+        <v>321</v>
+      </c>
+      <c r="D40" s="40" t="str">
+        <f t="shared" ref="D40" si="20">"STR_"&amp;UPPER(C40)</f>
+        <v>STR_MOB_N_0014</v>
+      </c>
+      <c r="E40" s="40" t="str">
+        <f t="shared" ref="E40" si="21">D40&amp;"_DESC"</f>
+        <v>STR_MOB_N_0014_DESC</v>
+      </c>
+      <c r="F40" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G40" s="40">
+        <v>20</v>
+      </c>
+      <c r="H40" s="40">
+        <v>60</v>
+      </c>
+      <c r="I40" s="40">
+        <v>3</v>
+      </c>
+      <c r="J40" s="40">
+        <v>0</v>
+      </c>
+      <c r="K40" s="40">
+        <v>1500</v>
+      </c>
+      <c r="L40" s="40">
+        <v>15</v>
+      </c>
+      <c r="M40" s="40">
+        <v>70</v>
+      </c>
+      <c r="N40" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="O40" s="40"/>
+      <c r="P40" s="40"/>
+      <c r="Q40" s="40" t="s">
+        <v>322</v>
+      </c>
+      <c r="R40" s="40"/>
+      <c r="S40" s="40" t="s">
+        <v>285</v>
+      </c>
+      <c r="T40" s="40"/>
+      <c r="U40" s="40"/>
+      <c r="V40" s="40"/>
+      <c r="W40" s="40"/>
+      <c r="X40" s="40"/>
+      <c r="Y40" s="40"/>
+      <c r="Z40" s="40"/>
+      <c r="AA40" s="40"/>
+      <c r="AB40" s="40"/>
+      <c r="AC40" s="40"/>
+    </row>
+    <row r="41" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A41" s="33">
         <v>25000</v>
       </c>
-      <c r="B39" s="34" t="s">
+      <c r="B41" s="34" t="s">
+        <v>323</v>
+      </c>
+      <c r="C41" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="C39" s="35" t="s">
-        <v>205</v>
-      </c>
-      <c r="D39" s="33" t="s">
-        <v>225</v>
-      </c>
-      <c r="E39" s="33" t="str">
+      <c r="D41" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="E41" s="33" t="str">
         <f t="shared" si="13"/>
         <v>STR_BOX_N_0001_DESC</v>
       </c>
-      <c r="F39" s="33" t="s">
+      <c r="F41" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="G39" s="33">
-        <v>0</v>
-      </c>
-      <c r="H39" s="33">
-        <v>0</v>
-      </c>
-      <c r="I39" s="33">
+      <c r="G41" s="33">
+        <v>0</v>
+      </c>
+      <c r="H41" s="33">
+        <v>0</v>
+      </c>
+      <c r="I41" s="33">
         <v>1</v>
       </c>
-      <c r="J39" s="33">
-        <v>0</v>
-      </c>
-      <c r="K39" s="33">
-        <v>0</v>
-      </c>
-      <c r="L39" s="33">
-        <v>0</v>
-      </c>
-      <c r="M39" s="33">
-        <v>0</v>
-      </c>
-      <c r="N39" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="O39" s="33"/>
-      <c r="P39" s="33"/>
-      <c r="Q39" s="36" t="s">
-        <v>206</v>
-      </c>
-      <c r="T39" s="33"/>
-      <c r="U39" s="33"/>
-      <c r="V39" s="33"/>
-      <c r="W39" s="33"/>
-      <c r="X39" s="33"/>
-      <c r="Y39" s="33"/>
-      <c r="Z39" s="33"/>
-      <c r="AA39" s="33"/>
-      <c r="AB39" s="33"/>
-      <c r="AC39" s="33"/>
-    </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A40" s="33"/>
-      <c r="D40" s="33"/>
-      <c r="E40" s="33"/>
-      <c r="M40" s="33"/>
-      <c r="N40" s="33"/>
-      <c r="O40" s="33"/>
-      <c r="P40" s="33"/>
-      <c r="T40" s="33"/>
-      <c r="U40" s="33"/>
-      <c r="V40" s="33"/>
-      <c r="W40" s="33"/>
-      <c r="X40" s="33"/>
-      <c r="Y40" s="33"/>
-      <c r="Z40" s="33"/>
-      <c r="AA40" s="33"/>
-      <c r="AB40" s="33"/>
-      <c r="AC40" s="33"/>
-    </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A41" s="33"/>
-      <c r="D41" s="33"/>
-      <c r="E41" s="33"/>
-      <c r="M41" s="33"/>
-      <c r="N41" s="33"/>
+      <c r="J41" s="33">
+        <v>0</v>
+      </c>
+      <c r="K41" s="33">
+        <v>0</v>
+      </c>
+      <c r="L41" s="33">
+        <v>0</v>
+      </c>
+      <c r="M41" s="33">
+        <v>0</v>
+      </c>
+      <c r="N41" s="33" t="s">
+        <v>205</v>
+      </c>
       <c r="O41" s="33"/>
       <c r="P41" s="33"/>
+      <c r="Q41" s="36" t="s">
+        <v>330</v>
+      </c>
       <c r="T41" s="33"/>
       <c r="U41" s="33"/>
       <c r="V41" s="33"/>
@@ -7765,14 +7945,54 @@
       <c r="AC41" s="33"/>
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A42" s="33"/>
-      <c r="B42" s="34"/>
-      <c r="D42" s="33"/>
-      <c r="E42" s="33"/>
-      <c r="M42" s="33"/>
-      <c r="N42" s="33"/>
+      <c r="A42" s="33">
+        <v>25001</v>
+      </c>
+      <c r="B42" s="34" t="s">
+        <v>324</v>
+      </c>
+      <c r="C42" s="35" t="s">
+        <v>325</v>
+      </c>
+      <c r="D42" s="33" t="s">
+        <v>326</v>
+      </c>
+      <c r="E42" s="33" t="str">
+        <f t="shared" ref="E42:E44" si="22">D42&amp;"_DESC"</f>
+        <v>STR_BOX_N_0002_DESC</v>
+      </c>
+      <c r="F42" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G42" s="33">
+        <v>0</v>
+      </c>
+      <c r="H42" s="33">
+        <v>0</v>
+      </c>
+      <c r="I42" s="33">
+        <v>1</v>
+      </c>
+      <c r="J42" s="33">
+        <v>0</v>
+      </c>
+      <c r="K42" s="33">
+        <v>0</v>
+      </c>
+      <c r="L42" s="33">
+        <v>0</v>
+      </c>
+      <c r="M42" s="33">
+        <v>0</v>
+      </c>
+      <c r="N42" s="33" t="s">
+        <v>205</v>
+      </c>
       <c r="O42" s="33"/>
       <c r="P42" s="33"/>
+      <c r="Q42" s="36" t="s">
+        <v>330</v>
+      </c>
       <c r="T42" s="33"/>
       <c r="U42" s="33"/>
       <c r="V42" s="33"/>
@@ -7785,13 +8005,54 @@
       <c r="AC42" s="33"/>
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A43" s="33"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="33"/>
-      <c r="M43" s="33"/>
-      <c r="N43" s="33"/>
+      <c r="A43" s="33">
+        <v>25002</v>
+      </c>
+      <c r="B43" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="C43" s="35" t="s">
+        <v>328</v>
+      </c>
+      <c r="D43" s="33" t="s">
+        <v>329</v>
+      </c>
+      <c r="E43" s="33" t="str">
+        <f t="shared" si="22"/>
+        <v>STR_BOX_N_0003_DESC</v>
+      </c>
+      <c r="F43" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G43" s="33">
+        <v>0</v>
+      </c>
+      <c r="H43" s="33">
+        <v>0</v>
+      </c>
+      <c r="I43" s="33">
+        <v>1</v>
+      </c>
+      <c r="J43" s="33">
+        <v>0</v>
+      </c>
+      <c r="K43" s="33">
+        <v>0</v>
+      </c>
+      <c r="L43" s="33">
+        <v>0</v>
+      </c>
+      <c r="M43" s="33">
+        <v>0</v>
+      </c>
+      <c r="N43" s="33" t="s">
+        <v>205</v>
+      </c>
       <c r="O43" s="33"/>
       <c r="P43" s="33"/>
+      <c r="Q43" s="36" t="s">
+        <v>331</v>
+      </c>
       <c r="T43" s="33"/>
       <c r="U43" s="33"/>
       <c r="V43" s="33"/>
@@ -7804,65 +8065,187 @@
       <c r="AC43" s="33"/>
     </row>
     <row r="44" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A44" s="33"/>
-      <c r="D44" s="33"/>
-      <c r="E44" s="33"/>
-      <c r="M44" s="33"/>
-      <c r="N44" s="33"/>
-      <c r="O44" s="33"/>
-      <c r="P44" s="33"/>
-      <c r="T44" s="33"/>
-      <c r="U44" s="33"/>
-      <c r="V44" s="33"/>
-      <c r="W44" s="33"/>
-      <c r="X44" s="33"/>
-      <c r="Y44" s="33"/>
-      <c r="Z44" s="33"/>
-      <c r="AA44" s="33"/>
-      <c r="AB44" s="33"/>
-      <c r="AC44" s="33"/>
+      <c r="A44" s="40">
+        <v>26000</v>
+      </c>
+      <c r="B44" s="41" t="s">
+        <v>332</v>
+      </c>
+      <c r="C44" s="42" t="s">
+        <v>333</v>
+      </c>
+      <c r="D44" s="40" t="s">
+        <v>223</v>
+      </c>
+      <c r="E44" s="40" t="str">
+        <f t="shared" si="22"/>
+        <v>STR_BOX_N_0001_DESC</v>
+      </c>
+      <c r="F44" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="G44" s="40">
+        <v>300</v>
+      </c>
+      <c r="H44" s="40">
+        <v>0</v>
+      </c>
+      <c r="I44" s="40">
+        <v>1</v>
+      </c>
+      <c r="J44" s="40">
+        <v>0</v>
+      </c>
+      <c r="K44" s="40">
+        <v>0</v>
+      </c>
+      <c r="L44" s="40">
+        <v>0</v>
+      </c>
+      <c r="M44" s="40">
+        <v>0</v>
+      </c>
+      <c r="N44" s="40"/>
+      <c r="O44" s="40"/>
+      <c r="P44" s="40"/>
+      <c r="Q44" s="40" t="s">
+        <v>335</v>
+      </c>
+      <c r="R44" s="40"/>
+      <c r="S44" s="40"/>
+      <c r="T44" s="40"/>
+      <c r="U44" s="40"/>
+      <c r="V44" s="40"/>
+      <c r="W44" s="40"/>
+      <c r="X44" s="40"/>
+      <c r="Y44" s="40"/>
+      <c r="Z44" s="40"/>
+      <c r="AA44" s="40"/>
+      <c r="AB44" s="40"/>
+      <c r="AC44" s="40"/>
     </row>
     <row r="45" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A45" s="33"/>
-      <c r="D45" s="33"/>
-      <c r="E45" s="33"/>
-      <c r="M45" s="33"/>
-      <c r="N45" s="33"/>
-      <c r="O45" s="33"/>
-      <c r="P45" s="33"/>
-      <c r="T45" s="33"/>
-      <c r="U45" s="33"/>
-      <c r="V45" s="33"/>
-      <c r="W45" s="33"/>
-      <c r="X45" s="33"/>
-      <c r="Y45" s="33"/>
-      <c r="Z45" s="33"/>
-      <c r="AA45" s="33"/>
-      <c r="AB45" s="33"/>
-      <c r="AC45" s="33"/>
+      <c r="A45" s="40">
+        <v>26001</v>
+      </c>
+      <c r="B45" s="41" t="s">
+        <v>336</v>
+      </c>
+      <c r="C45" s="42" t="s">
+        <v>337</v>
+      </c>
+      <c r="D45" s="40" t="s">
+        <v>338</v>
+      </c>
+      <c r="E45" s="40" t="str">
+        <f t="shared" ref="E45:E46" si="23">D45&amp;"_DESC"</f>
+        <v>STR_TRAP_N_0001_DESC</v>
+      </c>
+      <c r="F45" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="G45" s="40">
+        <v>300</v>
+      </c>
+      <c r="H45" s="40">
+        <v>0</v>
+      </c>
+      <c r="I45" s="40">
+        <v>1</v>
+      </c>
+      <c r="J45" s="40">
+        <v>0</v>
+      </c>
+      <c r="K45" s="40">
+        <v>2000</v>
+      </c>
+      <c r="L45" s="40">
+        <v>0</v>
+      </c>
+      <c r="M45" s="40">
+        <v>0</v>
+      </c>
+      <c r="N45" s="40"/>
+      <c r="O45" s="40"/>
+      <c r="P45" s="40"/>
+      <c r="Q45" s="40" t="s">
+        <v>342</v>
+      </c>
+      <c r="R45" s="40"/>
+      <c r="S45" s="40"/>
+      <c r="T45" s="40"/>
+      <c r="U45" s="40"/>
+      <c r="V45" s="40"/>
+      <c r="W45" s="40"/>
+      <c r="X45" s="40"/>
+      <c r="Y45" s="40"/>
+      <c r="Z45" s="40"/>
+      <c r="AA45" s="40"/>
+      <c r="AB45" s="40"/>
+      <c r="AC45" s="40"/>
     </row>
     <row r="46" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A46" s="33"/>
-      <c r="D46" s="33"/>
-      <c r="E46" s="33"/>
-      <c r="M46" s="33"/>
-      <c r="N46" s="33"/>
-      <c r="O46" s="33"/>
-      <c r="P46" s="33"/>
-      <c r="T46" s="33"/>
-      <c r="U46" s="33"/>
-      <c r="V46" s="33"/>
-      <c r="W46" s="33"/>
-      <c r="X46" s="33"/>
-      <c r="Y46" s="33"/>
-      <c r="Z46" s="33"/>
-      <c r="AA46" s="33"/>
-      <c r="AB46" s="33"/>
-      <c r="AC46" s="33"/>
+      <c r="A46" s="40">
+        <v>26002</v>
+      </c>
+      <c r="B46" s="41" t="s">
+        <v>339</v>
+      </c>
+      <c r="C46" s="42" t="s">
+        <v>340</v>
+      </c>
+      <c r="D46" s="40" t="s">
+        <v>341</v>
+      </c>
+      <c r="E46" s="40" t="str">
+        <f t="shared" si="23"/>
+        <v>STR_TRAP_N_0002_DESC</v>
+      </c>
+      <c r="F46" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="G46" s="40">
+        <v>0</v>
+      </c>
+      <c r="H46" s="40">
+        <v>0</v>
+      </c>
+      <c r="I46" s="40">
+        <v>1</v>
+      </c>
+      <c r="J46" s="40">
+        <v>0</v>
+      </c>
+      <c r="K46" s="40">
+        <v>0</v>
+      </c>
+      <c r="L46" s="40">
+        <v>0</v>
+      </c>
+      <c r="M46" s="40">
+        <v>0</v>
+      </c>
+      <c r="N46" s="40"/>
+      <c r="O46" s="40"/>
+      <c r="P46" s="40"/>
+      <c r="Q46" s="40" t="s">
+        <v>343</v>
+      </c>
+      <c r="R46" s="40"/>
+      <c r="S46" s="40"/>
+      <c r="T46" s="40"/>
+      <c r="U46" s="40"/>
+      <c r="V46" s="40"/>
+      <c r="W46" s="40"/>
+      <c r="X46" s="40"/>
+      <c r="Y46" s="40"/>
+      <c r="Z46" s="40"/>
+      <c r="AA46" s="40"/>
+      <c r="AB46" s="40"/>
+      <c r="AC46" s="40"/>
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A47" s="33"/>
-      <c r="B47" s="34"/>
       <c r="D47" s="33"/>
       <c r="E47" s="33"/>
       <c r="M47" s="33"/>
@@ -7901,6 +8284,7 @@
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A49" s="33"/>
+      <c r="B49" s="34"/>
       <c r="D49" s="33"/>
       <c r="E49" s="33"/>
       <c r="M49" s="33"/>
@@ -7956,6 +8340,44 @@
       <c r="AB51" s="33"/>
       <c r="AC51" s="33"/>
     </row>
+    <row r="52" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A52" s="33"/>
+      <c r="D52" s="33"/>
+      <c r="E52" s="33"/>
+      <c r="M52" s="33"/>
+      <c r="N52" s="33"/>
+      <c r="O52" s="33"/>
+      <c r="P52" s="33"/>
+      <c r="T52" s="33"/>
+      <c r="U52" s="33"/>
+      <c r="V52" s="33"/>
+      <c r="W52" s="33"/>
+      <c r="X52" s="33"/>
+      <c r="Y52" s="33"/>
+      <c r="Z52" s="33"/>
+      <c r="AA52" s="33"/>
+      <c r="AB52" s="33"/>
+      <c r="AC52" s="33"/>
+    </row>
+    <row r="53" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A53" s="33"/>
+      <c r="D53" s="33"/>
+      <c r="E53" s="33"/>
+      <c r="M53" s="33"/>
+      <c r="N53" s="33"/>
+      <c r="O53" s="33"/>
+      <c r="P53" s="33"/>
+      <c r="T53" s="33"/>
+      <c r="U53" s="33"/>
+      <c r="V53" s="33"/>
+      <c r="W53" s="33"/>
+      <c r="X53" s="33"/>
+      <c r="Y53" s="33"/>
+      <c r="Z53" s="33"/>
+      <c r="AA53" s="33"/>
+      <c r="AB53" s="33"/>
+      <c r="AC53" s="33"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:U2"/>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7968,7 +8390,7 @@
           <x14:formula1>
             <xm:f>Type!$A$2:$A$20</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F39</xm:sqref>
+          <xm:sqref>F2:F46</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/30_table/01_테스트버전/Table_Data_Npc.xlsx
+++ b/30_table/01_테스트버전/Table_Data_Npc.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="352">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1237,6 +1237,35 @@
   </si>
   <si>
     <t>trap_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>문 01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>door_n_0001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_DOOR_N_0001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>door_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trap_n_0003</t>
+  </si>
+  <si>
+    <t>STR_TRAP_N_0003</t>
+  </si>
+  <si>
+    <t>데미지 필드 03</t>
+  </si>
+  <si>
+    <t>empty</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5235,7 +5264,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AC53"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" style="36" bestFit="1" customWidth="1"/>
@@ -8138,7 +8167,7 @@
         <v>338</v>
       </c>
       <c r="E45" s="40" t="str">
-        <f t="shared" ref="E45:E46" si="23">D45&amp;"_DESC"</f>
+        <f t="shared" ref="E45:E48" si="23">D45&amp;"_DESC"</f>
         <v>STR_TRAP_N_0001_DESC</v>
       </c>
       <c r="F45" s="40" t="s">
@@ -8245,32 +8274,112 @@
       <c r="AC46" s="40"/>
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A47" s="33"/>
-      <c r="D47" s="33"/>
-      <c r="E47" s="33"/>
-      <c r="M47" s="33"/>
-      <c r="N47" s="33"/>
-      <c r="O47" s="33"/>
-      <c r="P47" s="33"/>
-      <c r="T47" s="33"/>
-      <c r="U47" s="33"/>
-      <c r="V47" s="33"/>
-      <c r="W47" s="33"/>
-      <c r="X47" s="33"/>
-      <c r="Y47" s="33"/>
-      <c r="Z47" s="33"/>
-      <c r="AA47" s="33"/>
-      <c r="AB47" s="33"/>
-      <c r="AC47" s="33"/>
+      <c r="A47" s="40">
+        <v>26003</v>
+      </c>
+      <c r="B47" s="41" t="s">
+        <v>350</v>
+      </c>
+      <c r="C47" s="42" t="s">
+        <v>348</v>
+      </c>
+      <c r="D47" s="40" t="s">
+        <v>349</v>
+      </c>
+      <c r="E47" s="40" t="str">
+        <f t="shared" ref="E47" si="24">D47&amp;"_DESC"</f>
+        <v>STR_TRAP_N_0003_DESC</v>
+      </c>
+      <c r="F47" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="G47" s="40">
+        <v>0</v>
+      </c>
+      <c r="H47" s="40">
+        <v>0</v>
+      </c>
+      <c r="I47" s="40">
+        <v>1</v>
+      </c>
+      <c r="J47" s="40">
+        <v>0</v>
+      </c>
+      <c r="K47" s="40">
+        <v>0</v>
+      </c>
+      <c r="L47" s="40">
+        <v>0</v>
+      </c>
+      <c r="M47" s="40">
+        <v>0</v>
+      </c>
+      <c r="N47" s="40"/>
+      <c r="O47" s="40"/>
+      <c r="P47" s="40"/>
+      <c r="Q47" s="40" t="s">
+        <v>351</v>
+      </c>
+      <c r="R47" s="40"/>
+      <c r="S47" s="40"/>
+      <c r="T47" s="40"/>
+      <c r="U47" s="40"/>
+      <c r="V47" s="40"/>
+      <c r="W47" s="40"/>
+      <c r="X47" s="40"/>
+      <c r="Y47" s="40"/>
+      <c r="Z47" s="40"/>
+      <c r="AA47" s="40"/>
+      <c r="AB47" s="40"/>
+      <c r="AC47" s="40"/>
     </row>
     <row r="48" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A48" s="33"/>
-      <c r="D48" s="33"/>
-      <c r="E48" s="33"/>
-      <c r="M48" s="33"/>
+      <c r="A48" s="33">
+        <v>27000</v>
+      </c>
+      <c r="B48" s="34" t="s">
+        <v>344</v>
+      </c>
+      <c r="C48" s="35" t="s">
+        <v>345</v>
+      </c>
+      <c r="D48" s="33" t="s">
+        <v>346</v>
+      </c>
+      <c r="E48" s="33" t="str">
+        <f t="shared" si="23"/>
+        <v>STR_DOOR_N_0001_DESC</v>
+      </c>
+      <c r="F48" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G48" s="33">
+        <v>0</v>
+      </c>
+      <c r="H48" s="33">
+        <v>0</v>
+      </c>
+      <c r="I48" s="33">
+        <v>1</v>
+      </c>
+      <c r="J48" s="33">
+        <v>0</v>
+      </c>
+      <c r="K48" s="33">
+        <v>0</v>
+      </c>
+      <c r="L48" s="33">
+        <v>0</v>
+      </c>
+      <c r="M48" s="33">
+        <v>0</v>
+      </c>
       <c r="N48" s="33"/>
       <c r="O48" s="33"/>
       <c r="P48" s="33"/>
+      <c r="Q48" s="36" t="s">
+        <v>347</v>
+      </c>
       <c r="T48" s="33"/>
       <c r="U48" s="33"/>
       <c r="V48" s="33"/>
@@ -8284,7 +8393,6 @@
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A49" s="33"/>
-      <c r="B49" s="34"/>
       <c r="D49" s="33"/>
       <c r="E49" s="33"/>
       <c r="M49" s="33"/>
@@ -8304,6 +8412,7 @@
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A50" s="33"/>
+      <c r="B50" s="34"/>
       <c r="D50" s="33"/>
       <c r="E50" s="33"/>
       <c r="M50" s="33"/>
@@ -8378,6 +8487,25 @@
       <c r="AB53" s="33"/>
       <c r="AC53" s="33"/>
     </row>
+    <row r="54" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A54" s="33"/>
+      <c r="D54" s="33"/>
+      <c r="E54" s="33"/>
+      <c r="M54" s="33"/>
+      <c r="N54" s="33"/>
+      <c r="O54" s="33"/>
+      <c r="P54" s="33"/>
+      <c r="T54" s="33"/>
+      <c r="U54" s="33"/>
+      <c r="V54" s="33"/>
+      <c r="W54" s="33"/>
+      <c r="X54" s="33"/>
+      <c r="Y54" s="33"/>
+      <c r="Z54" s="33"/>
+      <c r="AA54" s="33"/>
+      <c r="AB54" s="33"/>
+      <c r="AC54" s="33"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:U2"/>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8390,7 +8518,7 @@
           <x14:formula1>
             <xm:f>Type!$A$2:$A$20</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F46</xm:sqref>
+          <xm:sqref>F2:F48</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/30_table/01_테스트버전/Table_Data_Npc.xlsx
+++ b/30_table/01_테스트버전/Table_Data_Npc.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="390">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1192,81 +1192,206 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>데미지 상자 01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>damagn_box_n_0001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT</t>
+  </si>
+  <si>
+    <t>데미지 필드 01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trap_n_0001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_TRAP_N_0001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지 필드 02</t>
+  </si>
+  <si>
+    <t>trap_n_0002</t>
+  </si>
+  <si>
+    <t>STR_TRAP_N_0002</t>
+  </si>
+  <si>
+    <t>trap_03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trap_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>문 01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>door_n_0001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_DOOR_N_0001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>door_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trap_n_0003</t>
+  </si>
+  <si>
+    <t>STR_TRAP_N_0003</t>
+  </si>
+  <si>
+    <t>데미지 필드 03</t>
+  </si>
+  <si>
+    <t>empty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_n_0026</t>
+  </si>
+  <si>
+    <t>STR_NPC_N_0026</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_0011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20026_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>라미_50072</t>
+  </si>
+  <si>
+    <t>npc_n_0027</t>
+  </si>
+  <si>
+    <t>라미_50073</t>
+  </si>
+  <si>
+    <t>npc_n_0028</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20027_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20028_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>라미_50070</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20026_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20026_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20026_04</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20026_05</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20027_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20027_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20027_04</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20027_05</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20027_06</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20028_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20028_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20028_04</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20028_05</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20028_06</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20028_07</t>
+  </si>
+  <si>
+    <t>라미_50072_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_n_0029</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20029_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20029_02</t>
+  </si>
+  <si>
     <t>chest_01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>데미지 상자 01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>damagn_box_n_0001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OBJECT</t>
-  </si>
-  <si>
     <t>chest_02</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>데미지 필드 01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>trap_n_0001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STR_TRAP_N_0001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>데미지 필드 02</t>
-  </si>
-  <si>
-    <t>trap_n_0002</t>
-  </si>
-  <si>
-    <t>STR_TRAP_N_0002</t>
-  </si>
-  <si>
-    <t>trap_03</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>trap_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>문 01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>door_n_0001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STR_DOOR_N_0001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>door_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>trap_n_0003</t>
-  </si>
-  <si>
-    <t>STR_TRAP_N_0003</t>
-  </si>
-  <si>
-    <t>데미지 필드 03</t>
-  </si>
-  <si>
-    <t>empty</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>책_50079</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_n_0030</t>
+  </si>
+  <si>
+    <t>STR_NPC_N_0030</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_0012</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20030_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20030_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20030_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20030_04</t>
   </si>
 </sst>
 </file>
@@ -5264,7 +5389,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" style="36" bestFit="1" customWidth="1"/>
@@ -7026,341 +7151,366 @@
       <c r="AC26" s="33"/>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A27" s="40">
-        <v>22000</v>
-      </c>
-      <c r="B27" s="41" t="s">
-        <v>247</v>
-      </c>
-      <c r="C27" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="D27" s="40" t="str">
-        <f t="shared" ref="D27:D28" si="12">"STR_"&amp;UPPER(C27)</f>
-        <v>STR_MOB_N_0001</v>
-      </c>
-      <c r="E27" s="40" t="str">
-        <f t="shared" ref="E27:E41" si="13">D27&amp;"_DESC"</f>
-        <v>STR_MOB_N_0001_DESC</v>
-      </c>
-      <c r="F27" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G27" s="40">
-        <v>10</v>
-      </c>
-      <c r="H27" s="40">
+      <c r="A27" s="33">
+        <v>20025</v>
+      </c>
+      <c r="B27" s="34" t="s">
+        <v>360</v>
+      </c>
+      <c r="C27" s="35" t="s">
+        <v>350</v>
+      </c>
+      <c r="D27" s="33" t="s">
+        <v>351</v>
+      </c>
+      <c r="E27" s="33" t="str">
+        <f t="shared" ref="E27:E29" si="12">D27&amp;"_DESC"</f>
+        <v>STR_NPC_N_0026_DESC</v>
+      </c>
+      <c r="F27" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G27" s="33">
+        <v>0</v>
+      </c>
+      <c r="H27" s="33">
+        <v>0</v>
+      </c>
+      <c r="I27" s="33">
         <v>1</v>
       </c>
-      <c r="I27" s="40">
+      <c r="J27" s="33">
+        <v>0</v>
+      </c>
+      <c r="K27" s="33">
+        <v>0</v>
+      </c>
+      <c r="L27" s="33">
+        <v>0</v>
+      </c>
+      <c r="M27" s="33">
+        <v>0</v>
+      </c>
+      <c r="N27" s="33"/>
+      <c r="O27" s="33"/>
+      <c r="P27" s="33"/>
+      <c r="Q27" s="36" t="s">
+        <v>352</v>
+      </c>
+      <c r="T27" s="33" t="s">
+        <v>353</v>
+      </c>
+      <c r="U27" s="33" t="s">
+        <v>361</v>
+      </c>
+      <c r="V27" s="33" t="s">
+        <v>362</v>
+      </c>
+      <c r="W27" s="33" t="s">
+        <v>363</v>
+      </c>
+      <c r="X27" s="33" t="s">
+        <v>364</v>
+      </c>
+      <c r="Y27" s="33"/>
+      <c r="Z27" s="33"/>
+      <c r="AA27" s="33"/>
+      <c r="AB27" s="33"/>
+      <c r="AC27" s="33"/>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A28" s="33">
+        <v>20026</v>
+      </c>
+      <c r="B28" s="34" t="s">
+        <v>354</v>
+      </c>
+      <c r="C28" s="35" t="s">
+        <v>355</v>
+      </c>
+      <c r="D28" s="33" t="s">
+        <v>351</v>
+      </c>
+      <c r="E28" s="33" t="str">
+        <f>D28&amp;"_DESC"</f>
+        <v>STR_NPC_N_0026_DESC</v>
+      </c>
+      <c r="F28" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G28" s="33">
+        <v>0</v>
+      </c>
+      <c r="H28" s="33">
+        <v>0</v>
+      </c>
+      <c r="I28" s="33">
         <v>1</v>
       </c>
-      <c r="J27" s="40">
-        <v>0</v>
-      </c>
-      <c r="K27" s="40">
-        <v>1200</v>
-      </c>
-      <c r="L27" s="40">
-        <v>30</v>
-      </c>
-      <c r="M27" s="40">
-        <v>20</v>
-      </c>
-      <c r="N27" s="40" t="s">
-        <v>225</v>
-      </c>
-      <c r="O27" s="40"/>
-      <c r="P27" s="40"/>
-      <c r="Q27" s="40" t="s">
-        <v>226</v>
-      </c>
-      <c r="R27" s="40"/>
-      <c r="S27" s="40"/>
-      <c r="T27" s="40"/>
-      <c r="U27" s="40"/>
-      <c r="V27" s="40"/>
-      <c r="W27" s="40"/>
-      <c r="X27" s="40"/>
-      <c r="Y27" s="40"/>
-      <c r="Z27" s="40"/>
-      <c r="AA27" s="40"/>
-      <c r="AB27" s="40"/>
-      <c r="AC27" s="40"/>
-    </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A28" s="40">
-        <v>22001</v>
-      </c>
-      <c r="B28" s="40" t="s">
-        <v>137</v>
-      </c>
-      <c r="C28" s="41" t="s">
-        <v>138</v>
-      </c>
-      <c r="D28" s="40" t="str">
+      <c r="J28" s="33">
+        <v>0</v>
+      </c>
+      <c r="K28" s="33">
+        <v>0</v>
+      </c>
+      <c r="L28" s="33">
+        <v>0</v>
+      </c>
+      <c r="M28" s="33">
+        <v>0</v>
+      </c>
+      <c r="N28" s="33"/>
+      <c r="O28" s="33"/>
+      <c r="P28" s="33"/>
+      <c r="Q28" s="36" t="s">
+        <v>352</v>
+      </c>
+      <c r="T28" s="33" t="s">
+        <v>358</v>
+      </c>
+      <c r="U28" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="V28" s="33" t="s">
+        <v>366</v>
+      </c>
+      <c r="W28" s="33" t="s">
+        <v>367</v>
+      </c>
+      <c r="X28" s="33" t="s">
+        <v>368</v>
+      </c>
+      <c r="Y28" s="33" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z28" s="33"/>
+      <c r="AA28" s="33"/>
+      <c r="AB28" s="33"/>
+      <c r="AC28" s="33"/>
+    </row>
+    <row r="29" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A29" s="33">
+        <v>20027</v>
+      </c>
+      <c r="B29" s="34" t="s">
+        <v>356</v>
+      </c>
+      <c r="C29" s="35" t="s">
+        <v>357</v>
+      </c>
+      <c r="D29" s="33" t="s">
+        <v>351</v>
+      </c>
+      <c r="E29" s="33" t="str">
         <f t="shared" si="12"/>
-        <v>STR_MOB_N_0002</v>
-      </c>
-      <c r="E28" s="40" t="str">
-        <f t="shared" si="13"/>
-        <v>STR_MOB_N_0002_DESC</v>
-      </c>
-      <c r="F28" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G28" s="40">
+        <v>STR_NPC_N_0026_DESC</v>
+      </c>
+      <c r="F29" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G29" s="33">
+        <v>0</v>
+      </c>
+      <c r="H29" s="33">
+        <v>0</v>
+      </c>
+      <c r="I29" s="33">
         <v>1</v>
       </c>
-      <c r="H28" s="40">
+      <c r="J29" s="33">
+        <v>0</v>
+      </c>
+      <c r="K29" s="33">
+        <v>0</v>
+      </c>
+      <c r="L29" s="33">
+        <v>0</v>
+      </c>
+      <c r="M29" s="33">
+        <v>0</v>
+      </c>
+      <c r="N29" s="33"/>
+      <c r="O29" s="33"/>
+      <c r="P29" s="33"/>
+      <c r="Q29" s="36" t="s">
+        <v>352</v>
+      </c>
+      <c r="T29" s="33" t="s">
+        <v>359</v>
+      </c>
+      <c r="U29" s="33" t="s">
+        <v>370</v>
+      </c>
+      <c r="V29" s="33" t="s">
+        <v>371</v>
+      </c>
+      <c r="W29" s="33" t="s">
+        <v>372</v>
+      </c>
+      <c r="X29" s="33" t="s">
+        <v>373</v>
+      </c>
+      <c r="Y29" s="33" t="s">
+        <v>374</v>
+      </c>
+      <c r="Z29" s="33" t="s">
+        <v>375</v>
+      </c>
+      <c r="AA29" s="33"/>
+      <c r="AB29" s="33"/>
+      <c r="AC29" s="33"/>
+    </row>
+    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A30" s="33">
+        <v>20028</v>
+      </c>
+      <c r="B30" s="34" t="s">
+        <v>376</v>
+      </c>
+      <c r="C30" s="35" t="s">
+        <v>377</v>
+      </c>
+      <c r="D30" s="33" t="s">
+        <v>351</v>
+      </c>
+      <c r="E30" s="33" t="str">
+        <f>D30&amp;"_DESC"</f>
+        <v>STR_NPC_N_0026_DESC</v>
+      </c>
+      <c r="F30" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G30" s="33">
+        <v>0</v>
+      </c>
+      <c r="H30" s="33">
+        <v>0</v>
+      </c>
+      <c r="I30" s="33">
         <v>1</v>
       </c>
-      <c r="I28" s="40">
+      <c r="J30" s="33">
+        <v>0</v>
+      </c>
+      <c r="K30" s="33">
+        <v>0</v>
+      </c>
+      <c r="L30" s="33">
+        <v>0</v>
+      </c>
+      <c r="M30" s="33">
+        <v>0</v>
+      </c>
+      <c r="N30" s="33"/>
+      <c r="O30" s="33"/>
+      <c r="P30" s="33"/>
+      <c r="Q30" s="36" t="s">
+        <v>352</v>
+      </c>
+      <c r="T30" s="33" t="s">
+        <v>378</v>
+      </c>
+      <c r="U30" s="33" t="s">
+        <v>379</v>
+      </c>
+      <c r="V30" s="33"/>
+      <c r="W30" s="33"/>
+      <c r="X30" s="33"/>
+      <c r="Y30" s="33"/>
+      <c r="Z30" s="33"/>
+      <c r="AA30" s="33"/>
+      <c r="AB30" s="33"/>
+      <c r="AC30" s="33"/>
+    </row>
+    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A31" s="33">
+        <v>20029</v>
+      </c>
+      <c r="B31" s="34" t="s">
+        <v>382</v>
+      </c>
+      <c r="C31" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="D31" s="33" t="s">
+        <v>384</v>
+      </c>
+      <c r="E31" s="33" t="str">
+        <f>D31&amp;"_DESC"</f>
+        <v>STR_NPC_N_0030_DESC</v>
+      </c>
+      <c r="F31" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G31" s="33">
+        <v>0</v>
+      </c>
+      <c r="H31" s="33">
+        <v>0</v>
+      </c>
+      <c r="I31" s="33">
         <v>1</v>
       </c>
-      <c r="J28" s="40">
-        <v>0</v>
-      </c>
-      <c r="K28" s="40">
-        <v>2400</v>
-      </c>
-      <c r="L28" s="40">
-        <v>0</v>
-      </c>
-      <c r="M28" s="40">
-        <v>10</v>
-      </c>
-      <c r="N28" s="40"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="40"/>
-      <c r="Q28" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="R28" s="40"/>
-      <c r="S28" s="40"/>
-      <c r="T28" s="40"/>
-      <c r="U28" s="40"/>
-      <c r="V28" s="40"/>
-      <c r="W28" s="40"/>
-      <c r="X28" s="40"/>
-      <c r="Y28" s="40"/>
-      <c r="Z28" s="40"/>
-      <c r="AA28" s="40"/>
-      <c r="AB28" s="40"/>
-      <c r="AC28" s="40"/>
-    </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A29" s="40">
-        <v>22002</v>
-      </c>
-      <c r="B29" s="41" t="s">
-        <v>249</v>
-      </c>
-      <c r="C29" s="42" t="s">
-        <v>286</v>
-      </c>
-      <c r="D29" s="40" t="str">
-        <f t="shared" ref="D29" si="14">"STR_"&amp;UPPER(C29)</f>
-        <v>STR_MOB_N_0003</v>
-      </c>
-      <c r="E29" s="40" t="str">
-        <f t="shared" ref="E29" si="15">D29&amp;"_DESC"</f>
-        <v>STR_MOB_N_0003_DESC</v>
-      </c>
-      <c r="F29" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G29" s="40">
-        <v>60</v>
-      </c>
-      <c r="H29" s="40">
-        <v>1</v>
-      </c>
-      <c r="I29" s="40">
-        <v>1</v>
-      </c>
-      <c r="J29" s="40">
-        <v>0</v>
-      </c>
-      <c r="K29" s="40">
-        <v>1500</v>
-      </c>
-      <c r="L29" s="40">
-        <v>15</v>
-      </c>
-      <c r="M29" s="40">
-        <v>30</v>
-      </c>
-      <c r="N29" s="40" t="s">
-        <v>224</v>
-      </c>
-      <c r="O29" s="40"/>
-      <c r="P29" s="40"/>
-      <c r="Q29" s="40" t="s">
-        <v>102</v>
-      </c>
-      <c r="R29" s="40"/>
-      <c r="S29" s="40"/>
-      <c r="T29" s="40"/>
-      <c r="U29" s="40"/>
-      <c r="V29" s="40"/>
-      <c r="W29" s="40"/>
-      <c r="X29" s="40"/>
-      <c r="Y29" s="40"/>
-      <c r="Z29" s="40"/>
-      <c r="AA29" s="40"/>
-      <c r="AB29" s="40"/>
-      <c r="AC29" s="40"/>
-    </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A30" s="40">
-        <v>22003</v>
-      </c>
-      <c r="B30" s="41" t="s">
-        <v>243</v>
-      </c>
-      <c r="C30" s="42" t="s">
-        <v>234</v>
-      </c>
-      <c r="D30" s="40" t="str">
-        <f t="shared" ref="D30" si="16">"STR_"&amp;UPPER(C30)</f>
-        <v>STR_MOB_N_0004</v>
-      </c>
-      <c r="E30" s="40" t="str">
-        <f t="shared" ref="E30" si="17">D30&amp;"_DESC"</f>
-        <v>STR_MOB_N_0004_DESC</v>
-      </c>
-      <c r="F30" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G30" s="40">
-        <v>25</v>
-      </c>
-      <c r="H30" s="40">
-        <v>1</v>
-      </c>
-      <c r="I30" s="40">
-        <v>1</v>
-      </c>
-      <c r="J30" s="40">
-        <v>0</v>
-      </c>
-      <c r="K30" s="40">
-        <v>1500</v>
-      </c>
-      <c r="L30" s="40">
-        <v>20</v>
-      </c>
-      <c r="M30" s="40">
-        <v>50</v>
-      </c>
-      <c r="N30" s="40" t="s">
-        <v>224</v>
-      </c>
-      <c r="O30" s="40"/>
-      <c r="P30" s="40"/>
-      <c r="Q30" s="40" t="s">
-        <v>244</v>
-      </c>
-      <c r="R30" s="40"/>
-      <c r="S30" s="40"/>
-      <c r="T30" s="40"/>
-      <c r="U30" s="40"/>
-      <c r="V30" s="40"/>
-      <c r="W30" s="40"/>
-      <c r="X30" s="40"/>
-      <c r="Y30" s="40"/>
-      <c r="Z30" s="40"/>
-      <c r="AA30" s="40"/>
-      <c r="AB30" s="40"/>
-      <c r="AC30" s="40"/>
-    </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A31" s="40">
-        <v>22004</v>
-      </c>
-      <c r="B31" s="41" t="s">
-        <v>245</v>
-      </c>
-      <c r="C31" s="42" t="s">
-        <v>235</v>
-      </c>
-      <c r="D31" s="40" t="str">
-        <f t="shared" ref="D31:D39" si="18">"STR_"&amp;UPPER(C31)</f>
-        <v>STR_MOB_N_0005</v>
-      </c>
-      <c r="E31" s="40" t="str">
-        <f t="shared" ref="E31:E39" si="19">D31&amp;"_DESC"</f>
-        <v>STR_MOB_N_0005_DESC</v>
-      </c>
-      <c r="F31" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G31" s="40">
-        <v>1</v>
-      </c>
-      <c r="H31" s="40">
-        <v>1</v>
-      </c>
-      <c r="I31" s="40">
-        <v>1</v>
-      </c>
-      <c r="J31" s="40">
-        <v>0</v>
-      </c>
-      <c r="K31" s="40">
-        <v>1200</v>
-      </c>
-      <c r="L31" s="40">
-        <v>70</v>
-      </c>
-      <c r="M31" s="40">
-        <v>10</v>
-      </c>
-      <c r="N31" s="40" t="s">
-        <v>224</v>
-      </c>
-      <c r="O31" s="40"/>
-      <c r="P31" s="40"/>
-      <c r="Q31" s="40" t="s">
-        <v>246</v>
-      </c>
-      <c r="R31" s="40"/>
-      <c r="S31" s="40"/>
-      <c r="T31" s="40"/>
-      <c r="U31" s="40"/>
-      <c r="V31" s="40"/>
-      <c r="W31" s="40"/>
-      <c r="X31" s="40"/>
-      <c r="Y31" s="40"/>
-      <c r="Z31" s="40"/>
-      <c r="AA31" s="40"/>
-      <c r="AB31" s="40"/>
-      <c r="AC31" s="40"/>
+      <c r="J31" s="33">
+        <v>0</v>
+      </c>
+      <c r="K31" s="33">
+        <v>0</v>
+      </c>
+      <c r="L31" s="33">
+        <v>0</v>
+      </c>
+      <c r="M31" s="33">
+        <v>0</v>
+      </c>
+      <c r="N31" s="33"/>
+      <c r="O31" s="33"/>
+      <c r="P31" s="33"/>
+      <c r="Q31" s="36" t="s">
+        <v>385</v>
+      </c>
+      <c r="T31" s="33" t="s">
+        <v>386</v>
+      </c>
+      <c r="U31" s="33" t="s">
+        <v>387</v>
+      </c>
+      <c r="V31" s="33" t="s">
+        <v>388</v>
+      </c>
+      <c r="W31" s="33" t="s">
+        <v>389</v>
+      </c>
+      <c r="X31" s="33"/>
+      <c r="Y31" s="33"/>
+      <c r="Z31" s="33"/>
+      <c r="AA31" s="33"/>
+      <c r="AB31" s="33"/>
+      <c r="AC31" s="33"/>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A32" s="40">
-        <v>22005</v>
+        <v>22000</v>
       </c>
       <c r="B32" s="41" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C32" s="42" t="s">
-        <v>236</v>
+        <v>100</v>
       </c>
       <c r="D32" s="40" t="str">
-        <f t="shared" si="18"/>
-        <v>STR_MOB_N_0006</v>
+        <f t="shared" ref="D32:D33" si="13">"STR_"&amp;UPPER(C32)</f>
+        <v>STR_MOB_N_0001</v>
       </c>
       <c r="E32" s="40" t="str">
-        <f t="shared" si="19"/>
-        <v>STR_MOB_N_0006_DESC</v>
+        <f t="shared" ref="E32:E46" si="14">D32&amp;"_DESC"</f>
+        <v>STR_MOB_N_0001_DESC</v>
       </c>
       <c r="F32" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G32" s="40">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H32" s="40">
         <v>1</v>
@@ -7372,21 +7522,21 @@
         <v>0</v>
       </c>
       <c r="K32" s="40">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="L32" s="40">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="M32" s="40">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N32" s="40" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O32" s="40"/>
       <c r="P32" s="40"/>
       <c r="Q32" s="40" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="R32" s="40"/>
       <c r="S32" s="40"/>
@@ -7403,27 +7553,27 @@
     </row>
     <row r="33" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A33" s="40">
-        <v>22006</v>
-      </c>
-      <c r="B33" s="41" t="s">
-        <v>250</v>
-      </c>
-      <c r="C33" s="42" t="s">
-        <v>237</v>
+        <v>22001</v>
+      </c>
+      <c r="B33" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="C33" s="41" t="s">
+        <v>138</v>
       </c>
       <c r="D33" s="40" t="str">
-        <f t="shared" si="18"/>
-        <v>STR_MOB_N_0007</v>
+        <f t="shared" si="13"/>
+        <v>STR_MOB_N_0002</v>
       </c>
       <c r="E33" s="40" t="str">
-        <f t="shared" si="19"/>
-        <v>STR_MOB_N_0007_DESC</v>
+        <f t="shared" si="14"/>
+        <v>STR_MOB_N_0002_DESC</v>
       </c>
       <c r="F33" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G33" s="40">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H33" s="40">
         <v>1</v>
@@ -7435,21 +7585,19 @@
         <v>0</v>
       </c>
       <c r="K33" s="40">
-        <v>900</v>
+        <v>2400</v>
       </c>
       <c r="L33" s="40">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M33" s="40">
-        <v>35</v>
-      </c>
-      <c r="N33" s="40" t="s">
-        <v>224</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="N33" s="40"/>
       <c r="O33" s="40"/>
       <c r="P33" s="40"/>
       <c r="Q33" s="40" t="s">
-        <v>252</v>
+        <v>139</v>
       </c>
       <c r="R33" s="40"/>
       <c r="S33" s="40"/>
@@ -7466,27 +7614,27 @@
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A34" s="40">
-        <v>22007</v>
+        <v>22002</v>
       </c>
       <c r="B34" s="41" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="C34" s="42" t="s">
-        <v>238</v>
+        <v>286</v>
       </c>
       <c r="D34" s="40" t="str">
-        <f t="shared" si="18"/>
-        <v>STR_MOB_N_0008</v>
+        <f t="shared" ref="D34" si="15">"STR_"&amp;UPPER(C34)</f>
+        <v>STR_MOB_N_0003</v>
       </c>
       <c r="E34" s="40" t="str">
-        <f t="shared" si="19"/>
-        <v>STR_MOB_N_0008_DESC</v>
+        <f t="shared" ref="E34" si="16">D34&amp;"_DESC"</f>
+        <v>STR_MOB_N_0003_DESC</v>
       </c>
       <c r="F34" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G34" s="40">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H34" s="40">
         <v>1</v>
@@ -7498,13 +7646,13 @@
         <v>0</v>
       </c>
       <c r="K34" s="40">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="L34" s="40">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="M34" s="40">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N34" s="40" t="s">
         <v>224</v>
@@ -7512,7 +7660,7 @@
       <c r="O34" s="40"/>
       <c r="P34" s="40"/>
       <c r="Q34" s="40" t="s">
-        <v>253</v>
+        <v>102</v>
       </c>
       <c r="R34" s="40"/>
       <c r="S34" s="40"/>
@@ -7529,27 +7677,27 @@
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A35" s="40">
-        <v>22008</v>
+        <v>22003</v>
       </c>
       <c r="B35" s="41" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="C35" s="42" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="D35" s="40" t="str">
-        <f t="shared" si="18"/>
-        <v>STR_MOB_N_0009</v>
+        <f t="shared" ref="D35" si="17">"STR_"&amp;UPPER(C35)</f>
+        <v>STR_MOB_N_0004</v>
       </c>
       <c r="E35" s="40" t="str">
-        <f t="shared" si="19"/>
-        <v>STR_MOB_N_0009_DESC</v>
+        <f t="shared" ref="E35" si="18">D35&amp;"_DESC"</f>
+        <v>STR_MOB_N_0004_DESC</v>
       </c>
       <c r="F35" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G35" s="40">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H35" s="40">
         <v>1</v>
@@ -7561,13 +7709,13 @@
         <v>0</v>
       </c>
       <c r="K35" s="40">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="L35" s="40">
         <v>20</v>
       </c>
       <c r="M35" s="40">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="N35" s="40" t="s">
         <v>224</v>
@@ -7575,7 +7723,7 @@
       <c r="O35" s="40"/>
       <c r="P35" s="40"/>
       <c r="Q35" s="40" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="R35" s="40"/>
       <c r="S35" s="40"/>
@@ -7592,45 +7740,45 @@
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A36" s="40">
-        <v>22009</v>
+        <v>22004</v>
       </c>
       <c r="B36" s="41" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="C36" s="42" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D36" s="40" t="str">
-        <f t="shared" si="18"/>
-        <v>STR_MOB_N_0010</v>
+        <f t="shared" ref="D36:D44" si="19">"STR_"&amp;UPPER(C36)</f>
+        <v>STR_MOB_N_0005</v>
       </c>
       <c r="E36" s="40" t="str">
-        <f t="shared" si="19"/>
-        <v>STR_MOB_N_0010_DESC</v>
+        <f t="shared" ref="E36:E44" si="20">D36&amp;"_DESC"</f>
+        <v>STR_MOB_N_0005_DESC</v>
       </c>
       <c r="F36" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G36" s="40">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H36" s="40">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I36" s="40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J36" s="40">
         <v>0</v>
       </c>
       <c r="K36" s="40">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="L36" s="40">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M36" s="40">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="N36" s="40" t="s">
         <v>224</v>
@@ -7638,12 +7786,10 @@
       <c r="O36" s="40"/>
       <c r="P36" s="40"/>
       <c r="Q36" s="40" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="R36" s="40"/>
-      <c r="S36" s="40" t="s">
-        <v>285</v>
-      </c>
+      <c r="S36" s="40"/>
       <c r="T36" s="40"/>
       <c r="U36" s="40"/>
       <c r="V36" s="40"/>
@@ -7657,45 +7803,45 @@
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A37" s="40">
-        <v>22010</v>
+        <v>22005</v>
       </c>
       <c r="B37" s="41" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="C37" s="42" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D37" s="40" t="str">
-        <f t="shared" si="18"/>
-        <v>STR_MOB_N_0011</v>
+        <f t="shared" si="19"/>
+        <v>STR_MOB_N_0006</v>
       </c>
       <c r="E37" s="40" t="str">
-        <f t="shared" si="19"/>
-        <v>STR_MOB_N_0011_DESC</v>
+        <f t="shared" si="20"/>
+        <v>STR_MOB_N_0006_DESC</v>
       </c>
       <c r="F37" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G37" s="40">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H37" s="40">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="I37" s="40">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J37" s="40">
         <v>0</v>
       </c>
       <c r="K37" s="40">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="L37" s="40">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="M37" s="40">
-        <v>250</v>
+        <v>25</v>
       </c>
       <c r="N37" s="40" t="s">
         <v>224</v>
@@ -7703,12 +7849,10 @@
       <c r="O37" s="40"/>
       <c r="P37" s="40"/>
       <c r="Q37" s="40" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="R37" s="40"/>
-      <c r="S37" s="40" t="s">
-        <v>285</v>
-      </c>
+      <c r="S37" s="40"/>
       <c r="T37" s="40"/>
       <c r="U37" s="40"/>
       <c r="V37" s="40"/>
@@ -7722,45 +7866,45 @@
     </row>
     <row r="38" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A38" s="40">
-        <v>22011</v>
+        <v>22006</v>
       </c>
       <c r="B38" s="41" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="C38" s="42" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D38" s="40" t="str">
-        <f t="shared" si="18"/>
-        <v>STR_MOB_N_0012</v>
+        <f t="shared" si="19"/>
+        <v>STR_MOB_N_0007</v>
       </c>
       <c r="E38" s="40" t="str">
-        <f t="shared" si="19"/>
-        <v>STR_MOB_N_0012_DESC</v>
+        <f t="shared" si="20"/>
+        <v>STR_MOB_N_0007_DESC</v>
       </c>
       <c r="F38" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G38" s="40">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="H38" s="40">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="I38" s="40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J38" s="40">
         <v>0</v>
       </c>
       <c r="K38" s="40">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="L38" s="40">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="M38" s="40">
-        <v>200</v>
+        <v>35</v>
       </c>
       <c r="N38" s="40" t="s">
         <v>224</v>
@@ -7768,12 +7912,10 @@
       <c r="O38" s="40"/>
       <c r="P38" s="40"/>
       <c r="Q38" s="40" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="R38" s="40"/>
-      <c r="S38" s="40" t="s">
-        <v>285</v>
-      </c>
+      <c r="S38" s="40"/>
       <c r="T38" s="40"/>
       <c r="U38" s="40"/>
       <c r="V38" s="40"/>
@@ -7787,27 +7929,27 @@
     </row>
     <row r="39" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A39" s="40">
-        <v>22012</v>
+        <v>22007</v>
       </c>
       <c r="B39" s="41" t="s">
-        <v>317</v>
+        <v>258</v>
       </c>
       <c r="C39" s="42" t="s">
-        <v>318</v>
+        <v>238</v>
       </c>
       <c r="D39" s="40" t="str">
-        <f t="shared" si="18"/>
-        <v>STR_MOB_N_0013</v>
+        <f t="shared" si="19"/>
+        <v>STR_MOB_N_0008</v>
       </c>
       <c r="E39" s="40" t="str">
-        <f t="shared" si="19"/>
-        <v>STR_MOB_N_0013_DESC</v>
+        <f t="shared" si="20"/>
+        <v>STR_MOB_N_0008_DESC</v>
       </c>
       <c r="F39" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G39" s="40">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="H39" s="40">
         <v>1</v>
@@ -7819,13 +7961,13 @@
         <v>0</v>
       </c>
       <c r="K39" s="40">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="L39" s="40">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="M39" s="40">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="N39" s="40" t="s">
         <v>224</v>
@@ -7833,7 +7975,7 @@
       <c r="O39" s="40"/>
       <c r="P39" s="40"/>
       <c r="Q39" s="40" t="s">
-        <v>319</v>
+        <v>253</v>
       </c>
       <c r="R39" s="40"/>
       <c r="S39" s="40"/>
@@ -7850,45 +7992,45 @@
     </row>
     <row r="40" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A40" s="40">
-        <v>22013</v>
+        <v>22008</v>
       </c>
       <c r="B40" s="41" t="s">
-        <v>320</v>
+        <v>259</v>
       </c>
       <c r="C40" s="42" t="s">
-        <v>321</v>
+        <v>239</v>
       </c>
       <c r="D40" s="40" t="str">
-        <f t="shared" ref="D40" si="20">"STR_"&amp;UPPER(C40)</f>
-        <v>STR_MOB_N_0014</v>
+        <f t="shared" si="19"/>
+        <v>STR_MOB_N_0009</v>
       </c>
       <c r="E40" s="40" t="str">
-        <f t="shared" ref="E40" si="21">D40&amp;"_DESC"</f>
-        <v>STR_MOB_N_0014_DESC</v>
+        <f t="shared" si="20"/>
+        <v>STR_MOB_N_0009_DESC</v>
       </c>
       <c r="F40" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G40" s="40">
+        <v>1</v>
+      </c>
+      <c r="H40" s="40">
+        <v>1</v>
+      </c>
+      <c r="I40" s="40">
+        <v>1</v>
+      </c>
+      <c r="J40" s="40">
+        <v>0</v>
+      </c>
+      <c r="K40" s="40">
+        <v>1800</v>
+      </c>
+      <c r="L40" s="40">
         <v>20</v>
       </c>
-      <c r="H40" s="40">
-        <v>60</v>
-      </c>
-      <c r="I40" s="40">
-        <v>3</v>
-      </c>
-      <c r="J40" s="40">
-        <v>0</v>
-      </c>
-      <c r="K40" s="40">
-        <v>1500</v>
-      </c>
-      <c r="L40" s="40">
-        <v>15</v>
-      </c>
       <c r="M40" s="40">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="N40" s="40" t="s">
         <v>224</v>
@@ -7896,12 +8038,10 @@
       <c r="O40" s="40"/>
       <c r="P40" s="40"/>
       <c r="Q40" s="40" t="s">
-        <v>322</v>
+        <v>254</v>
       </c>
       <c r="R40" s="40"/>
-      <c r="S40" s="40" t="s">
-        <v>285</v>
-      </c>
+      <c r="S40" s="40"/>
       <c r="T40" s="40"/>
       <c r="U40" s="40"/>
       <c r="V40" s="40"/>
@@ -7914,210 +8054,226 @@
       <c r="AC40" s="40"/>
     </row>
     <row r="41" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A41" s="33">
-        <v>25000</v>
-      </c>
-      <c r="B41" s="34" t="s">
-        <v>323</v>
-      </c>
-      <c r="C41" s="35" t="s">
-        <v>204</v>
-      </c>
-      <c r="D41" s="33" t="s">
-        <v>223</v>
-      </c>
-      <c r="E41" s="33" t="str">
-        <f t="shared" si="13"/>
-        <v>STR_BOX_N_0001_DESC</v>
-      </c>
-      <c r="F41" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="G41" s="33">
-        <v>0</v>
-      </c>
-      <c r="H41" s="33">
-        <v>0</v>
-      </c>
-      <c r="I41" s="33">
-        <v>1</v>
-      </c>
-      <c r="J41" s="33">
-        <v>0</v>
-      </c>
-      <c r="K41" s="33">
-        <v>0</v>
-      </c>
-      <c r="L41" s="33">
-        <v>0</v>
-      </c>
-      <c r="M41" s="33">
-        <v>0</v>
-      </c>
-      <c r="N41" s="33" t="s">
-        <v>205</v>
-      </c>
-      <c r="O41" s="33"/>
-      <c r="P41" s="33"/>
-      <c r="Q41" s="36" t="s">
-        <v>330</v>
-      </c>
-      <c r="T41" s="33"/>
-      <c r="U41" s="33"/>
-      <c r="V41" s="33"/>
-      <c r="W41" s="33"/>
-      <c r="X41" s="33"/>
-      <c r="Y41" s="33"/>
-      <c r="Z41" s="33"/>
-      <c r="AA41" s="33"/>
-      <c r="AB41" s="33"/>
-      <c r="AC41" s="33"/>
+      <c r="A41" s="40">
+        <v>22009</v>
+      </c>
+      <c r="B41" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="C41" s="42" t="s">
+        <v>240</v>
+      </c>
+      <c r="D41" s="40" t="str">
+        <f t="shared" si="19"/>
+        <v>STR_MOB_N_0010</v>
+      </c>
+      <c r="E41" s="40" t="str">
+        <f t="shared" si="20"/>
+        <v>STR_MOB_N_0010_DESC</v>
+      </c>
+      <c r="F41" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G41" s="40">
+        <v>50</v>
+      </c>
+      <c r="H41" s="40">
+        <v>50</v>
+      </c>
+      <c r="I41" s="40">
+        <v>3</v>
+      </c>
+      <c r="J41" s="40">
+        <v>0</v>
+      </c>
+      <c r="K41" s="40">
+        <v>1500</v>
+      </c>
+      <c r="L41" s="40">
+        <v>0</v>
+      </c>
+      <c r="M41" s="40">
+        <v>70</v>
+      </c>
+      <c r="N41" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="O41" s="40"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="40" t="s">
+        <v>255</v>
+      </c>
+      <c r="R41" s="40"/>
+      <c r="S41" s="40" t="s">
+        <v>285</v>
+      </c>
+      <c r="T41" s="40"/>
+      <c r="U41" s="40"/>
+      <c r="V41" s="40"/>
+      <c r="W41" s="40"/>
+      <c r="X41" s="40"/>
+      <c r="Y41" s="40"/>
+      <c r="Z41" s="40"/>
+      <c r="AA41" s="40"/>
+      <c r="AB41" s="40"/>
+      <c r="AC41" s="40"/>
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A42" s="33">
-        <v>25001</v>
-      </c>
-      <c r="B42" s="34" t="s">
-        <v>324</v>
-      </c>
-      <c r="C42" s="35" t="s">
-        <v>325</v>
-      </c>
-      <c r="D42" s="33" t="s">
-        <v>326</v>
-      </c>
-      <c r="E42" s="33" t="str">
-        <f t="shared" ref="E42:E44" si="22">D42&amp;"_DESC"</f>
-        <v>STR_BOX_N_0002_DESC</v>
-      </c>
-      <c r="F42" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="G42" s="33">
-        <v>0</v>
-      </c>
-      <c r="H42" s="33">
-        <v>0</v>
-      </c>
-      <c r="I42" s="33">
-        <v>1</v>
-      </c>
-      <c r="J42" s="33">
-        <v>0</v>
-      </c>
-      <c r="K42" s="33">
-        <v>0</v>
-      </c>
-      <c r="L42" s="33">
-        <v>0</v>
-      </c>
-      <c r="M42" s="33">
-        <v>0</v>
-      </c>
-      <c r="N42" s="33" t="s">
-        <v>205</v>
-      </c>
-      <c r="O42" s="33"/>
-      <c r="P42" s="33"/>
-      <c r="Q42" s="36" t="s">
-        <v>330</v>
-      </c>
-      <c r="T42" s="33"/>
-      <c r="U42" s="33"/>
-      <c r="V42" s="33"/>
-      <c r="W42" s="33"/>
-      <c r="X42" s="33"/>
-      <c r="Y42" s="33"/>
-      <c r="Z42" s="33"/>
-      <c r="AA42" s="33"/>
-      <c r="AB42" s="33"/>
-      <c r="AC42" s="33"/>
+      <c r="A42" s="40">
+        <v>22010</v>
+      </c>
+      <c r="B42" s="41" t="s">
+        <v>260</v>
+      </c>
+      <c r="C42" s="42" t="s">
+        <v>241</v>
+      </c>
+      <c r="D42" s="40" t="str">
+        <f t="shared" si="19"/>
+        <v>STR_MOB_N_0011</v>
+      </c>
+      <c r="E42" s="40" t="str">
+        <f t="shared" si="20"/>
+        <v>STR_MOB_N_0011_DESC</v>
+      </c>
+      <c r="F42" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G42" s="40">
+        <v>100</v>
+      </c>
+      <c r="H42" s="40">
+        <v>70</v>
+      </c>
+      <c r="I42" s="40">
+        <v>5</v>
+      </c>
+      <c r="J42" s="40">
+        <v>0</v>
+      </c>
+      <c r="K42" s="40">
+        <v>1200</v>
+      </c>
+      <c r="L42" s="40">
+        <v>45</v>
+      </c>
+      <c r="M42" s="40">
+        <v>250</v>
+      </c>
+      <c r="N42" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="O42" s="40"/>
+      <c r="P42" s="40"/>
+      <c r="Q42" s="40" t="s">
+        <v>256</v>
+      </c>
+      <c r="R42" s="40"/>
+      <c r="S42" s="40" t="s">
+        <v>285</v>
+      </c>
+      <c r="T42" s="40"/>
+      <c r="U42" s="40"/>
+      <c r="V42" s="40"/>
+      <c r="W42" s="40"/>
+      <c r="X42" s="40"/>
+      <c r="Y42" s="40"/>
+      <c r="Z42" s="40"/>
+      <c r="AA42" s="40"/>
+      <c r="AB42" s="40"/>
+      <c r="AC42" s="40"/>
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A43" s="33">
-        <v>25002</v>
-      </c>
-      <c r="B43" s="34" t="s">
-        <v>327</v>
-      </c>
-      <c r="C43" s="35" t="s">
-        <v>328</v>
-      </c>
-      <c r="D43" s="33" t="s">
-        <v>329</v>
-      </c>
-      <c r="E43" s="33" t="str">
-        <f t="shared" si="22"/>
-        <v>STR_BOX_N_0003_DESC</v>
-      </c>
-      <c r="F43" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="G43" s="33">
-        <v>0</v>
-      </c>
-      <c r="H43" s="33">
-        <v>0</v>
-      </c>
-      <c r="I43" s="33">
-        <v>1</v>
-      </c>
-      <c r="J43" s="33">
-        <v>0</v>
-      </c>
-      <c r="K43" s="33">
-        <v>0</v>
-      </c>
-      <c r="L43" s="33">
-        <v>0</v>
-      </c>
-      <c r="M43" s="33">
-        <v>0</v>
-      </c>
-      <c r="N43" s="33" t="s">
-        <v>205</v>
-      </c>
-      <c r="O43" s="33"/>
-      <c r="P43" s="33"/>
-      <c r="Q43" s="36" t="s">
-        <v>331</v>
-      </c>
-      <c r="T43" s="33"/>
-      <c r="U43" s="33"/>
-      <c r="V43" s="33"/>
-      <c r="W43" s="33"/>
-      <c r="X43" s="33"/>
-      <c r="Y43" s="33"/>
-      <c r="Z43" s="33"/>
-      <c r="AA43" s="33"/>
-      <c r="AB43" s="33"/>
-      <c r="AC43" s="33"/>
+      <c r="A43" s="40">
+        <v>22011</v>
+      </c>
+      <c r="B43" s="41" t="s">
+        <v>261</v>
+      </c>
+      <c r="C43" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="D43" s="40" t="str">
+        <f t="shared" si="19"/>
+        <v>STR_MOB_N_0012</v>
+      </c>
+      <c r="E43" s="40" t="str">
+        <f t="shared" si="20"/>
+        <v>STR_MOB_N_0012_DESC</v>
+      </c>
+      <c r="F43" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G43" s="40">
+        <v>120</v>
+      </c>
+      <c r="H43" s="40">
+        <v>80</v>
+      </c>
+      <c r="I43" s="40">
+        <v>4</v>
+      </c>
+      <c r="J43" s="40">
+        <v>0</v>
+      </c>
+      <c r="K43" s="40">
+        <v>1000</v>
+      </c>
+      <c r="L43" s="40">
+        <v>60</v>
+      </c>
+      <c r="M43" s="40">
+        <v>200</v>
+      </c>
+      <c r="N43" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="O43" s="40"/>
+      <c r="P43" s="40"/>
+      <c r="Q43" s="40" t="s">
+        <v>257</v>
+      </c>
+      <c r="R43" s="40"/>
+      <c r="S43" s="40" t="s">
+        <v>285</v>
+      </c>
+      <c r="T43" s="40"/>
+      <c r="U43" s="40"/>
+      <c r="V43" s="40"/>
+      <c r="W43" s="40"/>
+      <c r="X43" s="40"/>
+      <c r="Y43" s="40"/>
+      <c r="Z43" s="40"/>
+      <c r="AA43" s="40"/>
+      <c r="AB43" s="40"/>
+      <c r="AC43" s="40"/>
     </row>
     <row r="44" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A44" s="40">
-        <v>26000</v>
+        <v>22012</v>
       </c>
       <c r="B44" s="41" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="C44" s="42" t="s">
-        <v>333</v>
-      </c>
-      <c r="D44" s="40" t="s">
-        <v>223</v>
+        <v>318</v>
+      </c>
+      <c r="D44" s="40" t="str">
+        <f t="shared" si="19"/>
+        <v>STR_MOB_N_0013</v>
       </c>
       <c r="E44" s="40" t="str">
-        <f t="shared" si="22"/>
-        <v>STR_BOX_N_0001_DESC</v>
+        <f t="shared" si="20"/>
+        <v>STR_MOB_N_0013_DESC</v>
       </c>
       <c r="F44" s="40" t="s">
-        <v>334</v>
+        <v>101</v>
       </c>
       <c r="G44" s="40">
-        <v>300</v>
+        <v>25</v>
       </c>
       <c r="H44" s="40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" s="40">
         <v>1</v>
@@ -8126,19 +8282,21 @@
         <v>0</v>
       </c>
       <c r="K44" s="40">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="L44" s="40">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M44" s="40">
-        <v>0</v>
-      </c>
-      <c r="N44" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="N44" s="40" t="s">
+        <v>224</v>
+      </c>
       <c r="O44" s="40"/>
       <c r="P44" s="40"/>
       <c r="Q44" s="40" t="s">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c r="R44" s="40"/>
       <c r="S44" s="40"/>
@@ -8155,53 +8313,58 @@
     </row>
     <row r="45" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A45" s="40">
-        <v>26001</v>
+        <v>22013</v>
       </c>
       <c r="B45" s="41" t="s">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="C45" s="42" t="s">
-        <v>337</v>
-      </c>
-      <c r="D45" s="40" t="s">
-        <v>338</v>
+        <v>321</v>
+      </c>
+      <c r="D45" s="40" t="str">
+        <f t="shared" ref="D45" si="21">"STR_"&amp;UPPER(C45)</f>
+        <v>STR_MOB_N_0014</v>
       </c>
       <c r="E45" s="40" t="str">
-        <f t="shared" ref="E45:E48" si="23">D45&amp;"_DESC"</f>
-        <v>STR_TRAP_N_0001_DESC</v>
+        <f t="shared" ref="E45" si="22">D45&amp;"_DESC"</f>
+        <v>STR_MOB_N_0014_DESC</v>
       </c>
       <c r="F45" s="40" t="s">
-        <v>334</v>
+        <v>101</v>
       </c>
       <c r="G45" s="40">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="H45" s="40">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I45" s="40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J45" s="40">
         <v>0</v>
       </c>
       <c r="K45" s="40">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="L45" s="40">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M45" s="40">
-        <v>0</v>
-      </c>
-      <c r="N45" s="40"/>
+        <v>70</v>
+      </c>
+      <c r="N45" s="40" t="s">
+        <v>224</v>
+      </c>
       <c r="O45" s="40"/>
       <c r="P45" s="40"/>
       <c r="Q45" s="40" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="R45" s="40"/>
-      <c r="S45" s="40"/>
+      <c r="S45" s="40" t="s">
+        <v>285</v>
+      </c>
       <c r="T45" s="40"/>
       <c r="U45" s="40"/>
       <c r="V45" s="40"/>
@@ -8214,141 +8377,141 @@
       <c r="AC45" s="40"/>
     </row>
     <row r="46" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A46" s="40">
-        <v>26002</v>
-      </c>
-      <c r="B46" s="41" t="s">
-        <v>339</v>
-      </c>
-      <c r="C46" s="42" t="s">
-        <v>340</v>
-      </c>
-      <c r="D46" s="40" t="s">
-        <v>341</v>
-      </c>
-      <c r="E46" s="40" t="str">
-        <f t="shared" si="23"/>
-        <v>STR_TRAP_N_0002_DESC</v>
-      </c>
-      <c r="F46" s="40" t="s">
-        <v>334</v>
-      </c>
-      <c r="G46" s="40">
-        <v>0</v>
-      </c>
-      <c r="H46" s="40">
-        <v>0</v>
-      </c>
-      <c r="I46" s="40">
+      <c r="A46" s="33">
+        <v>25000</v>
+      </c>
+      <c r="B46" s="34" t="s">
+        <v>323</v>
+      </c>
+      <c r="C46" s="35" t="s">
+        <v>204</v>
+      </c>
+      <c r="D46" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="E46" s="33" t="str">
+        <f t="shared" si="14"/>
+        <v>STR_BOX_N_0001_DESC</v>
+      </c>
+      <c r="F46" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G46" s="33">
+        <v>0</v>
+      </c>
+      <c r="H46" s="33">
+        <v>0</v>
+      </c>
+      <c r="I46" s="33">
         <v>1</v>
       </c>
-      <c r="J46" s="40">
-        <v>0</v>
-      </c>
-      <c r="K46" s="40">
-        <v>0</v>
-      </c>
-      <c r="L46" s="40">
-        <v>0</v>
-      </c>
-      <c r="M46" s="40">
-        <v>0</v>
-      </c>
-      <c r="N46" s="40"/>
-      <c r="O46" s="40"/>
-      <c r="P46" s="40"/>
-      <c r="Q46" s="40" t="s">
-        <v>343</v>
-      </c>
-      <c r="R46" s="40"/>
-      <c r="S46" s="40"/>
-      <c r="T46" s="40"/>
-      <c r="U46" s="40"/>
-      <c r="V46" s="40"/>
-      <c r="W46" s="40"/>
-      <c r="X46" s="40"/>
-      <c r="Y46" s="40"/>
-      <c r="Z46" s="40"/>
-      <c r="AA46" s="40"/>
-      <c r="AB46" s="40"/>
-      <c r="AC46" s="40"/>
+      <c r="J46" s="33">
+        <v>0</v>
+      </c>
+      <c r="K46" s="33">
+        <v>0</v>
+      </c>
+      <c r="L46" s="33">
+        <v>0</v>
+      </c>
+      <c r="M46" s="33">
+        <v>0</v>
+      </c>
+      <c r="N46" s="33" t="s">
+        <v>205</v>
+      </c>
+      <c r="O46" s="33"/>
+      <c r="P46" s="33"/>
+      <c r="Q46" s="36" t="s">
+        <v>330</v>
+      </c>
+      <c r="T46" s="33"/>
+      <c r="U46" s="33"/>
+      <c r="V46" s="33"/>
+      <c r="W46" s="33"/>
+      <c r="X46" s="33"/>
+      <c r="Y46" s="33"/>
+      <c r="Z46" s="33"/>
+      <c r="AA46" s="33"/>
+      <c r="AB46" s="33"/>
+      <c r="AC46" s="33"/>
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A47" s="40">
-        <v>26003</v>
-      </c>
-      <c r="B47" s="41" t="s">
-        <v>350</v>
-      </c>
-      <c r="C47" s="42" t="s">
-        <v>348</v>
-      </c>
-      <c r="D47" s="40" t="s">
-        <v>349</v>
-      </c>
-      <c r="E47" s="40" t="str">
-        <f t="shared" ref="E47" si="24">D47&amp;"_DESC"</f>
-        <v>STR_TRAP_N_0003_DESC</v>
-      </c>
-      <c r="F47" s="40" t="s">
-        <v>334</v>
-      </c>
-      <c r="G47" s="40">
-        <v>0</v>
-      </c>
-      <c r="H47" s="40">
-        <v>0</v>
-      </c>
-      <c r="I47" s="40">
+      <c r="A47" s="33">
+        <v>25001</v>
+      </c>
+      <c r="B47" s="34" t="s">
+        <v>324</v>
+      </c>
+      <c r="C47" s="35" t="s">
+        <v>325</v>
+      </c>
+      <c r="D47" s="33" t="s">
+        <v>326</v>
+      </c>
+      <c r="E47" s="33" t="str">
+        <f t="shared" ref="E47:E49" si="23">D47&amp;"_DESC"</f>
+        <v>STR_BOX_N_0002_DESC</v>
+      </c>
+      <c r="F47" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G47" s="33">
+        <v>0</v>
+      </c>
+      <c r="H47" s="33">
+        <v>0</v>
+      </c>
+      <c r="I47" s="33">
         <v>1</v>
       </c>
-      <c r="J47" s="40">
-        <v>0</v>
-      </c>
-      <c r="K47" s="40">
-        <v>0</v>
-      </c>
-      <c r="L47" s="40">
-        <v>0</v>
-      </c>
-      <c r="M47" s="40">
-        <v>0</v>
-      </c>
-      <c r="N47" s="40"/>
-      <c r="O47" s="40"/>
-      <c r="P47" s="40"/>
-      <c r="Q47" s="40" t="s">
-        <v>351</v>
-      </c>
-      <c r="R47" s="40"/>
-      <c r="S47" s="40"/>
-      <c r="T47" s="40"/>
-      <c r="U47" s="40"/>
-      <c r="V47" s="40"/>
-      <c r="W47" s="40"/>
-      <c r="X47" s="40"/>
-      <c r="Y47" s="40"/>
-      <c r="Z47" s="40"/>
-      <c r="AA47" s="40"/>
-      <c r="AB47" s="40"/>
-      <c r="AC47" s="40"/>
+      <c r="J47" s="33">
+        <v>0</v>
+      </c>
+      <c r="K47" s="33">
+        <v>0</v>
+      </c>
+      <c r="L47" s="33">
+        <v>0</v>
+      </c>
+      <c r="M47" s="33">
+        <v>0</v>
+      </c>
+      <c r="N47" s="33" t="s">
+        <v>205</v>
+      </c>
+      <c r="O47" s="33"/>
+      <c r="P47" s="33"/>
+      <c r="Q47" s="36" t="s">
+        <v>330</v>
+      </c>
+      <c r="T47" s="33"/>
+      <c r="U47" s="33"/>
+      <c r="V47" s="33"/>
+      <c r="W47" s="33"/>
+      <c r="X47" s="33"/>
+      <c r="Y47" s="33"/>
+      <c r="Z47" s="33"/>
+      <c r="AA47" s="33"/>
+      <c r="AB47" s="33"/>
+      <c r="AC47" s="33"/>
     </row>
     <row r="48" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A48" s="33">
-        <v>27000</v>
+        <v>25002</v>
       </c>
       <c r="B48" s="34" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="C48" s="35" t="s">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="D48" s="33" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="E48" s="33" t="str">
         <f t="shared" si="23"/>
-        <v>STR_DOOR_N_0001_DESC</v>
+        <v>STR_BOX_N_0003_DESC</v>
       </c>
       <c r="F48" s="33" t="s">
         <v>88</v>
@@ -8374,11 +8537,13 @@
       <c r="M48" s="33">
         <v>0</v>
       </c>
-      <c r="N48" s="33"/>
+      <c r="N48" s="33" t="s">
+        <v>205</v>
+      </c>
       <c r="O48" s="33"/>
       <c r="P48" s="33"/>
       <c r="Q48" s="36" t="s">
-        <v>347</v>
+        <v>381</v>
       </c>
       <c r="T48" s="33"/>
       <c r="U48" s="33"/>
@@ -8392,90 +8557,292 @@
       <c r="AC48" s="33"/>
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A49" s="33"/>
-      <c r="D49" s="33"/>
-      <c r="E49" s="33"/>
-      <c r="M49" s="33"/>
-      <c r="N49" s="33"/>
-      <c r="O49" s="33"/>
-      <c r="P49" s="33"/>
-      <c r="T49" s="33"/>
-      <c r="U49" s="33"/>
-      <c r="V49" s="33"/>
-      <c r="W49" s="33"/>
-      <c r="X49" s="33"/>
-      <c r="Y49" s="33"/>
-      <c r="Z49" s="33"/>
-      <c r="AA49" s="33"/>
-      <c r="AB49" s="33"/>
-      <c r="AC49" s="33"/>
+      <c r="A49" s="40">
+        <v>26000</v>
+      </c>
+      <c r="B49" s="41" t="s">
+        <v>331</v>
+      </c>
+      <c r="C49" s="42" t="s">
+        <v>332</v>
+      </c>
+      <c r="D49" s="40" t="s">
+        <v>223</v>
+      </c>
+      <c r="E49" s="40" t="str">
+        <f t="shared" si="23"/>
+        <v>STR_BOX_N_0001_DESC</v>
+      </c>
+      <c r="F49" s="40" t="s">
+        <v>333</v>
+      </c>
+      <c r="G49" s="40">
+        <v>300</v>
+      </c>
+      <c r="H49" s="40">
+        <v>0</v>
+      </c>
+      <c r="I49" s="40">
+        <v>1</v>
+      </c>
+      <c r="J49" s="40">
+        <v>0</v>
+      </c>
+      <c r="K49" s="40">
+        <v>0</v>
+      </c>
+      <c r="L49" s="40">
+        <v>0</v>
+      </c>
+      <c r="M49" s="40">
+        <v>0</v>
+      </c>
+      <c r="N49" s="40"/>
+      <c r="O49" s="40"/>
+      <c r="P49" s="40"/>
+      <c r="Q49" s="40" t="s">
+        <v>380</v>
+      </c>
+      <c r="R49" s="40"/>
+      <c r="S49" s="40"/>
+      <c r="T49" s="40"/>
+      <c r="U49" s="40"/>
+      <c r="V49" s="40"/>
+      <c r="W49" s="40"/>
+      <c r="X49" s="40"/>
+      <c r="Y49" s="40"/>
+      <c r="Z49" s="40"/>
+      <c r="AA49" s="40"/>
+      <c r="AB49" s="40"/>
+      <c r="AC49" s="40"/>
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A50" s="33"/>
-      <c r="B50" s="34"/>
-      <c r="D50" s="33"/>
-      <c r="E50" s="33"/>
-      <c r="M50" s="33"/>
-      <c r="N50" s="33"/>
-      <c r="O50" s="33"/>
-      <c r="P50" s="33"/>
-      <c r="T50" s="33"/>
-      <c r="U50" s="33"/>
-      <c r="V50" s="33"/>
-      <c r="W50" s="33"/>
-      <c r="X50" s="33"/>
-      <c r="Y50" s="33"/>
-      <c r="Z50" s="33"/>
-      <c r="AA50" s="33"/>
-      <c r="AB50" s="33"/>
-      <c r="AC50" s="33"/>
+      <c r="A50" s="40">
+        <v>26001</v>
+      </c>
+      <c r="B50" s="41" t="s">
+        <v>334</v>
+      </c>
+      <c r="C50" s="42" t="s">
+        <v>335</v>
+      </c>
+      <c r="D50" s="40" t="s">
+        <v>336</v>
+      </c>
+      <c r="E50" s="40" t="str">
+        <f t="shared" ref="E50:E53" si="24">D50&amp;"_DESC"</f>
+        <v>STR_TRAP_N_0001_DESC</v>
+      </c>
+      <c r="F50" s="40" t="s">
+        <v>333</v>
+      </c>
+      <c r="G50" s="40">
+        <v>300</v>
+      </c>
+      <c r="H50" s="40">
+        <v>0</v>
+      </c>
+      <c r="I50" s="40">
+        <v>1</v>
+      </c>
+      <c r="J50" s="40">
+        <v>0</v>
+      </c>
+      <c r="K50" s="40">
+        <v>2000</v>
+      </c>
+      <c r="L50" s="40">
+        <v>0</v>
+      </c>
+      <c r="M50" s="40">
+        <v>0</v>
+      </c>
+      <c r="N50" s="40"/>
+      <c r="O50" s="40"/>
+      <c r="P50" s="40"/>
+      <c r="Q50" s="40" t="s">
+        <v>340</v>
+      </c>
+      <c r="R50" s="40"/>
+      <c r="S50" s="40"/>
+      <c r="T50" s="40"/>
+      <c r="U50" s="40"/>
+      <c r="V50" s="40"/>
+      <c r="W50" s="40"/>
+      <c r="X50" s="40"/>
+      <c r="Y50" s="40"/>
+      <c r="Z50" s="40"/>
+      <c r="AA50" s="40"/>
+      <c r="AB50" s="40"/>
+      <c r="AC50" s="40"/>
     </row>
     <row r="51" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A51" s="33"/>
-      <c r="D51" s="33"/>
-      <c r="E51" s="33"/>
-      <c r="M51" s="33"/>
-      <c r="N51" s="33"/>
-      <c r="O51" s="33"/>
-      <c r="P51" s="33"/>
-      <c r="T51" s="33"/>
-      <c r="U51" s="33"/>
-      <c r="V51" s="33"/>
-      <c r="W51" s="33"/>
-      <c r="X51" s="33"/>
-      <c r="Y51" s="33"/>
-      <c r="Z51" s="33"/>
-      <c r="AA51" s="33"/>
-      <c r="AB51" s="33"/>
-      <c r="AC51" s="33"/>
+      <c r="A51" s="40">
+        <v>26002</v>
+      </c>
+      <c r="B51" s="41" t="s">
+        <v>337</v>
+      </c>
+      <c r="C51" s="42" t="s">
+        <v>338</v>
+      </c>
+      <c r="D51" s="40" t="s">
+        <v>339</v>
+      </c>
+      <c r="E51" s="40" t="str">
+        <f t="shared" si="24"/>
+        <v>STR_TRAP_N_0002_DESC</v>
+      </c>
+      <c r="F51" s="40" t="s">
+        <v>333</v>
+      </c>
+      <c r="G51" s="40">
+        <v>0</v>
+      </c>
+      <c r="H51" s="40">
+        <v>0</v>
+      </c>
+      <c r="I51" s="40">
+        <v>1</v>
+      </c>
+      <c r="J51" s="40">
+        <v>0</v>
+      </c>
+      <c r="K51" s="40">
+        <v>0</v>
+      </c>
+      <c r="L51" s="40">
+        <v>0</v>
+      </c>
+      <c r="M51" s="40">
+        <v>0</v>
+      </c>
+      <c r="N51" s="40"/>
+      <c r="O51" s="40"/>
+      <c r="P51" s="40"/>
+      <c r="Q51" s="40" t="s">
+        <v>341</v>
+      </c>
+      <c r="R51" s="40"/>
+      <c r="S51" s="40"/>
+      <c r="T51" s="40"/>
+      <c r="U51" s="40"/>
+      <c r="V51" s="40"/>
+      <c r="W51" s="40"/>
+      <c r="X51" s="40"/>
+      <c r="Y51" s="40"/>
+      <c r="Z51" s="40"/>
+      <c r="AA51" s="40"/>
+      <c r="AB51" s="40"/>
+      <c r="AC51" s="40"/>
     </row>
     <row r="52" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A52" s="33"/>
-      <c r="D52" s="33"/>
-      <c r="E52" s="33"/>
-      <c r="M52" s="33"/>
-      <c r="N52" s="33"/>
-      <c r="O52" s="33"/>
-      <c r="P52" s="33"/>
-      <c r="T52" s="33"/>
-      <c r="U52" s="33"/>
-      <c r="V52" s="33"/>
-      <c r="W52" s="33"/>
-      <c r="X52" s="33"/>
-      <c r="Y52" s="33"/>
-      <c r="Z52" s="33"/>
-      <c r="AA52" s="33"/>
-      <c r="AB52" s="33"/>
-      <c r="AC52" s="33"/>
+      <c r="A52" s="40">
+        <v>26003</v>
+      </c>
+      <c r="B52" s="41" t="s">
+        <v>348</v>
+      </c>
+      <c r="C52" s="42" t="s">
+        <v>346</v>
+      </c>
+      <c r="D52" s="40" t="s">
+        <v>347</v>
+      </c>
+      <c r="E52" s="40" t="str">
+        <f t="shared" ref="E52" si="25">D52&amp;"_DESC"</f>
+        <v>STR_TRAP_N_0003_DESC</v>
+      </c>
+      <c r="F52" s="40" t="s">
+        <v>333</v>
+      </c>
+      <c r="G52" s="40">
+        <v>0</v>
+      </c>
+      <c r="H52" s="40">
+        <v>0</v>
+      </c>
+      <c r="I52" s="40">
+        <v>1</v>
+      </c>
+      <c r="J52" s="40">
+        <v>0</v>
+      </c>
+      <c r="K52" s="40">
+        <v>0</v>
+      </c>
+      <c r="L52" s="40">
+        <v>0</v>
+      </c>
+      <c r="M52" s="40">
+        <v>0</v>
+      </c>
+      <c r="N52" s="40"/>
+      <c r="O52" s="40"/>
+      <c r="P52" s="40"/>
+      <c r="Q52" s="40" t="s">
+        <v>349</v>
+      </c>
+      <c r="R52" s="40"/>
+      <c r="S52" s="40"/>
+      <c r="T52" s="40"/>
+      <c r="U52" s="40"/>
+      <c r="V52" s="40"/>
+      <c r="W52" s="40"/>
+      <c r="X52" s="40"/>
+      <c r="Y52" s="40"/>
+      <c r="Z52" s="40"/>
+      <c r="AA52" s="40"/>
+      <c r="AB52" s="40"/>
+      <c r="AC52" s="40"/>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A53" s="33"/>
-      <c r="D53" s="33"/>
-      <c r="E53" s="33"/>
-      <c r="M53" s="33"/>
+      <c r="A53" s="33">
+        <v>27000</v>
+      </c>
+      <c r="B53" s="34" t="s">
+        <v>342</v>
+      </c>
+      <c r="C53" s="35" t="s">
+        <v>343</v>
+      </c>
+      <c r="D53" s="33" t="s">
+        <v>344</v>
+      </c>
+      <c r="E53" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v>STR_DOOR_N_0001_DESC</v>
+      </c>
+      <c r="F53" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G53" s="33">
+        <v>0</v>
+      </c>
+      <c r="H53" s="33">
+        <v>0</v>
+      </c>
+      <c r="I53" s="33">
+        <v>1</v>
+      </c>
+      <c r="J53" s="33">
+        <v>0</v>
+      </c>
+      <c r="K53" s="33">
+        <v>0</v>
+      </c>
+      <c r="L53" s="33">
+        <v>0</v>
+      </c>
+      <c r="M53" s="33">
+        <v>0</v>
+      </c>
       <c r="N53" s="33"/>
       <c r="O53" s="33"/>
       <c r="P53" s="33"/>
+      <c r="Q53" s="36" t="s">
+        <v>345</v>
+      </c>
       <c r="T53" s="33"/>
       <c r="U53" s="33"/>
       <c r="V53" s="33"/>
@@ -8506,6 +8873,102 @@
       <c r="AB54" s="33"/>
       <c r="AC54" s="33"/>
     </row>
+    <row r="55" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A55" s="33"/>
+      <c r="B55" s="34"/>
+      <c r="D55" s="33"/>
+      <c r="E55" s="33"/>
+      <c r="M55" s="33"/>
+      <c r="N55" s="33"/>
+      <c r="O55" s="33"/>
+      <c r="P55" s="33"/>
+      <c r="T55" s="33"/>
+      <c r="U55" s="33"/>
+      <c r="V55" s="33"/>
+      <c r="W55" s="33"/>
+      <c r="X55" s="33"/>
+      <c r="Y55" s="33"/>
+      <c r="Z55" s="33"/>
+      <c r="AA55" s="33"/>
+      <c r="AB55" s="33"/>
+      <c r="AC55" s="33"/>
+    </row>
+    <row r="56" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A56" s="33"/>
+      <c r="D56" s="33"/>
+      <c r="E56" s="33"/>
+      <c r="M56" s="33"/>
+      <c r="N56" s="33"/>
+      <c r="O56" s="33"/>
+      <c r="P56" s="33"/>
+      <c r="T56" s="33"/>
+      <c r="U56" s="33"/>
+      <c r="V56" s="33"/>
+      <c r="W56" s="33"/>
+      <c r="X56" s="33"/>
+      <c r="Y56" s="33"/>
+      <c r="Z56" s="33"/>
+      <c r="AA56" s="33"/>
+      <c r="AB56" s="33"/>
+      <c r="AC56" s="33"/>
+    </row>
+    <row r="57" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A57" s="33"/>
+      <c r="D57" s="33"/>
+      <c r="E57" s="33"/>
+      <c r="M57" s="33"/>
+      <c r="N57" s="33"/>
+      <c r="O57" s="33"/>
+      <c r="P57" s="33"/>
+      <c r="T57" s="33"/>
+      <c r="U57" s="33"/>
+      <c r="V57" s="33"/>
+      <c r="W57" s="33"/>
+      <c r="X57" s="33"/>
+      <c r="Y57" s="33"/>
+      <c r="Z57" s="33"/>
+      <c r="AA57" s="33"/>
+      <c r="AB57" s="33"/>
+      <c r="AC57" s="33"/>
+    </row>
+    <row r="58" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A58" s="33"/>
+      <c r="D58" s="33"/>
+      <c r="E58" s="33"/>
+      <c r="M58" s="33"/>
+      <c r="N58" s="33"/>
+      <c r="O58" s="33"/>
+      <c r="P58" s="33"/>
+      <c r="T58" s="33"/>
+      <c r="U58" s="33"/>
+      <c r="V58" s="33"/>
+      <c r="W58" s="33"/>
+      <c r="X58" s="33"/>
+      <c r="Y58" s="33"/>
+      <c r="Z58" s="33"/>
+      <c r="AA58" s="33"/>
+      <c r="AB58" s="33"/>
+      <c r="AC58" s="33"/>
+    </row>
+    <row r="59" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A59" s="33"/>
+      <c r="D59" s="33"/>
+      <c r="E59" s="33"/>
+      <c r="M59" s="33"/>
+      <c r="N59" s="33"/>
+      <c r="O59" s="33"/>
+      <c r="P59" s="33"/>
+      <c r="T59" s="33"/>
+      <c r="U59" s="33"/>
+      <c r="V59" s="33"/>
+      <c r="W59" s="33"/>
+      <c r="X59" s="33"/>
+      <c r="Y59" s="33"/>
+      <c r="Z59" s="33"/>
+      <c r="AA59" s="33"/>
+      <c r="AB59" s="33"/>
+      <c r="AC59" s="33"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:U2"/>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8518,7 +8981,7 @@
           <x14:formula1>
             <xm:f>Type!$A$2:$A$20</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F48</xm:sqref>
+          <xm:sqref>F2:F53</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/30_table/01_테스트버전/Table_Data_Npc.xlsx
+++ b/30_table/01_테스트버전/Table_Data_Npc.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="105" windowWidth="19215" windowHeight="12075" activeTab="2"/>
+    <workbookView xWindow="-15" yWindow="165" windowWidth="19215" windowHeight="12015" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="DOC History" sheetId="6" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="400">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1166,22 +1166,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>보물상자 01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>보물상자 02</t>
-  </si>
-  <si>
     <t>box_n_0002</t>
   </si>
   <si>
     <t>STR_BOX_N_0002</t>
   </si>
   <si>
-    <t>보물상자 03</t>
-  </si>
-  <si>
     <t>box_n_0003</t>
   </si>
   <si>
@@ -1363,10 +1353,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>chest_02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>책_50079</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1392,6 +1378,59 @@
   </si>
   <si>
     <t>STR_STORY_NPC_20030_04</t>
+  </si>
+  <si>
+    <t>C등급 보물상자 01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B등급 보물상자 02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_0039</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A등급 보물상자 03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_0040</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_0036</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_0037</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_0038</t>
+  </si>
+  <si>
+    <t>drop_0030</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_0031</t>
+  </si>
+  <si>
+    <t>drop_0034</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_0035</t>
+  </si>
+  <si>
+    <t>drop_0032</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_0033</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -7155,13 +7194,13 @@
         <v>20025</v>
       </c>
       <c r="B27" s="34" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E27" s="33" t="str">
         <f t="shared" ref="E27:E29" si="12">D27&amp;"_DESC"</f>
@@ -7195,22 +7234,22 @@
       <c r="O27" s="33"/>
       <c r="P27" s="33"/>
       <c r="Q27" s="36" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="T27" s="33" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="U27" s="33" t="s">
+        <v>358</v>
+      </c>
+      <c r="V27" s="33" t="s">
+        <v>359</v>
+      </c>
+      <c r="W27" s="33" t="s">
+        <v>360</v>
+      </c>
+      <c r="X27" s="33" t="s">
         <v>361</v>
-      </c>
-      <c r="V27" s="33" t="s">
-        <v>362</v>
-      </c>
-      <c r="W27" s="33" t="s">
-        <v>363</v>
-      </c>
-      <c r="X27" s="33" t="s">
-        <v>364</v>
       </c>
       <c r="Y27" s="33"/>
       <c r="Z27" s="33"/>
@@ -7223,13 +7262,13 @@
         <v>20026</v>
       </c>
       <c r="B28" s="34" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E28" s="33" t="str">
         <f>D28&amp;"_DESC"</f>
@@ -7263,25 +7302,25 @@
       <c r="O28" s="33"/>
       <c r="P28" s="33"/>
       <c r="Q28" s="36" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="T28" s="33" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="U28" s="33" t="s">
+        <v>362</v>
+      </c>
+      <c r="V28" s="33" t="s">
+        <v>363</v>
+      </c>
+      <c r="W28" s="33" t="s">
+        <v>364</v>
+      </c>
+      <c r="X28" s="33" t="s">
         <v>365</v>
       </c>
-      <c r="V28" s="33" t="s">
+      <c r="Y28" s="33" t="s">
         <v>366</v>
-      </c>
-      <c r="W28" s="33" t="s">
-        <v>367</v>
-      </c>
-      <c r="X28" s="33" t="s">
-        <v>368</v>
-      </c>
-      <c r="Y28" s="33" t="s">
-        <v>369</v>
       </c>
       <c r="Z28" s="33"/>
       <c r="AA28" s="33"/>
@@ -7293,13 +7332,13 @@
         <v>20027</v>
       </c>
       <c r="B29" s="34" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E29" s="33" t="str">
         <f t="shared" si="12"/>
@@ -7333,28 +7372,28 @@
       <c r="O29" s="33"/>
       <c r="P29" s="33"/>
       <c r="Q29" s="36" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="T29" s="33" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="U29" s="33" t="s">
+        <v>367</v>
+      </c>
+      <c r="V29" s="33" t="s">
+        <v>368</v>
+      </c>
+      <c r="W29" s="33" t="s">
+        <v>369</v>
+      </c>
+      <c r="X29" s="33" t="s">
         <v>370</v>
       </c>
-      <c r="V29" s="33" t="s">
+      <c r="Y29" s="33" t="s">
         <v>371</v>
       </c>
-      <c r="W29" s="33" t="s">
+      <c r="Z29" s="33" t="s">
         <v>372</v>
-      </c>
-      <c r="X29" s="33" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y29" s="33" t="s">
-        <v>374</v>
-      </c>
-      <c r="Z29" s="33" t="s">
-        <v>375</v>
       </c>
       <c r="AA29" s="33"/>
       <c r="AB29" s="33"/>
@@ -7365,13 +7404,13 @@
         <v>20028</v>
       </c>
       <c r="B30" s="34" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C30" s="35" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E30" s="33" t="str">
         <f>D30&amp;"_DESC"</f>
@@ -7405,13 +7444,13 @@
       <c r="O30" s="33"/>
       <c r="P30" s="33"/>
       <c r="Q30" s="36" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="T30" s="33" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="U30" s="33" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="V30" s="33"/>
       <c r="W30" s="33"/>
@@ -7427,13 +7466,13 @@
         <v>20029</v>
       </c>
       <c r="B31" s="34" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C31" s="35" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E31" s="33" t="str">
         <f>D31&amp;"_DESC"</f>
@@ -7467,19 +7506,19 @@
       <c r="O31" s="33"/>
       <c r="P31" s="33"/>
       <c r="Q31" s="36" t="s">
+        <v>381</v>
+      </c>
+      <c r="T31" s="33" t="s">
+        <v>382</v>
+      </c>
+      <c r="U31" s="33" t="s">
+        <v>383</v>
+      </c>
+      <c r="V31" s="33" t="s">
+        <v>384</v>
+      </c>
+      <c r="W31" s="33" t="s">
         <v>385</v>
-      </c>
-      <c r="T31" s="33" t="s">
-        <v>386</v>
-      </c>
-      <c r="U31" s="33" t="s">
-        <v>387</v>
-      </c>
-      <c r="V31" s="33" t="s">
-        <v>388</v>
-      </c>
-      <c r="W31" s="33" t="s">
-        <v>389</v>
       </c>
       <c r="X31" s="33"/>
       <c r="Y31" s="33"/>
@@ -7718,9 +7757,11 @@
         <v>50</v>
       </c>
       <c r="N35" s="40" t="s">
-        <v>224</v>
-      </c>
-      <c r="O35" s="40"/>
+        <v>394</v>
+      </c>
+      <c r="O35" s="40" t="s">
+        <v>395</v>
+      </c>
       <c r="P35" s="40"/>
       <c r="Q35" s="40" t="s">
         <v>244</v>
@@ -7844,7 +7885,7 @@
         <v>25</v>
       </c>
       <c r="N37" s="40" t="s">
-        <v>224</v>
+        <v>391</v>
       </c>
       <c r="O37" s="40"/>
       <c r="P37" s="40"/>
@@ -7907,9 +7948,11 @@
         <v>35</v>
       </c>
       <c r="N38" s="40" t="s">
-        <v>224</v>
-      </c>
-      <c r="O38" s="40"/>
+        <v>392</v>
+      </c>
+      <c r="O38" s="40" t="s">
+        <v>393</v>
+      </c>
       <c r="P38" s="40"/>
       <c r="Q38" s="40" t="s">
         <v>252</v>
@@ -8143,7 +8186,7 @@
         <v>100</v>
       </c>
       <c r="H42" s="40">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="I42" s="40">
         <v>5</v>
@@ -8220,15 +8263,17 @@
         <v>1000</v>
       </c>
       <c r="L43" s="40">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="M43" s="40">
         <v>200</v>
       </c>
       <c r="N43" s="40" t="s">
-        <v>224</v>
-      </c>
-      <c r="O43" s="40"/>
+        <v>396</v>
+      </c>
+      <c r="O43" s="40" t="s">
+        <v>397</v>
+      </c>
       <c r="P43" s="40"/>
       <c r="Q43" s="40" t="s">
         <v>257</v>
@@ -8291,7 +8336,7 @@
         <v>1</v>
       </c>
       <c r="N44" s="40" t="s">
-        <v>224</v>
+        <v>398</v>
       </c>
       <c r="O44" s="40"/>
       <c r="P44" s="40"/>
@@ -8354,7 +8399,7 @@
         <v>70</v>
       </c>
       <c r="N45" s="40" t="s">
-        <v>224</v>
+        <v>399</v>
       </c>
       <c r="O45" s="40"/>
       <c r="P45" s="40"/>
@@ -8381,7 +8426,7 @@
         <v>25000</v>
       </c>
       <c r="B46" s="34" t="s">
-        <v>323</v>
+        <v>386</v>
       </c>
       <c r="C46" s="35" t="s">
         <v>204</v>
@@ -8423,7 +8468,7 @@
       <c r="O46" s="33"/>
       <c r="P46" s="33"/>
       <c r="Q46" s="36" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="T46" s="33"/>
       <c r="U46" s="33"/>
@@ -8441,13 +8486,13 @@
         <v>25001</v>
       </c>
       <c r="B47" s="34" t="s">
+        <v>387</v>
+      </c>
+      <c r="C47" s="35" t="s">
+        <v>323</v>
+      </c>
+      <c r="D47" s="33" t="s">
         <v>324</v>
-      </c>
-      <c r="C47" s="35" t="s">
-        <v>325</v>
-      </c>
-      <c r="D47" s="33" t="s">
-        <v>326</v>
       </c>
       <c r="E47" s="33" t="str">
         <f t="shared" ref="E47:E49" si="23">D47&amp;"_DESC"</f>
@@ -8478,12 +8523,12 @@
         <v>0</v>
       </c>
       <c r="N47" s="33" t="s">
-        <v>205</v>
+        <v>388</v>
       </c>
       <c r="O47" s="33"/>
       <c r="P47" s="33"/>
       <c r="Q47" s="36" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="T47" s="33"/>
       <c r="U47" s="33"/>
@@ -8501,13 +8546,13 @@
         <v>25002</v>
       </c>
       <c r="B48" s="34" t="s">
-        <v>327</v>
+        <v>389</v>
       </c>
       <c r="C48" s="35" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D48" s="33" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E48" s="33" t="str">
         <f t="shared" si="23"/>
@@ -8538,12 +8583,12 @@
         <v>0</v>
       </c>
       <c r="N48" s="33" t="s">
-        <v>205</v>
+        <v>390</v>
       </c>
       <c r="O48" s="33"/>
       <c r="P48" s="33"/>
       <c r="Q48" s="36" t="s">
-        <v>381</v>
+        <v>327</v>
       </c>
       <c r="T48" s="33"/>
       <c r="U48" s="33"/>
@@ -8561,10 +8606,10 @@
         <v>26000</v>
       </c>
       <c r="B49" s="41" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C49" s="42" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D49" s="40" t="s">
         <v>223</v>
@@ -8574,7 +8619,7 @@
         <v>STR_BOX_N_0001_DESC</v>
       </c>
       <c r="F49" s="40" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G49" s="40">
         <v>300</v>
@@ -8601,7 +8646,7 @@
       <c r="O49" s="40"/>
       <c r="P49" s="40"/>
       <c r="Q49" s="40" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="R49" s="40"/>
       <c r="S49" s="40"/>
@@ -8621,20 +8666,20 @@
         <v>26001</v>
       </c>
       <c r="B50" s="41" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C50" s="42" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D50" s="40" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E50" s="40" t="str">
         <f t="shared" ref="E50:E53" si="24">D50&amp;"_DESC"</f>
         <v>STR_TRAP_N_0001_DESC</v>
       </c>
       <c r="F50" s="40" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G50" s="40">
         <v>300</v>
@@ -8661,7 +8706,7 @@
       <c r="O50" s="40"/>
       <c r="P50" s="40"/>
       <c r="Q50" s="40" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="R50" s="40"/>
       <c r="S50" s="40"/>
@@ -8681,20 +8726,20 @@
         <v>26002</v>
       </c>
       <c r="B51" s="41" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C51" s="42" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D51" s="40" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E51" s="40" t="str">
         <f t="shared" si="24"/>
         <v>STR_TRAP_N_0002_DESC</v>
       </c>
       <c r="F51" s="40" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G51" s="40">
         <v>0</v>
@@ -8721,7 +8766,7 @@
       <c r="O51" s="40"/>
       <c r="P51" s="40"/>
       <c r="Q51" s="40" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="R51" s="40"/>
       <c r="S51" s="40"/>
@@ -8741,20 +8786,20 @@
         <v>26003</v>
       </c>
       <c r="B52" s="41" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C52" s="42" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D52" s="40" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="E52" s="40" t="str">
         <f t="shared" ref="E52" si="25">D52&amp;"_DESC"</f>
         <v>STR_TRAP_N_0003_DESC</v>
       </c>
       <c r="F52" s="40" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G52" s="40">
         <v>0</v>
@@ -8781,7 +8826,7 @@
       <c r="O52" s="40"/>
       <c r="P52" s="40"/>
       <c r="Q52" s="40" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="R52" s="40"/>
       <c r="S52" s="40"/>
@@ -8801,13 +8846,13 @@
         <v>27000</v>
       </c>
       <c r="B53" s="34" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C53" s="35" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D53" s="33" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="E53" s="33" t="str">
         <f t="shared" si="24"/>
@@ -8841,7 +8886,7 @@
       <c r="O53" s="33"/>
       <c r="P53" s="33"/>
       <c r="Q53" s="36" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="T53" s="33"/>
       <c r="U53" s="33"/>

--- a/30_table/01_테스트버전/Table_Data_Npc.xlsx
+++ b/30_table/01_테스트버전/Table_Data_Npc.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="401">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1430,6 +1430,10 @@
   </si>
   <si>
     <t>drop_0033</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pf_fire_01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8183,7 +8187,7 @@
         <v>101</v>
       </c>
       <c r="G42" s="40">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H42" s="40">
         <v>150</v>
@@ -8213,7 +8217,7 @@
       </c>
       <c r="R42" s="40"/>
       <c r="S42" s="40" t="s">
-        <v>285</v>
+        <v>400</v>
       </c>
       <c r="T42" s="40"/>
       <c r="U42" s="40"/>
@@ -8254,7 +8258,7 @@
         <v>80</v>
       </c>
       <c r="I43" s="40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J43" s="40">
         <v>0</v>

--- a/30_table/01_테스트버전/Table_Data_Npc.xlsx
+++ b/30_table/01_테스트버전/Table_Data_Npc.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="538">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1435,6 +1435,479 @@
   <si>
     <t>pf_fire_01</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_n_0031</t>
+  </si>
+  <si>
+    <t>npc_n_0032</t>
+  </si>
+  <si>
+    <t>STR_NPC_N_0031</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_0014</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20031_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20031_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20032_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>민병대원 마르코_50080</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>민병대원 마르코_50081</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법사 작클레_50083_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법사 작클레_50083_2</t>
+  </si>
+  <si>
+    <t>npc_n_0033</t>
+  </si>
+  <si>
+    <t>npc_n_0034</t>
+  </si>
+  <si>
+    <t>STR_NPC_N_0033</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_0016</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20033_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여관주인 줄리아_50085</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_n_0035</t>
+  </si>
+  <si>
+    <t>STR_NPC_N_0035</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_0020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20035_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20034_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여관주인 줄리아_50086</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_n_0036</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20036_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법사 작클레_50088</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_n_0037</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20037_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파머의 상자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>box_n_0004</t>
+  </si>
+  <si>
+    <t>STR_BOX_N_0004</t>
+  </si>
+  <si>
+    <t>파머_50092</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_n_0038</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_NPC_N_0038</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_0021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20038_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호박</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>obj_n_0001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_OBJ_N_0001</t>
+  </si>
+  <si>
+    <t>STR_OBJ_N_0001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pumkin_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지 상자 02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pumkin_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파머_50094_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파머_50094_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_n_0039</t>
+  </si>
+  <si>
+    <t>npc_n_0040</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20039_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20040_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조합장 코퍼_50096</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조합장 코퍼_50097_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조합장 코퍼_50097_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_n_0041</t>
+  </si>
+  <si>
+    <t>npc_n_0042</t>
+  </si>
+  <si>
+    <t>npc_n_0043</t>
+  </si>
+  <si>
+    <t>STR_NPC_N_0041</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>귀신</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mob_n_0015</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mob_0015</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도둑_50100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_n_0044</t>
+  </si>
+  <si>
+    <t>STR_NPC_N_0044</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_0018</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20044_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20041_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20042_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20043_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조합장 코퍼_50101_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조합장 코퍼_50101_2</t>
+  </si>
+  <si>
+    <t>조합장 코퍼_50102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_n_0045</t>
+  </si>
+  <si>
+    <t>npc_n_0046</t>
+  </si>
+  <si>
+    <t>npc_n_0047</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20045_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20046_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20047_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_n_0048</t>
+  </si>
+  <si>
+    <t>STR_NPC_N_0048</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20048_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법사 작클레_50108</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_n_0049</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20049_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>민병대원 카를로스_50110</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_n_0050</t>
+  </si>
+  <si>
+    <t>STR_NPC_N_0050</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20050_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>민병대원 산체스_50104</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20031_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20031_04</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20032_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20032_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20033_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20033_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20033_04</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20033_05</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20034_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20034_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20035_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20035_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20035_04</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20036_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20036_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20037_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20037_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20037_04</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20037_05</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20038_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20038_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20038_04</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20038_05</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20041_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20042_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20042_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20042_04</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20043_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20044_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20045_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20046_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20047_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20048_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20048_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20048_04</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20040_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20041_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20041_04</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20041_05</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20047_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20047_04</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20048_05</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20049_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20049_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20049_04</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20049_05</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20049_06</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20050_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20050_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20050_04</t>
   </si>
 </sst>
 </file>
@@ -5432,7 +5905,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC83"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" style="36" bestFit="1" customWidth="1"/>
@@ -7532,915 +8005,929 @@
       <c r="AC31" s="33"/>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A32" s="40">
-        <v>22000</v>
-      </c>
-      <c r="B32" s="41" t="s">
-        <v>247</v>
-      </c>
-      <c r="C32" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="D32" s="40" t="str">
-        <f t="shared" ref="D32:D33" si="13">"STR_"&amp;UPPER(C32)</f>
-        <v>STR_MOB_N_0001</v>
-      </c>
-      <c r="E32" s="40" t="str">
-        <f t="shared" ref="E32:E46" si="14">D32&amp;"_DESC"</f>
-        <v>STR_MOB_N_0001_DESC</v>
-      </c>
-      <c r="F32" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G32" s="40">
-        <v>10</v>
-      </c>
-      <c r="H32" s="40">
+      <c r="A32" s="33">
+        <v>20030</v>
+      </c>
+      <c r="B32" s="34" t="s">
+        <v>408</v>
+      </c>
+      <c r="C32" s="35" t="s">
+        <v>401</v>
+      </c>
+      <c r="D32" s="33" t="s">
+        <v>403</v>
+      </c>
+      <c r="E32" s="33" t="str">
+        <f>D32&amp;"_DESC"</f>
+        <v>STR_NPC_N_0031_DESC</v>
+      </c>
+      <c r="F32" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" s="33">
+        <v>0</v>
+      </c>
+      <c r="H32" s="33">
+        <v>0</v>
+      </c>
+      <c r="I32" s="33">
         <v>1</v>
       </c>
-      <c r="I32" s="40">
+      <c r="J32" s="33">
+        <v>0</v>
+      </c>
+      <c r="K32" s="33">
+        <v>0</v>
+      </c>
+      <c r="L32" s="33">
+        <v>0</v>
+      </c>
+      <c r="M32" s="33">
+        <v>0</v>
+      </c>
+      <c r="N32" s="33"/>
+      <c r="O32" s="33"/>
+      <c r="P32" s="33"/>
+      <c r="Q32" s="36" t="s">
+        <v>404</v>
+      </c>
+      <c r="T32" s="33" t="s">
+        <v>405</v>
+      </c>
+      <c r="U32" s="33" t="s">
+        <v>406</v>
+      </c>
+      <c r="V32" s="33" t="s">
+        <v>488</v>
+      </c>
+      <c r="W32" s="33" t="s">
+        <v>489</v>
+      </c>
+      <c r="X32" s="33"/>
+      <c r="Y32" s="33"/>
+      <c r="Z32" s="33"/>
+      <c r="AA32" s="33"/>
+      <c r="AB32" s="33"/>
+      <c r="AC32" s="33"/>
+    </row>
+    <row r="33" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A33" s="33">
+        <v>20031</v>
+      </c>
+      <c r="B33" s="34" t="s">
+        <v>409</v>
+      </c>
+      <c r="C33" s="35" t="s">
+        <v>402</v>
+      </c>
+      <c r="D33" s="33" t="s">
+        <v>403</v>
+      </c>
+      <c r="E33" s="33" t="str">
+        <f>D33&amp;"_DESC"</f>
+        <v>STR_NPC_N_0031_DESC</v>
+      </c>
+      <c r="F33" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33" s="33">
+        <v>0</v>
+      </c>
+      <c r="H33" s="33">
+        <v>0</v>
+      </c>
+      <c r="I33" s="33">
         <v>1</v>
       </c>
-      <c r="J32" s="40">
-        <v>0</v>
-      </c>
-      <c r="K32" s="40">
-        <v>1200</v>
-      </c>
-      <c r="L32" s="40">
-        <v>30</v>
-      </c>
-      <c r="M32" s="40">
-        <v>20</v>
-      </c>
-      <c r="N32" s="40" t="s">
-        <v>225</v>
-      </c>
-      <c r="O32" s="40"/>
-      <c r="P32" s="40"/>
-      <c r="Q32" s="40" t="s">
-        <v>226</v>
-      </c>
-      <c r="R32" s="40"/>
-      <c r="S32" s="40"/>
-      <c r="T32" s="40"/>
-      <c r="U32" s="40"/>
-      <c r="V32" s="40"/>
-      <c r="W32" s="40"/>
-      <c r="X32" s="40"/>
-      <c r="Y32" s="40"/>
-      <c r="Z32" s="40"/>
-      <c r="AA32" s="40"/>
-      <c r="AB32" s="40"/>
-      <c r="AC32" s="40"/>
-    </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A33" s="40">
-        <v>22001</v>
-      </c>
-      <c r="B33" s="40" t="s">
-        <v>137</v>
-      </c>
-      <c r="C33" s="41" t="s">
-        <v>138</v>
-      </c>
-      <c r="D33" s="40" t="str">
-        <f t="shared" si="13"/>
-        <v>STR_MOB_N_0002</v>
-      </c>
-      <c r="E33" s="40" t="str">
-        <f t="shared" si="14"/>
-        <v>STR_MOB_N_0002_DESC</v>
-      </c>
-      <c r="F33" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G33" s="40">
+      <c r="J33" s="33">
+        <v>0</v>
+      </c>
+      <c r="K33" s="33">
+        <v>0</v>
+      </c>
+      <c r="L33" s="33">
+        <v>0</v>
+      </c>
+      <c r="M33" s="33">
+        <v>0</v>
+      </c>
+      <c r="N33" s="33"/>
+      <c r="O33" s="33"/>
+      <c r="P33" s="33"/>
+      <c r="Q33" s="36" t="s">
+        <v>404</v>
+      </c>
+      <c r="T33" s="33" t="s">
+        <v>407</v>
+      </c>
+      <c r="U33" s="33" t="s">
+        <v>490</v>
+      </c>
+      <c r="V33" s="33" t="s">
+        <v>491</v>
+      </c>
+      <c r="W33" s="33"/>
+      <c r="X33" s="33"/>
+      <c r="Y33" s="33"/>
+      <c r="Z33" s="33"/>
+      <c r="AA33" s="33"/>
+      <c r="AB33" s="33"/>
+      <c r="AC33" s="33"/>
+    </row>
+    <row r="34" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A34" s="33">
+        <v>20032</v>
+      </c>
+      <c r="B34" s="34" t="s">
+        <v>410</v>
+      </c>
+      <c r="C34" s="35" t="s">
+        <v>412</v>
+      </c>
+      <c r="D34" s="33" t="s">
+        <v>414</v>
+      </c>
+      <c r="E34" s="33" t="str">
+        <f>D34&amp;"_DESC"</f>
+        <v>STR_NPC_N_0033_DESC</v>
+      </c>
+      <c r="F34" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G34" s="33">
+        <v>0</v>
+      </c>
+      <c r="H34" s="33">
+        <v>0</v>
+      </c>
+      <c r="I34" s="33">
         <v>1</v>
       </c>
-      <c r="H33" s="40">
+      <c r="J34" s="33">
+        <v>0</v>
+      </c>
+      <c r="K34" s="33">
+        <v>0</v>
+      </c>
+      <c r="L34" s="33">
+        <v>0</v>
+      </c>
+      <c r="M34" s="33">
+        <v>0</v>
+      </c>
+      <c r="N34" s="33"/>
+      <c r="O34" s="33"/>
+      <c r="P34" s="33"/>
+      <c r="Q34" s="36" t="s">
+        <v>415</v>
+      </c>
+      <c r="T34" s="33" t="s">
+        <v>416</v>
+      </c>
+      <c r="U34" s="33" t="s">
+        <v>492</v>
+      </c>
+      <c r="V34" s="33" t="s">
+        <v>493</v>
+      </c>
+      <c r="W34" s="33" t="s">
+        <v>494</v>
+      </c>
+      <c r="X34" s="33" t="s">
+        <v>495</v>
+      </c>
+      <c r="Y34" s="33"/>
+      <c r="Z34" s="33"/>
+      <c r="AA34" s="33"/>
+      <c r="AB34" s="33"/>
+      <c r="AC34" s="33"/>
+    </row>
+    <row r="35" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A35" s="33">
+        <v>20033</v>
+      </c>
+      <c r="B35" s="34" t="s">
+        <v>411</v>
+      </c>
+      <c r="C35" s="35" t="s">
+        <v>413</v>
+      </c>
+      <c r="D35" s="33" t="s">
+        <v>414</v>
+      </c>
+      <c r="E35" s="33" t="str">
+        <f>D35&amp;"_DESC"</f>
+        <v>STR_NPC_N_0033_DESC</v>
+      </c>
+      <c r="F35" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G35" s="33">
+        <v>0</v>
+      </c>
+      <c r="H35" s="33">
+        <v>0</v>
+      </c>
+      <c r="I35" s="33">
         <v>1</v>
       </c>
-      <c r="I33" s="40">
+      <c r="J35" s="33">
+        <v>0</v>
+      </c>
+      <c r="K35" s="33">
+        <v>0</v>
+      </c>
+      <c r="L35" s="33">
+        <v>0</v>
+      </c>
+      <c r="M35" s="33">
+        <v>0</v>
+      </c>
+      <c r="N35" s="33"/>
+      <c r="O35" s="33"/>
+      <c r="P35" s="33"/>
+      <c r="Q35" s="36" t="s">
+        <v>415</v>
+      </c>
+      <c r="T35" s="33" t="s">
+        <v>422</v>
+      </c>
+      <c r="U35" s="33" t="s">
+        <v>496</v>
+      </c>
+      <c r="V35" s="33" t="s">
+        <v>497</v>
+      </c>
+      <c r="W35" s="33"/>
+      <c r="X35" s="33"/>
+      <c r="Y35" s="33"/>
+      <c r="Z35" s="33"/>
+      <c r="AA35" s="33"/>
+      <c r="AB35" s="33"/>
+      <c r="AC35" s="33"/>
+    </row>
+    <row r="36" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A36" s="33">
+        <v>20034</v>
+      </c>
+      <c r="B36" s="34" t="s">
+        <v>417</v>
+      </c>
+      <c r="C36" s="35" t="s">
+        <v>418</v>
+      </c>
+      <c r="D36" s="33" t="s">
+        <v>419</v>
+      </c>
+      <c r="E36" s="33" t="str">
+        <f>D36&amp;"_DESC"</f>
+        <v>STR_NPC_N_0035_DESC</v>
+      </c>
+      <c r="F36" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G36" s="33">
+        <v>0</v>
+      </c>
+      <c r="H36" s="33">
+        <v>0</v>
+      </c>
+      <c r="I36" s="33">
         <v>1</v>
       </c>
-      <c r="J33" s="40">
-        <v>0</v>
-      </c>
-      <c r="K33" s="40">
-        <v>2400</v>
-      </c>
-      <c r="L33" s="40">
-        <v>0</v>
-      </c>
-      <c r="M33" s="40">
-        <v>10</v>
-      </c>
-      <c r="N33" s="40"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="40"/>
-      <c r="Q33" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="R33" s="40"/>
-      <c r="S33" s="40"/>
-      <c r="T33" s="40"/>
-      <c r="U33" s="40"/>
-      <c r="V33" s="40"/>
-      <c r="W33" s="40"/>
-      <c r="X33" s="40"/>
-      <c r="Y33" s="40"/>
-      <c r="Z33" s="40"/>
-      <c r="AA33" s="40"/>
-      <c r="AB33" s="40"/>
-      <c r="AC33" s="40"/>
-    </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A34" s="40">
-        <v>22002</v>
-      </c>
-      <c r="B34" s="41" t="s">
-        <v>249</v>
-      </c>
-      <c r="C34" s="42" t="s">
-        <v>286</v>
-      </c>
-      <c r="D34" s="40" t="str">
-        <f t="shared" ref="D34" si="15">"STR_"&amp;UPPER(C34)</f>
-        <v>STR_MOB_N_0003</v>
-      </c>
-      <c r="E34" s="40" t="str">
-        <f t="shared" ref="E34" si="16">D34&amp;"_DESC"</f>
-        <v>STR_MOB_N_0003_DESC</v>
-      </c>
-      <c r="F34" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G34" s="40">
-        <v>60</v>
-      </c>
-      <c r="H34" s="40">
+      <c r="J36" s="33">
+        <v>0</v>
+      </c>
+      <c r="K36" s="33">
+        <v>0</v>
+      </c>
+      <c r="L36" s="33">
+        <v>0</v>
+      </c>
+      <c r="M36" s="33">
+        <v>0</v>
+      </c>
+      <c r="N36" s="33"/>
+      <c r="O36" s="33"/>
+      <c r="P36" s="33"/>
+      <c r="Q36" s="36" t="s">
+        <v>420</v>
+      </c>
+      <c r="T36" s="33" t="s">
+        <v>421</v>
+      </c>
+      <c r="U36" s="33" t="s">
+        <v>498</v>
+      </c>
+      <c r="V36" s="33" t="s">
+        <v>499</v>
+      </c>
+      <c r="W36" s="33" t="s">
+        <v>500</v>
+      </c>
+      <c r="X36" s="33"/>
+      <c r="Y36" s="33"/>
+      <c r="Z36" s="33"/>
+      <c r="AA36" s="33"/>
+      <c r="AB36" s="33"/>
+      <c r="AC36" s="33"/>
+    </row>
+    <row r="37" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A37" s="33">
+        <v>20035</v>
+      </c>
+      <c r="B37" s="34" t="s">
+        <v>423</v>
+      </c>
+      <c r="C37" s="35" t="s">
+        <v>424</v>
+      </c>
+      <c r="D37" s="33" t="s">
+        <v>419</v>
+      </c>
+      <c r="E37" s="33" t="str">
+        <f>D37&amp;"_DESC"</f>
+        <v>STR_NPC_N_0035_DESC</v>
+      </c>
+      <c r="F37" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G37" s="33">
+        <v>0</v>
+      </c>
+      <c r="H37" s="33">
+        <v>0</v>
+      </c>
+      <c r="I37" s="33">
         <v>1</v>
       </c>
-      <c r="I34" s="40">
+      <c r="J37" s="33">
+        <v>0</v>
+      </c>
+      <c r="K37" s="33">
+        <v>0</v>
+      </c>
+      <c r="L37" s="33">
+        <v>0</v>
+      </c>
+      <c r="M37" s="33">
+        <v>0</v>
+      </c>
+      <c r="N37" s="33"/>
+      <c r="O37" s="33"/>
+      <c r="P37" s="33"/>
+      <c r="Q37" s="36" t="s">
+        <v>420</v>
+      </c>
+      <c r="T37" s="33" t="s">
+        <v>425</v>
+      </c>
+      <c r="U37" s="33" t="s">
+        <v>501</v>
+      </c>
+      <c r="V37" s="33" t="s">
+        <v>502</v>
+      </c>
+      <c r="W37" s="33"/>
+      <c r="X37" s="33"/>
+      <c r="Y37" s="33"/>
+      <c r="Z37" s="33"/>
+      <c r="AA37" s="33"/>
+      <c r="AB37" s="33"/>
+      <c r="AC37" s="33"/>
+    </row>
+    <row r="38" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A38" s="33">
+        <v>20037</v>
+      </c>
+      <c r="B38" s="34" t="s">
+        <v>426</v>
+      </c>
+      <c r="C38" s="35" t="s">
+        <v>427</v>
+      </c>
+      <c r="D38" s="33" t="s">
+        <v>414</v>
+      </c>
+      <c r="E38" s="33" t="str">
+        <f>D38&amp;"_DESC"</f>
+        <v>STR_NPC_N_0033_DESC</v>
+      </c>
+      <c r="F38" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G38" s="33">
+        <v>0</v>
+      </c>
+      <c r="H38" s="33">
+        <v>0</v>
+      </c>
+      <c r="I38" s="33">
         <v>1</v>
       </c>
-      <c r="J34" s="40">
-        <v>0</v>
-      </c>
-      <c r="K34" s="40">
-        <v>1500</v>
-      </c>
-      <c r="L34" s="40">
-        <v>15</v>
-      </c>
-      <c r="M34" s="40">
-        <v>30</v>
-      </c>
-      <c r="N34" s="40" t="s">
-        <v>224</v>
-      </c>
-      <c r="O34" s="40"/>
-      <c r="P34" s="40"/>
-      <c r="Q34" s="40" t="s">
-        <v>102</v>
-      </c>
-      <c r="R34" s="40"/>
-      <c r="S34" s="40"/>
-      <c r="T34" s="40"/>
-      <c r="U34" s="40"/>
-      <c r="V34" s="40"/>
-      <c r="W34" s="40"/>
-      <c r="X34" s="40"/>
-      <c r="Y34" s="40"/>
-      <c r="Z34" s="40"/>
-      <c r="AA34" s="40"/>
-      <c r="AB34" s="40"/>
-      <c r="AC34" s="40"/>
-    </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A35" s="40">
-        <v>22003</v>
-      </c>
-      <c r="B35" s="41" t="s">
-        <v>243</v>
-      </c>
-      <c r="C35" s="42" t="s">
-        <v>234</v>
-      </c>
-      <c r="D35" s="40" t="str">
-        <f t="shared" ref="D35" si="17">"STR_"&amp;UPPER(C35)</f>
-        <v>STR_MOB_N_0004</v>
-      </c>
-      <c r="E35" s="40" t="str">
-        <f t="shared" ref="E35" si="18">D35&amp;"_DESC"</f>
-        <v>STR_MOB_N_0004_DESC</v>
-      </c>
-      <c r="F35" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G35" s="40">
-        <v>25</v>
-      </c>
-      <c r="H35" s="40">
+      <c r="J38" s="33">
+        <v>0</v>
+      </c>
+      <c r="K38" s="33">
+        <v>0</v>
+      </c>
+      <c r="L38" s="33">
+        <v>0</v>
+      </c>
+      <c r="M38" s="33">
+        <v>0</v>
+      </c>
+      <c r="N38" s="33"/>
+      <c r="O38" s="33"/>
+      <c r="P38" s="33"/>
+      <c r="Q38" s="36" t="s">
+        <v>415</v>
+      </c>
+      <c r="T38" s="33" t="s">
+        <v>428</v>
+      </c>
+      <c r="U38" s="33" t="s">
+        <v>503</v>
+      </c>
+      <c r="V38" s="33" t="s">
+        <v>504</v>
+      </c>
+      <c r="W38" s="33" t="s">
+        <v>505</v>
+      </c>
+      <c r="X38" s="33" t="s">
+        <v>506</v>
+      </c>
+      <c r="Y38" s="33"/>
+      <c r="Z38" s="33"/>
+      <c r="AA38" s="33"/>
+      <c r="AB38" s="33"/>
+      <c r="AC38" s="33"/>
+    </row>
+    <row r="39" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A39" s="33">
+        <v>20038</v>
+      </c>
+      <c r="B39" s="34" t="s">
+        <v>432</v>
+      </c>
+      <c r="C39" s="35" t="s">
+        <v>433</v>
+      </c>
+      <c r="D39" s="33" t="s">
+        <v>434</v>
+      </c>
+      <c r="E39" s="33" t="str">
+        <f>D39&amp;"_DESC"</f>
+        <v>STR_NPC_N_0038_DESC</v>
+      </c>
+      <c r="F39" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G39" s="33">
+        <v>0</v>
+      </c>
+      <c r="H39" s="33">
+        <v>0</v>
+      </c>
+      <c r="I39" s="33">
         <v>1</v>
       </c>
-      <c r="I35" s="40">
+      <c r="J39" s="33">
+        <v>0</v>
+      </c>
+      <c r="K39" s="33">
+        <v>0</v>
+      </c>
+      <c r="L39" s="33">
+        <v>0</v>
+      </c>
+      <c r="M39" s="33">
+        <v>0</v>
+      </c>
+      <c r="N39" s="33"/>
+      <c r="O39" s="33"/>
+      <c r="P39" s="33"/>
+      <c r="Q39" s="36" t="s">
+        <v>435</v>
+      </c>
+      <c r="T39" s="33" t="s">
+        <v>436</v>
+      </c>
+      <c r="U39" s="33" t="s">
+        <v>507</v>
+      </c>
+      <c r="V39" s="33" t="s">
+        <v>508</v>
+      </c>
+      <c r="W39" s="33" t="s">
+        <v>509</v>
+      </c>
+      <c r="X39" s="33" t="s">
+        <v>510</v>
+      </c>
+      <c r="Y39" s="33"/>
+      <c r="Z39" s="33"/>
+      <c r="AA39" s="33"/>
+      <c r="AB39" s="33"/>
+      <c r="AC39" s="33"/>
+    </row>
+    <row r="40" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A40" s="33">
+        <v>20039</v>
+      </c>
+      <c r="B40" s="34" t="s">
+        <v>444</v>
+      </c>
+      <c r="C40" s="35" t="s">
+        <v>446</v>
+      </c>
+      <c r="D40" s="33" t="s">
+        <v>434</v>
+      </c>
+      <c r="E40" s="33" t="str">
+        <f>D40&amp;"_DESC"</f>
+        <v>STR_NPC_N_0038_DESC</v>
+      </c>
+      <c r="F40" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G40" s="33">
+        <v>0</v>
+      </c>
+      <c r="H40" s="33">
+        <v>0</v>
+      </c>
+      <c r="I40" s="33">
         <v>1</v>
       </c>
-      <c r="J35" s="40">
-        <v>0</v>
-      </c>
-      <c r="K35" s="40">
-        <v>1500</v>
-      </c>
-      <c r="L35" s="40">
-        <v>20</v>
-      </c>
-      <c r="M35" s="40">
-        <v>50</v>
-      </c>
-      <c r="N35" s="40" t="s">
-        <v>394</v>
-      </c>
-      <c r="O35" s="40" t="s">
-        <v>395</v>
-      </c>
-      <c r="P35" s="40"/>
-      <c r="Q35" s="40" t="s">
-        <v>244</v>
-      </c>
-      <c r="R35" s="40"/>
-      <c r="S35" s="40"/>
-      <c r="T35" s="40"/>
-      <c r="U35" s="40"/>
-      <c r="V35" s="40"/>
-      <c r="W35" s="40"/>
-      <c r="X35" s="40"/>
-      <c r="Y35" s="40"/>
-      <c r="Z35" s="40"/>
-      <c r="AA35" s="40"/>
-      <c r="AB35" s="40"/>
-      <c r="AC35" s="40"/>
-    </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A36" s="40">
-        <v>22004</v>
-      </c>
-      <c r="B36" s="41" t="s">
-        <v>245</v>
-      </c>
-      <c r="C36" s="42" t="s">
-        <v>235</v>
-      </c>
-      <c r="D36" s="40" t="str">
-        <f t="shared" ref="D36:D44" si="19">"STR_"&amp;UPPER(C36)</f>
-        <v>STR_MOB_N_0005</v>
-      </c>
-      <c r="E36" s="40" t="str">
-        <f t="shared" ref="E36:E44" si="20">D36&amp;"_DESC"</f>
-        <v>STR_MOB_N_0005_DESC</v>
-      </c>
-      <c r="F36" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G36" s="40">
+      <c r="J40" s="33">
+        <v>0</v>
+      </c>
+      <c r="K40" s="33">
+        <v>0</v>
+      </c>
+      <c r="L40" s="33">
+        <v>0</v>
+      </c>
+      <c r="M40" s="33">
+        <v>0</v>
+      </c>
+      <c r="N40" s="33"/>
+      <c r="O40" s="33"/>
+      <c r="P40" s="33"/>
+      <c r="Q40" s="36" t="s">
+        <v>435</v>
+      </c>
+      <c r="T40" s="33" t="s">
+        <v>448</v>
+      </c>
+      <c r="U40" s="33"/>
+      <c r="V40" s="33"/>
+      <c r="W40" s="33"/>
+      <c r="X40" s="33"/>
+      <c r="Y40" s="33"/>
+      <c r="Z40" s="33"/>
+      <c r="AA40" s="33"/>
+      <c r="AB40" s="33"/>
+      <c r="AC40" s="33"/>
+    </row>
+    <row r="41" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A41" s="33">
+        <v>20040</v>
+      </c>
+      <c r="B41" s="34" t="s">
+        <v>445</v>
+      </c>
+      <c r="C41" s="35" t="s">
+        <v>447</v>
+      </c>
+      <c r="D41" s="33" t="s">
+        <v>434</v>
+      </c>
+      <c r="E41" s="33" t="str">
+        <f>D41&amp;"_DESC"</f>
+        <v>STR_NPC_N_0038_DESC</v>
+      </c>
+      <c r="F41" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G41" s="33">
+        <v>0</v>
+      </c>
+      <c r="H41" s="33">
+        <v>0</v>
+      </c>
+      <c r="I41" s="33">
         <v>1</v>
       </c>
-      <c r="H36" s="40">
+      <c r="J41" s="33">
+        <v>0</v>
+      </c>
+      <c r="K41" s="33">
+        <v>0</v>
+      </c>
+      <c r="L41" s="33">
+        <v>0</v>
+      </c>
+      <c r="M41" s="33">
+        <v>0</v>
+      </c>
+      <c r="N41" s="33"/>
+      <c r="O41" s="33"/>
+      <c r="P41" s="33"/>
+      <c r="Q41" s="36" t="s">
+        <v>435</v>
+      </c>
+      <c r="T41" s="33" t="s">
+        <v>449</v>
+      </c>
+      <c r="U41" s="33" t="s">
+        <v>523</v>
+      </c>
+      <c r="V41" s="33"/>
+      <c r="W41" s="33"/>
+      <c r="X41" s="33"/>
+      <c r="Y41" s="33"/>
+      <c r="Z41" s="33"/>
+      <c r="AA41" s="33"/>
+      <c r="AB41" s="33"/>
+      <c r="AC41" s="33"/>
+    </row>
+    <row r="42" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A42" s="33">
+        <v>20041</v>
+      </c>
+      <c r="B42" s="34" t="s">
+        <v>450</v>
+      </c>
+      <c r="C42" s="35" t="s">
+        <v>453</v>
+      </c>
+      <c r="D42" s="33" t="s">
+        <v>456</v>
+      </c>
+      <c r="E42" s="33" t="str">
+        <f>D42&amp;"_DESC"</f>
+        <v>STR_NPC_N_0041_DESC</v>
+      </c>
+      <c r="F42" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G42" s="33">
+        <v>0</v>
+      </c>
+      <c r="H42" s="33">
+        <v>0</v>
+      </c>
+      <c r="I42" s="33">
         <v>1</v>
       </c>
-      <c r="I36" s="40">
+      <c r="J42" s="33">
+        <v>0</v>
+      </c>
+      <c r="K42" s="33">
+        <v>0</v>
+      </c>
+      <c r="L42" s="33">
+        <v>0</v>
+      </c>
+      <c r="M42" s="33">
+        <v>0</v>
+      </c>
+      <c r="N42" s="33"/>
+      <c r="O42" s="33"/>
+      <c r="P42" s="33"/>
+      <c r="Q42" s="36" t="s">
+        <v>435</v>
+      </c>
+      <c r="T42" s="33" t="s">
+        <v>465</v>
+      </c>
+      <c r="U42" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="V42" s="33" t="s">
+        <v>524</v>
+      </c>
+      <c r="W42" s="33" t="s">
+        <v>525</v>
+      </c>
+      <c r="X42" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="Y42" s="33"/>
+      <c r="Z42" s="33"/>
+      <c r="AA42" s="33"/>
+      <c r="AB42" s="33"/>
+      <c r="AC42" s="33"/>
+    </row>
+    <row r="43" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A43" s="33">
+        <v>20042</v>
+      </c>
+      <c r="B43" s="34" t="s">
+        <v>451</v>
+      </c>
+      <c r="C43" s="35" t="s">
+        <v>454</v>
+      </c>
+      <c r="D43" s="33" t="s">
+        <v>456</v>
+      </c>
+      <c r="E43" s="33" t="str">
+        <f>D43&amp;"_DESC"</f>
+        <v>STR_NPC_N_0041_DESC</v>
+      </c>
+      <c r="F43" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G43" s="33">
+        <v>0</v>
+      </c>
+      <c r="H43" s="33">
+        <v>0</v>
+      </c>
+      <c r="I43" s="33">
         <v>1</v>
       </c>
-      <c r="J36" s="40">
-        <v>0</v>
-      </c>
-      <c r="K36" s="40">
-        <v>1200</v>
-      </c>
-      <c r="L36" s="40">
-        <v>70</v>
-      </c>
-      <c r="M36" s="40">
-        <v>10</v>
-      </c>
-      <c r="N36" s="40" t="s">
-        <v>224</v>
-      </c>
-      <c r="O36" s="40"/>
-      <c r="P36" s="40"/>
-      <c r="Q36" s="40" t="s">
-        <v>246</v>
-      </c>
-      <c r="R36" s="40"/>
-      <c r="S36" s="40"/>
-      <c r="T36" s="40"/>
-      <c r="U36" s="40"/>
-      <c r="V36" s="40"/>
-      <c r="W36" s="40"/>
-      <c r="X36" s="40"/>
-      <c r="Y36" s="40"/>
-      <c r="Z36" s="40"/>
-      <c r="AA36" s="40"/>
-      <c r="AB36" s="40"/>
-      <c r="AC36" s="40"/>
-    </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A37" s="40">
-        <v>22005</v>
-      </c>
-      <c r="B37" s="41" t="s">
-        <v>248</v>
-      </c>
-      <c r="C37" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="D37" s="40" t="str">
-        <f t="shared" si="19"/>
-        <v>STR_MOB_N_0006</v>
-      </c>
-      <c r="E37" s="40" t="str">
-        <f t="shared" si="20"/>
-        <v>STR_MOB_N_0006_DESC</v>
-      </c>
-      <c r="F37" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G37" s="40">
-        <v>40</v>
-      </c>
-      <c r="H37" s="40">
+      <c r="J43" s="33">
+        <v>0</v>
+      </c>
+      <c r="K43" s="33">
+        <v>0</v>
+      </c>
+      <c r="L43" s="33">
+        <v>0</v>
+      </c>
+      <c r="M43" s="33">
+        <v>0</v>
+      </c>
+      <c r="N43" s="33"/>
+      <c r="O43" s="33"/>
+      <c r="P43" s="33"/>
+      <c r="Q43" s="36" t="s">
+        <v>435</v>
+      </c>
+      <c r="T43" s="33" t="s">
+        <v>466</v>
+      </c>
+      <c r="U43" s="33" t="s">
+        <v>512</v>
+      </c>
+      <c r="V43" s="33" t="s">
+        <v>513</v>
+      </c>
+      <c r="W43" s="33" t="s">
+        <v>514</v>
+      </c>
+      <c r="X43" s="33"/>
+      <c r="Y43" s="33"/>
+      <c r="Z43" s="33"/>
+      <c r="AA43" s="33"/>
+      <c r="AB43" s="33"/>
+      <c r="AC43" s="33"/>
+    </row>
+    <row r="44" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A44" s="33">
+        <v>20043</v>
+      </c>
+      <c r="B44" s="34" t="s">
+        <v>452</v>
+      </c>
+      <c r="C44" s="35" t="s">
+        <v>455</v>
+      </c>
+      <c r="D44" s="33" t="s">
+        <v>456</v>
+      </c>
+      <c r="E44" s="33" t="str">
+        <f>D44&amp;"_DESC"</f>
+        <v>STR_NPC_N_0041_DESC</v>
+      </c>
+      <c r="F44" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G44" s="33">
+        <v>0</v>
+      </c>
+      <c r="H44" s="33">
+        <v>0</v>
+      </c>
+      <c r="I44" s="33">
         <v>1</v>
       </c>
-      <c r="I37" s="40">
+      <c r="J44" s="33">
+        <v>0</v>
+      </c>
+      <c r="K44" s="33">
+        <v>0</v>
+      </c>
+      <c r="L44" s="33">
+        <v>0</v>
+      </c>
+      <c r="M44" s="33">
+        <v>0</v>
+      </c>
+      <c r="N44" s="33"/>
+      <c r="O44" s="33"/>
+      <c r="P44" s="33"/>
+      <c r="Q44" s="36" t="s">
+        <v>435</v>
+      </c>
+      <c r="T44" s="33" t="s">
+        <v>467</v>
+      </c>
+      <c r="U44" s="33" t="s">
+        <v>515</v>
+      </c>
+      <c r="V44" s="33"/>
+      <c r="W44" s="33"/>
+      <c r="X44" s="33"/>
+      <c r="Y44" s="33"/>
+      <c r="Z44" s="33"/>
+      <c r="AA44" s="33"/>
+      <c r="AB44" s="33"/>
+      <c r="AC44" s="33"/>
+    </row>
+    <row r="45" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A45" s="33">
+        <v>20044</v>
+      </c>
+      <c r="B45" s="34" t="s">
+        <v>460</v>
+      </c>
+      <c r="C45" s="35" t="s">
+        <v>461</v>
+      </c>
+      <c r="D45" s="33" t="s">
+        <v>462</v>
+      </c>
+      <c r="E45" s="33" t="str">
+        <f>D45&amp;"_DESC"</f>
+        <v>STR_NPC_N_0044_DESC</v>
+      </c>
+      <c r="F45" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G45" s="33">
+        <v>0</v>
+      </c>
+      <c r="H45" s="33">
+        <v>0</v>
+      </c>
+      <c r="I45" s="33">
         <v>1</v>
       </c>
-      <c r="J37" s="40">
-        <v>0</v>
-      </c>
-      <c r="K37" s="40">
-        <v>1000</v>
-      </c>
-      <c r="L37" s="40">
-        <v>60</v>
-      </c>
-      <c r="M37" s="40">
-        <v>25</v>
-      </c>
-      <c r="N37" s="40" t="s">
-        <v>391</v>
-      </c>
-      <c r="O37" s="40"/>
-      <c r="P37" s="40"/>
-      <c r="Q37" s="40" t="s">
-        <v>251</v>
-      </c>
-      <c r="R37" s="40"/>
-      <c r="S37" s="40"/>
-      <c r="T37" s="40"/>
-      <c r="U37" s="40"/>
-      <c r="V37" s="40"/>
-      <c r="W37" s="40"/>
-      <c r="X37" s="40"/>
-      <c r="Y37" s="40"/>
-      <c r="Z37" s="40"/>
-      <c r="AA37" s="40"/>
-      <c r="AB37" s="40"/>
-      <c r="AC37" s="40"/>
-    </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A38" s="40">
-        <v>22006</v>
-      </c>
-      <c r="B38" s="41" t="s">
-        <v>250</v>
-      </c>
-      <c r="C38" s="42" t="s">
-        <v>237</v>
-      </c>
-      <c r="D38" s="40" t="str">
-        <f t="shared" si="19"/>
-        <v>STR_MOB_N_0007</v>
-      </c>
-      <c r="E38" s="40" t="str">
-        <f t="shared" si="20"/>
-        <v>STR_MOB_N_0007_DESC</v>
-      </c>
-      <c r="F38" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G38" s="40">
-        <v>60</v>
-      </c>
-      <c r="H38" s="40">
-        <v>1</v>
-      </c>
-      <c r="I38" s="40">
-        <v>1</v>
-      </c>
-      <c r="J38" s="40">
-        <v>0</v>
-      </c>
-      <c r="K38" s="40">
-        <v>900</v>
-      </c>
-      <c r="L38" s="40">
-        <v>70</v>
-      </c>
-      <c r="M38" s="40">
-        <v>35</v>
-      </c>
-      <c r="N38" s="40" t="s">
-        <v>392</v>
-      </c>
-      <c r="O38" s="40" t="s">
-        <v>393</v>
-      </c>
-      <c r="P38" s="40"/>
-      <c r="Q38" s="40" t="s">
-        <v>252</v>
-      </c>
-      <c r="R38" s="40"/>
-      <c r="S38" s="40"/>
-      <c r="T38" s="40"/>
-      <c r="U38" s="40"/>
-      <c r="V38" s="40"/>
-      <c r="W38" s="40"/>
-      <c r="X38" s="40"/>
-      <c r="Y38" s="40"/>
-      <c r="Z38" s="40"/>
-      <c r="AA38" s="40"/>
-      <c r="AB38" s="40"/>
-      <c r="AC38" s="40"/>
-    </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A39" s="40">
-        <v>22007</v>
-      </c>
-      <c r="B39" s="41" t="s">
-        <v>258</v>
-      </c>
-      <c r="C39" s="42" t="s">
-        <v>238</v>
-      </c>
-      <c r="D39" s="40" t="str">
-        <f t="shared" si="19"/>
-        <v>STR_MOB_N_0008</v>
-      </c>
-      <c r="E39" s="40" t="str">
-        <f t="shared" si="20"/>
-        <v>STR_MOB_N_0008_DESC</v>
-      </c>
-      <c r="F39" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G39" s="40">
-        <v>80</v>
-      </c>
-      <c r="H39" s="40">
-        <v>1</v>
-      </c>
-      <c r="I39" s="40">
-        <v>1</v>
-      </c>
-      <c r="J39" s="40">
-        <v>0</v>
-      </c>
-      <c r="K39" s="40">
-        <v>800</v>
-      </c>
-      <c r="L39" s="40">
-        <v>80</v>
-      </c>
-      <c r="M39" s="40">
-        <v>45</v>
-      </c>
-      <c r="N39" s="40" t="s">
-        <v>224</v>
-      </c>
-      <c r="O39" s="40"/>
-      <c r="P39" s="40"/>
-      <c r="Q39" s="40" t="s">
-        <v>253</v>
-      </c>
-      <c r="R39" s="40"/>
-      <c r="S39" s="40"/>
-      <c r="T39" s="40"/>
-      <c r="U39" s="40"/>
-      <c r="V39" s="40"/>
-      <c r="W39" s="40"/>
-      <c r="X39" s="40"/>
-      <c r="Y39" s="40"/>
-      <c r="Z39" s="40"/>
-      <c r="AA39" s="40"/>
-      <c r="AB39" s="40"/>
-      <c r="AC39" s="40"/>
-    </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A40" s="40">
-        <v>22008</v>
-      </c>
-      <c r="B40" s="41" t="s">
-        <v>259</v>
-      </c>
-      <c r="C40" s="42" t="s">
-        <v>239</v>
-      </c>
-      <c r="D40" s="40" t="str">
-        <f t="shared" si="19"/>
-        <v>STR_MOB_N_0009</v>
-      </c>
-      <c r="E40" s="40" t="str">
-        <f t="shared" si="20"/>
-        <v>STR_MOB_N_0009_DESC</v>
-      </c>
-      <c r="F40" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G40" s="40">
-        <v>1</v>
-      </c>
-      <c r="H40" s="40">
-        <v>1</v>
-      </c>
-      <c r="I40" s="40">
-        <v>1</v>
-      </c>
-      <c r="J40" s="40">
-        <v>0</v>
-      </c>
-      <c r="K40" s="40">
-        <v>1800</v>
-      </c>
-      <c r="L40" s="40">
-        <v>20</v>
-      </c>
-      <c r="M40" s="40">
-        <v>5</v>
-      </c>
-      <c r="N40" s="40" t="s">
-        <v>224</v>
-      </c>
-      <c r="O40" s="40"/>
-      <c r="P40" s="40"/>
-      <c r="Q40" s="40" t="s">
-        <v>254</v>
-      </c>
-      <c r="R40" s="40"/>
-      <c r="S40" s="40"/>
-      <c r="T40" s="40"/>
-      <c r="U40" s="40"/>
-      <c r="V40" s="40"/>
-      <c r="W40" s="40"/>
-      <c r="X40" s="40"/>
-      <c r="Y40" s="40"/>
-      <c r="Z40" s="40"/>
-      <c r="AA40" s="40"/>
-      <c r="AB40" s="40"/>
-      <c r="AC40" s="40"/>
-    </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A41" s="40">
-        <v>22009</v>
-      </c>
-      <c r="B41" s="41" t="s">
-        <v>262</v>
-      </c>
-      <c r="C41" s="42" t="s">
-        <v>240</v>
-      </c>
-      <c r="D41" s="40" t="str">
-        <f t="shared" si="19"/>
-        <v>STR_MOB_N_0010</v>
-      </c>
-      <c r="E41" s="40" t="str">
-        <f t="shared" si="20"/>
-        <v>STR_MOB_N_0010_DESC</v>
-      </c>
-      <c r="F41" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G41" s="40">
-        <v>50</v>
-      </c>
-      <c r="H41" s="40">
-        <v>50</v>
-      </c>
-      <c r="I41" s="40">
-        <v>3</v>
-      </c>
-      <c r="J41" s="40">
-        <v>0</v>
-      </c>
-      <c r="K41" s="40">
-        <v>1500</v>
-      </c>
-      <c r="L41" s="40">
-        <v>0</v>
-      </c>
-      <c r="M41" s="40">
-        <v>70</v>
-      </c>
-      <c r="N41" s="40" t="s">
-        <v>224</v>
-      </c>
-      <c r="O41" s="40"/>
-      <c r="P41" s="40"/>
-      <c r="Q41" s="40" t="s">
-        <v>255</v>
-      </c>
-      <c r="R41" s="40"/>
-      <c r="S41" s="40" t="s">
-        <v>285</v>
-      </c>
-      <c r="T41" s="40"/>
-      <c r="U41" s="40"/>
-      <c r="V41" s="40"/>
-      <c r="W41" s="40"/>
-      <c r="X41" s="40"/>
-      <c r="Y41" s="40"/>
-      <c r="Z41" s="40"/>
-      <c r="AA41" s="40"/>
-      <c r="AB41" s="40"/>
-      <c r="AC41" s="40"/>
-    </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A42" s="40">
-        <v>22010</v>
-      </c>
-      <c r="B42" s="41" t="s">
-        <v>260</v>
-      </c>
-      <c r="C42" s="42" t="s">
-        <v>241</v>
-      </c>
-      <c r="D42" s="40" t="str">
-        <f t="shared" si="19"/>
-        <v>STR_MOB_N_0011</v>
-      </c>
-      <c r="E42" s="40" t="str">
-        <f t="shared" si="20"/>
-        <v>STR_MOB_N_0011_DESC</v>
-      </c>
-      <c r="F42" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G42" s="40">
-        <v>90</v>
-      </c>
-      <c r="H42" s="40">
-        <v>150</v>
-      </c>
-      <c r="I42" s="40">
-        <v>5</v>
-      </c>
-      <c r="J42" s="40">
-        <v>0</v>
-      </c>
-      <c r="K42" s="40">
-        <v>1200</v>
-      </c>
-      <c r="L42" s="40">
-        <v>45</v>
-      </c>
-      <c r="M42" s="40">
-        <v>250</v>
-      </c>
-      <c r="N42" s="40" t="s">
-        <v>224</v>
-      </c>
-      <c r="O42" s="40"/>
-      <c r="P42" s="40"/>
-      <c r="Q42" s="40" t="s">
-        <v>256</v>
-      </c>
-      <c r="R42" s="40"/>
-      <c r="S42" s="40" t="s">
-        <v>400</v>
-      </c>
-      <c r="T42" s="40"/>
-      <c r="U42" s="40"/>
-      <c r="V42" s="40"/>
-      <c r="W42" s="40"/>
-      <c r="X42" s="40"/>
-      <c r="Y42" s="40"/>
-      <c r="Z42" s="40"/>
-      <c r="AA42" s="40"/>
-      <c r="AB42" s="40"/>
-      <c r="AC42" s="40"/>
-    </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A43" s="40">
-        <v>22011</v>
-      </c>
-      <c r="B43" s="41" t="s">
-        <v>261</v>
-      </c>
-      <c r="C43" s="42" t="s">
-        <v>242</v>
-      </c>
-      <c r="D43" s="40" t="str">
-        <f t="shared" si="19"/>
-        <v>STR_MOB_N_0012</v>
-      </c>
-      <c r="E43" s="40" t="str">
-        <f t="shared" si="20"/>
-        <v>STR_MOB_N_0012_DESC</v>
-      </c>
-      <c r="F43" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G43" s="40">
-        <v>120</v>
-      </c>
-      <c r="H43" s="40">
-        <v>80</v>
-      </c>
-      <c r="I43" s="40">
-        <v>1</v>
-      </c>
-      <c r="J43" s="40">
-        <v>0</v>
-      </c>
-      <c r="K43" s="40">
-        <v>1000</v>
-      </c>
-      <c r="L43" s="40">
-        <v>53</v>
-      </c>
-      <c r="M43" s="40">
-        <v>200</v>
-      </c>
-      <c r="N43" s="40" t="s">
-        <v>396</v>
-      </c>
-      <c r="O43" s="40" t="s">
-        <v>397</v>
-      </c>
-      <c r="P43" s="40"/>
-      <c r="Q43" s="40" t="s">
-        <v>257</v>
-      </c>
-      <c r="R43" s="40"/>
-      <c r="S43" s="40" t="s">
-        <v>285</v>
-      </c>
-      <c r="T43" s="40"/>
-      <c r="U43" s="40"/>
-      <c r="V43" s="40"/>
-      <c r="W43" s="40"/>
-      <c r="X43" s="40"/>
-      <c r="Y43" s="40"/>
-      <c r="Z43" s="40"/>
-      <c r="AA43" s="40"/>
-      <c r="AB43" s="40"/>
-      <c r="AC43" s="40"/>
-    </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A44" s="40">
-        <v>22012</v>
-      </c>
-      <c r="B44" s="41" t="s">
-        <v>317</v>
-      </c>
-      <c r="C44" s="42" t="s">
-        <v>318</v>
-      </c>
-      <c r="D44" s="40" t="str">
-        <f t="shared" si="19"/>
-        <v>STR_MOB_N_0013</v>
-      </c>
-      <c r="E44" s="40" t="str">
-        <f t="shared" si="20"/>
-        <v>STR_MOB_N_0013_DESC</v>
-      </c>
-      <c r="F44" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G44" s="40">
-        <v>25</v>
-      </c>
-      <c r="H44" s="40">
-        <v>1</v>
-      </c>
-      <c r="I44" s="40">
-        <v>1</v>
-      </c>
-      <c r="J44" s="40">
-        <v>0</v>
-      </c>
-      <c r="K44" s="40">
-        <v>1500</v>
-      </c>
-      <c r="L44" s="40">
-        <v>20</v>
-      </c>
-      <c r="M44" s="40">
-        <v>1</v>
-      </c>
-      <c r="N44" s="40" t="s">
-        <v>398</v>
-      </c>
-      <c r="O44" s="40"/>
-      <c r="P44" s="40"/>
-      <c r="Q44" s="40" t="s">
-        <v>319</v>
-      </c>
-      <c r="R44" s="40"/>
-      <c r="S44" s="40"/>
-      <c r="T44" s="40"/>
-      <c r="U44" s="40"/>
-      <c r="V44" s="40"/>
-      <c r="W44" s="40"/>
-      <c r="X44" s="40"/>
-      <c r="Y44" s="40"/>
-      <c r="Z44" s="40"/>
-      <c r="AA44" s="40"/>
-      <c r="AB44" s="40"/>
-      <c r="AC44" s="40"/>
-    </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A45" s="40">
-        <v>22013</v>
-      </c>
-      <c r="B45" s="41" t="s">
-        <v>320</v>
-      </c>
-      <c r="C45" s="42" t="s">
-        <v>321</v>
-      </c>
-      <c r="D45" s="40" t="str">
-        <f t="shared" ref="D45" si="21">"STR_"&amp;UPPER(C45)</f>
-        <v>STR_MOB_N_0014</v>
-      </c>
-      <c r="E45" s="40" t="str">
-        <f t="shared" ref="E45" si="22">D45&amp;"_DESC"</f>
-        <v>STR_MOB_N_0014_DESC</v>
-      </c>
-      <c r="F45" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G45" s="40">
-        <v>20</v>
-      </c>
-      <c r="H45" s="40">
-        <v>60</v>
-      </c>
-      <c r="I45" s="40">
-        <v>3</v>
-      </c>
-      <c r="J45" s="40">
-        <v>0</v>
-      </c>
-      <c r="K45" s="40">
-        <v>1500</v>
-      </c>
-      <c r="L45" s="40">
-        <v>15</v>
-      </c>
-      <c r="M45" s="40">
-        <v>70</v>
-      </c>
-      <c r="N45" s="40" t="s">
-        <v>399</v>
-      </c>
-      <c r="O45" s="40"/>
-      <c r="P45" s="40"/>
-      <c r="Q45" s="40" t="s">
-        <v>322</v>
-      </c>
-      <c r="R45" s="40"/>
-      <c r="S45" s="40" t="s">
-        <v>285</v>
-      </c>
-      <c r="T45" s="40"/>
-      <c r="U45" s="40"/>
-      <c r="V45" s="40"/>
-      <c r="W45" s="40"/>
-      <c r="X45" s="40"/>
-      <c r="Y45" s="40"/>
-      <c r="Z45" s="40"/>
-      <c r="AA45" s="40"/>
-      <c r="AB45" s="40"/>
-      <c r="AC45" s="40"/>
+      <c r="J45" s="33">
+        <v>0</v>
+      </c>
+      <c r="K45" s="33">
+        <v>0</v>
+      </c>
+      <c r="L45" s="33">
+        <v>0</v>
+      </c>
+      <c r="M45" s="33">
+        <v>0</v>
+      </c>
+      <c r="N45" s="33"/>
+      <c r="O45" s="33"/>
+      <c r="P45" s="33"/>
+      <c r="Q45" s="36" t="s">
+        <v>463</v>
+      </c>
+      <c r="T45" s="33" t="s">
+        <v>464</v>
+      </c>
+      <c r="U45" s="33" t="s">
+        <v>516</v>
+      </c>
+      <c r="V45" s="33"/>
+      <c r="W45" s="33"/>
+      <c r="X45" s="33"/>
+      <c r="Y45" s="33"/>
+      <c r="Z45" s="33"/>
+      <c r="AA45" s="33"/>
+      <c r="AB45" s="33"/>
+      <c r="AC45" s="33"/>
     </row>
     <row r="46" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A46" s="33">
-        <v>25000</v>
+        <v>20045</v>
       </c>
       <c r="B46" s="34" t="s">
-        <v>386</v>
+        <v>468</v>
       </c>
       <c r="C46" s="35" t="s">
-        <v>204</v>
+        <v>471</v>
       </c>
       <c r="D46" s="33" t="s">
-        <v>223</v>
+        <v>456</v>
       </c>
       <c r="E46" s="33" t="str">
-        <f t="shared" si="14"/>
-        <v>STR_BOX_N_0001_DESC</v>
+        <f>D46&amp;"_DESC"</f>
+        <v>STR_NPC_N_0041_DESC</v>
       </c>
       <c r="F46" s="33" t="s">
         <v>88</v>
@@ -8466,16 +8953,18 @@
       <c r="M46" s="33">
         <v>0</v>
       </c>
-      <c r="N46" s="33" t="s">
-        <v>205</v>
-      </c>
+      <c r="N46" s="33"/>
       <c r="O46" s="33"/>
       <c r="P46" s="33"/>
       <c r="Q46" s="36" t="s">
-        <v>327</v>
-      </c>
-      <c r="T46" s="33"/>
-      <c r="U46" s="33"/>
+        <v>435</v>
+      </c>
+      <c r="T46" s="33" t="s">
+        <v>474</v>
+      </c>
+      <c r="U46" s="33" t="s">
+        <v>517</v>
+      </c>
       <c r="V46" s="33"/>
       <c r="W46" s="33"/>
       <c r="X46" s="33"/>
@@ -8487,20 +8976,20 @@
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A47" s="33">
-        <v>25001</v>
+        <v>20046</v>
       </c>
       <c r="B47" s="34" t="s">
-        <v>387</v>
+        <v>469</v>
       </c>
       <c r="C47" s="35" t="s">
-        <v>323</v>
+        <v>472</v>
       </c>
       <c r="D47" s="33" t="s">
-        <v>324</v>
+        <v>456</v>
       </c>
       <c r="E47" s="33" t="str">
-        <f t="shared" ref="E47:E49" si="23">D47&amp;"_DESC"</f>
-        <v>STR_BOX_N_0002_DESC</v>
+        <f>D47&amp;"_DESC"</f>
+        <v>STR_NPC_N_0041_DESC</v>
       </c>
       <c r="F47" s="33" t="s">
         <v>88</v>
@@ -8526,16 +9015,18 @@
       <c r="M47" s="33">
         <v>0</v>
       </c>
-      <c r="N47" s="33" t="s">
-        <v>388</v>
-      </c>
+      <c r="N47" s="33"/>
       <c r="O47" s="33"/>
       <c r="P47" s="33"/>
       <c r="Q47" s="36" t="s">
-        <v>327</v>
-      </c>
-      <c r="T47" s="33"/>
-      <c r="U47" s="33"/>
+        <v>435</v>
+      </c>
+      <c r="T47" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="U47" s="33" t="s">
+        <v>518</v>
+      </c>
       <c r="V47" s="33"/>
       <c r="W47" s="33"/>
       <c r="X47" s="33"/>
@@ -8547,20 +9038,20 @@
     </row>
     <row r="48" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A48" s="33">
-        <v>25002</v>
+        <v>20047</v>
       </c>
       <c r="B48" s="34" t="s">
-        <v>389</v>
+        <v>470</v>
       </c>
       <c r="C48" s="35" t="s">
-        <v>325</v>
+        <v>473</v>
       </c>
       <c r="D48" s="33" t="s">
-        <v>326</v>
+        <v>456</v>
       </c>
       <c r="E48" s="33" t="str">
-        <f t="shared" si="23"/>
-        <v>STR_BOX_N_0003_DESC</v>
+        <f>D48&amp;"_DESC"</f>
+        <v>STR_NPC_N_0041_DESC</v>
       </c>
       <c r="F48" s="33" t="s">
         <v>88</v>
@@ -8586,18 +9077,24 @@
       <c r="M48" s="33">
         <v>0</v>
       </c>
-      <c r="N48" s="33" t="s">
-        <v>390</v>
-      </c>
+      <c r="N48" s="33"/>
       <c r="O48" s="33"/>
       <c r="P48" s="33"/>
       <c r="Q48" s="36" t="s">
-        <v>327</v>
-      </c>
-      <c r="T48" s="33"/>
-      <c r="U48" s="33"/>
-      <c r="V48" s="33"/>
-      <c r="W48" s="33"/>
+        <v>435</v>
+      </c>
+      <c r="T48" s="33" t="s">
+        <v>476</v>
+      </c>
+      <c r="U48" s="33" t="s">
+        <v>519</v>
+      </c>
+      <c r="V48" s="33" t="s">
+        <v>527</v>
+      </c>
+      <c r="W48" s="33" t="s">
+        <v>528</v>
+      </c>
       <c r="X48" s="33"/>
       <c r="Y48" s="33"/>
       <c r="Z48" s="33"/>
@@ -8606,210 +9103,235 @@
       <c r="AC48" s="33"/>
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A49" s="40">
-        <v>26000</v>
-      </c>
-      <c r="B49" s="41" t="s">
-        <v>328</v>
-      </c>
-      <c r="C49" s="42" t="s">
-        <v>329</v>
-      </c>
-      <c r="D49" s="40" t="s">
-        <v>223</v>
-      </c>
-      <c r="E49" s="40" t="str">
-        <f t="shared" si="23"/>
-        <v>STR_BOX_N_0001_DESC</v>
-      </c>
-      <c r="F49" s="40" t="s">
-        <v>330</v>
-      </c>
-      <c r="G49" s="40">
-        <v>300</v>
-      </c>
-      <c r="H49" s="40">
-        <v>0</v>
-      </c>
-      <c r="I49" s="40">
+      <c r="A49" s="33">
+        <v>20048</v>
+      </c>
+      <c r="B49" s="34" t="s">
+        <v>487</v>
+      </c>
+      <c r="C49" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D49" s="33" t="s">
+        <v>478</v>
+      </c>
+      <c r="E49" s="33" t="str">
+        <f>D49&amp;"_DESC"</f>
+        <v>STR_NPC_N_0048_DESC</v>
+      </c>
+      <c r="F49" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G49" s="33">
+        <v>0</v>
+      </c>
+      <c r="H49" s="33">
+        <v>0</v>
+      </c>
+      <c r="I49" s="33">
         <v>1</v>
       </c>
-      <c r="J49" s="40">
-        <v>0</v>
-      </c>
-      <c r="K49" s="40">
-        <v>0</v>
-      </c>
-      <c r="L49" s="40">
-        <v>0</v>
-      </c>
-      <c r="M49" s="40">
-        <v>0</v>
-      </c>
-      <c r="N49" s="40"/>
-      <c r="O49" s="40"/>
-      <c r="P49" s="40"/>
-      <c r="Q49" s="40" t="s">
-        <v>377</v>
-      </c>
-      <c r="R49" s="40"/>
-      <c r="S49" s="40"/>
-      <c r="T49" s="40"/>
-      <c r="U49" s="40"/>
-      <c r="V49" s="40"/>
-      <c r="W49" s="40"/>
-      <c r="X49" s="40"/>
-      <c r="Y49" s="40"/>
-      <c r="Z49" s="40"/>
-      <c r="AA49" s="40"/>
-      <c r="AB49" s="40"/>
-      <c r="AC49" s="40"/>
+      <c r="J49" s="33">
+        <v>0</v>
+      </c>
+      <c r="K49" s="33">
+        <v>0</v>
+      </c>
+      <c r="L49" s="33">
+        <v>0</v>
+      </c>
+      <c r="M49" s="33">
+        <v>0</v>
+      </c>
+      <c r="N49" s="33"/>
+      <c r="O49" s="33"/>
+      <c r="P49" s="33"/>
+      <c r="Q49" s="36" t="s">
+        <v>404</v>
+      </c>
+      <c r="T49" s="33" t="s">
+        <v>479</v>
+      </c>
+      <c r="U49" s="33" t="s">
+        <v>520</v>
+      </c>
+      <c r="V49" s="33" t="s">
+        <v>521</v>
+      </c>
+      <c r="W49" s="33" t="s">
+        <v>522</v>
+      </c>
+      <c r="X49" s="33" t="s">
+        <v>529</v>
+      </c>
+      <c r="Y49" s="33"/>
+      <c r="Z49" s="33"/>
+      <c r="AA49" s="33"/>
+      <c r="AB49" s="33"/>
+      <c r="AC49" s="33"/>
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A50" s="40">
-        <v>26001</v>
-      </c>
-      <c r="B50" s="41" t="s">
-        <v>331</v>
-      </c>
-      <c r="C50" s="42" t="s">
-        <v>332</v>
-      </c>
-      <c r="D50" s="40" t="s">
-        <v>333</v>
-      </c>
-      <c r="E50" s="40" t="str">
-        <f t="shared" ref="E50:E53" si="24">D50&amp;"_DESC"</f>
-        <v>STR_TRAP_N_0001_DESC</v>
-      </c>
-      <c r="F50" s="40" t="s">
-        <v>330</v>
-      </c>
-      <c r="G50" s="40">
-        <v>300</v>
-      </c>
-      <c r="H50" s="40">
-        <v>0</v>
-      </c>
-      <c r="I50" s="40">
+      <c r="A50" s="33">
+        <v>20049</v>
+      </c>
+      <c r="B50" s="34" t="s">
+        <v>480</v>
+      </c>
+      <c r="C50" s="35" t="s">
+        <v>481</v>
+      </c>
+      <c r="D50" s="33" t="s">
+        <v>414</v>
+      </c>
+      <c r="E50" s="33" t="str">
+        <f>D50&amp;"_DESC"</f>
+        <v>STR_NPC_N_0033_DESC</v>
+      </c>
+      <c r="F50" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G50" s="33">
+        <v>0</v>
+      </c>
+      <c r="H50" s="33">
+        <v>0</v>
+      </c>
+      <c r="I50" s="33">
         <v>1</v>
       </c>
-      <c r="J50" s="40">
-        <v>0</v>
-      </c>
-      <c r="K50" s="40">
-        <v>2000</v>
-      </c>
-      <c r="L50" s="40">
-        <v>0</v>
-      </c>
-      <c r="M50" s="40">
-        <v>0</v>
-      </c>
-      <c r="N50" s="40"/>
-      <c r="O50" s="40"/>
-      <c r="P50" s="40"/>
-      <c r="Q50" s="40" t="s">
-        <v>337</v>
-      </c>
-      <c r="R50" s="40"/>
-      <c r="S50" s="40"/>
-      <c r="T50" s="40"/>
-      <c r="U50" s="40"/>
-      <c r="V50" s="40"/>
-      <c r="W50" s="40"/>
-      <c r="X50" s="40"/>
-      <c r="Y50" s="40"/>
-      <c r="Z50" s="40"/>
-      <c r="AA50" s="40"/>
-      <c r="AB50" s="40"/>
-      <c r="AC50" s="40"/>
+      <c r="J50" s="33">
+        <v>0</v>
+      </c>
+      <c r="K50" s="33">
+        <v>0</v>
+      </c>
+      <c r="L50" s="33">
+        <v>0</v>
+      </c>
+      <c r="M50" s="33">
+        <v>0</v>
+      </c>
+      <c r="N50" s="33"/>
+      <c r="O50" s="33"/>
+      <c r="P50" s="33"/>
+      <c r="Q50" s="36" t="s">
+        <v>415</v>
+      </c>
+      <c r="T50" s="33" t="s">
+        <v>482</v>
+      </c>
+      <c r="U50" s="33" t="s">
+        <v>530</v>
+      </c>
+      <c r="V50" s="33" t="s">
+        <v>531</v>
+      </c>
+      <c r="W50" s="33" t="s">
+        <v>532</v>
+      </c>
+      <c r="X50" s="33" t="s">
+        <v>533</v>
+      </c>
+      <c r="Y50" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="Z50" s="33"/>
+      <c r="AA50" s="33"/>
+      <c r="AB50" s="33"/>
+      <c r="AC50" s="33"/>
     </row>
     <row r="51" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A51" s="40">
-        <v>26002</v>
-      </c>
-      <c r="B51" s="41" t="s">
-        <v>334</v>
-      </c>
-      <c r="C51" s="42" t="s">
-        <v>335</v>
-      </c>
-      <c r="D51" s="40" t="s">
-        <v>336</v>
-      </c>
-      <c r="E51" s="40" t="str">
-        <f t="shared" si="24"/>
-        <v>STR_TRAP_N_0002_DESC</v>
-      </c>
-      <c r="F51" s="40" t="s">
-        <v>330</v>
-      </c>
-      <c r="G51" s="40">
-        <v>0</v>
-      </c>
-      <c r="H51" s="40">
-        <v>0</v>
-      </c>
-      <c r="I51" s="40">
+      <c r="A51" s="33">
+        <v>20050</v>
+      </c>
+      <c r="B51" s="34" t="s">
+        <v>483</v>
+      </c>
+      <c r="C51" s="35" t="s">
+        <v>484</v>
+      </c>
+      <c r="D51" s="33" t="s">
+        <v>485</v>
+      </c>
+      <c r="E51" s="33" t="str">
+        <f>D51&amp;"_DESC"</f>
+        <v>STR_NPC_N_0050_DESC</v>
+      </c>
+      <c r="F51" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G51" s="33">
+        <v>0</v>
+      </c>
+      <c r="H51" s="33">
+        <v>0</v>
+      </c>
+      <c r="I51" s="33">
         <v>1</v>
       </c>
-      <c r="J51" s="40">
-        <v>0</v>
-      </c>
-      <c r="K51" s="40">
-        <v>0</v>
-      </c>
-      <c r="L51" s="40">
-        <v>0</v>
-      </c>
-      <c r="M51" s="40">
-        <v>0</v>
-      </c>
-      <c r="N51" s="40"/>
-      <c r="O51" s="40"/>
-      <c r="P51" s="40"/>
-      <c r="Q51" s="40" t="s">
-        <v>338</v>
-      </c>
-      <c r="R51" s="40"/>
-      <c r="S51" s="40"/>
-      <c r="T51" s="40"/>
-      <c r="U51" s="40"/>
-      <c r="V51" s="40"/>
-      <c r="W51" s="40"/>
-      <c r="X51" s="40"/>
-      <c r="Y51" s="40"/>
-      <c r="Z51" s="40"/>
-      <c r="AA51" s="40"/>
-      <c r="AB51" s="40"/>
-      <c r="AC51" s="40"/>
+      <c r="J51" s="33">
+        <v>0</v>
+      </c>
+      <c r="K51" s="33">
+        <v>0</v>
+      </c>
+      <c r="L51" s="33">
+        <v>0</v>
+      </c>
+      <c r="M51" s="33">
+        <v>0</v>
+      </c>
+      <c r="N51" s="33"/>
+      <c r="O51" s="33"/>
+      <c r="P51" s="33"/>
+      <c r="Q51" s="36" t="s">
+        <v>404</v>
+      </c>
+      <c r="T51" s="33" t="s">
+        <v>486</v>
+      </c>
+      <c r="U51" s="33" t="s">
+        <v>535</v>
+      </c>
+      <c r="V51" s="33" t="s">
+        <v>536</v>
+      </c>
+      <c r="W51" s="33" t="s">
+        <v>537</v>
+      </c>
+      <c r="X51" s="33"/>
+      <c r="Y51" s="33"/>
+      <c r="Z51" s="33"/>
+      <c r="AA51" s="33"/>
+      <c r="AB51" s="33"/>
+      <c r="AC51" s="33"/>
     </row>
     <row r="52" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A52" s="40">
-        <v>26003</v>
+        <v>22000</v>
       </c>
       <c r="B52" s="41" t="s">
-        <v>345</v>
+        <v>247</v>
       </c>
       <c r="C52" s="42" t="s">
-        <v>343</v>
-      </c>
-      <c r="D52" s="40" t="s">
-        <v>344</v>
+        <v>100</v>
+      </c>
+      <c r="D52" s="40" t="str">
+        <f t="shared" ref="D52:D53" si="13">"STR_"&amp;UPPER(C52)</f>
+        <v>STR_MOB_N_0001</v>
       </c>
       <c r="E52" s="40" t="str">
-        <f t="shared" ref="E52" si="25">D52&amp;"_DESC"</f>
-        <v>STR_TRAP_N_0003_DESC</v>
+        <f t="shared" ref="E52:E67" si="14">D52&amp;"_DESC"</f>
+        <v>STR_MOB_N_0001_DESC</v>
       </c>
       <c r="F52" s="40" t="s">
-        <v>330</v>
+        <v>101</v>
       </c>
       <c r="G52" s="40">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H52" s="40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" s="40">
         <v>1</v>
@@ -8818,19 +9340,21 @@
         <v>0</v>
       </c>
       <c r="K52" s="40">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="L52" s="40">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M52" s="40">
-        <v>0</v>
-      </c>
-      <c r="N52" s="40"/>
+        <v>20</v>
+      </c>
+      <c r="N52" s="40" t="s">
+        <v>225</v>
+      </c>
       <c r="O52" s="40"/>
       <c r="P52" s="40"/>
       <c r="Q52" s="40" t="s">
-        <v>346</v>
+        <v>226</v>
       </c>
       <c r="R52" s="40"/>
       <c r="S52" s="40"/>
@@ -8846,177 +9370,1673 @@
       <c r="AC52" s="40"/>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A53" s="33">
+      <c r="A53" s="40">
+        <v>22001</v>
+      </c>
+      <c r="B53" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="C53" s="41" t="s">
+        <v>138</v>
+      </c>
+      <c r="D53" s="40" t="str">
+        <f t="shared" si="13"/>
+        <v>STR_MOB_N_0002</v>
+      </c>
+      <c r="E53" s="40" t="str">
+        <f t="shared" si="14"/>
+        <v>STR_MOB_N_0002_DESC</v>
+      </c>
+      <c r="F53" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G53" s="40">
+        <v>1</v>
+      </c>
+      <c r="H53" s="40">
+        <v>1</v>
+      </c>
+      <c r="I53" s="40">
+        <v>1</v>
+      </c>
+      <c r="J53" s="40">
+        <v>0</v>
+      </c>
+      <c r="K53" s="40">
+        <v>2400</v>
+      </c>
+      <c r="L53" s="40">
+        <v>0</v>
+      </c>
+      <c r="M53" s="40">
+        <v>10</v>
+      </c>
+      <c r="N53" s="40"/>
+      <c r="O53" s="40"/>
+      <c r="P53" s="40"/>
+      <c r="Q53" s="40" t="s">
+        <v>139</v>
+      </c>
+      <c r="R53" s="40"/>
+      <c r="S53" s="40"/>
+      <c r="T53" s="40"/>
+      <c r="U53" s="40"/>
+      <c r="V53" s="40"/>
+      <c r="W53" s="40"/>
+      <c r="X53" s="40"/>
+      <c r="Y53" s="40"/>
+      <c r="Z53" s="40"/>
+      <c r="AA53" s="40"/>
+      <c r="AB53" s="40"/>
+      <c r="AC53" s="40"/>
+    </row>
+    <row r="54" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A54" s="40">
+        <v>22002</v>
+      </c>
+      <c r="B54" s="41" t="s">
+        <v>249</v>
+      </c>
+      <c r="C54" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="D54" s="40" t="str">
+        <f t="shared" ref="D54" si="15">"STR_"&amp;UPPER(C54)</f>
+        <v>STR_MOB_N_0003</v>
+      </c>
+      <c r="E54" s="40" t="str">
+        <f t="shared" ref="E54" si="16">D54&amp;"_DESC"</f>
+        <v>STR_MOB_N_0003_DESC</v>
+      </c>
+      <c r="F54" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G54" s="40">
+        <v>60</v>
+      </c>
+      <c r="H54" s="40">
+        <v>1</v>
+      </c>
+      <c r="I54" s="40">
+        <v>1</v>
+      </c>
+      <c r="J54" s="40">
+        <v>0</v>
+      </c>
+      <c r="K54" s="40">
+        <v>1500</v>
+      </c>
+      <c r="L54" s="40">
+        <v>15</v>
+      </c>
+      <c r="M54" s="40">
+        <v>30</v>
+      </c>
+      <c r="N54" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="O54" s="40"/>
+      <c r="P54" s="40"/>
+      <c r="Q54" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="R54" s="40"/>
+      <c r="S54" s="40"/>
+      <c r="T54" s="40"/>
+      <c r="U54" s="40"/>
+      <c r="V54" s="40"/>
+      <c r="W54" s="40"/>
+      <c r="X54" s="40"/>
+      <c r="Y54" s="40"/>
+      <c r="Z54" s="40"/>
+      <c r="AA54" s="40"/>
+      <c r="AB54" s="40"/>
+      <c r="AC54" s="40"/>
+    </row>
+    <row r="55" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A55" s="40">
+        <v>22003</v>
+      </c>
+      <c r="B55" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="C55" s="42" t="s">
+        <v>234</v>
+      </c>
+      <c r="D55" s="40" t="str">
+        <f t="shared" ref="D55" si="17">"STR_"&amp;UPPER(C55)</f>
+        <v>STR_MOB_N_0004</v>
+      </c>
+      <c r="E55" s="40" t="str">
+        <f t="shared" ref="E55" si="18">D55&amp;"_DESC"</f>
+        <v>STR_MOB_N_0004_DESC</v>
+      </c>
+      <c r="F55" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G55" s="40">
+        <v>25</v>
+      </c>
+      <c r="H55" s="40">
+        <v>1</v>
+      </c>
+      <c r="I55" s="40">
+        <v>1</v>
+      </c>
+      <c r="J55" s="40">
+        <v>0</v>
+      </c>
+      <c r="K55" s="40">
+        <v>1500</v>
+      </c>
+      <c r="L55" s="40">
+        <v>20</v>
+      </c>
+      <c r="M55" s="40">
+        <v>50</v>
+      </c>
+      <c r="N55" s="40" t="s">
+        <v>394</v>
+      </c>
+      <c r="O55" s="40" t="s">
+        <v>395</v>
+      </c>
+      <c r="P55" s="40"/>
+      <c r="Q55" s="40" t="s">
+        <v>244</v>
+      </c>
+      <c r="R55" s="40"/>
+      <c r="S55" s="40"/>
+      <c r="T55" s="40"/>
+      <c r="U55" s="40"/>
+      <c r="V55" s="40"/>
+      <c r="W55" s="40"/>
+      <c r="X55" s="40"/>
+      <c r="Y55" s="40"/>
+      <c r="Z55" s="40"/>
+      <c r="AA55" s="40"/>
+      <c r="AB55" s="40"/>
+      <c r="AC55" s="40"/>
+    </row>
+    <row r="56" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A56" s="40">
+        <v>22004</v>
+      </c>
+      <c r="B56" s="41" t="s">
+        <v>245</v>
+      </c>
+      <c r="C56" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="D56" s="40" t="str">
+        <f t="shared" ref="D56:D64" si="19">"STR_"&amp;UPPER(C56)</f>
+        <v>STR_MOB_N_0005</v>
+      </c>
+      <c r="E56" s="40" t="str">
+        <f t="shared" ref="E56:E64" si="20">D56&amp;"_DESC"</f>
+        <v>STR_MOB_N_0005_DESC</v>
+      </c>
+      <c r="F56" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G56" s="40">
+        <v>1</v>
+      </c>
+      <c r="H56" s="40">
+        <v>1</v>
+      </c>
+      <c r="I56" s="40">
+        <v>1</v>
+      </c>
+      <c r="J56" s="40">
+        <v>0</v>
+      </c>
+      <c r="K56" s="40">
+        <v>1200</v>
+      </c>
+      <c r="L56" s="40">
+        <v>70</v>
+      </c>
+      <c r="M56" s="40">
+        <v>10</v>
+      </c>
+      <c r="N56" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="O56" s="40"/>
+      <c r="P56" s="40"/>
+      <c r="Q56" s="40" t="s">
+        <v>246</v>
+      </c>
+      <c r="R56" s="40"/>
+      <c r="S56" s="40"/>
+      <c r="T56" s="40"/>
+      <c r="U56" s="40"/>
+      <c r="V56" s="40"/>
+      <c r="W56" s="40"/>
+      <c r="X56" s="40"/>
+      <c r="Y56" s="40"/>
+      <c r="Z56" s="40"/>
+      <c r="AA56" s="40"/>
+      <c r="AB56" s="40"/>
+      <c r="AC56" s="40"/>
+    </row>
+    <row r="57" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A57" s="40">
+        <v>22005</v>
+      </c>
+      <c r="B57" s="41" t="s">
+        <v>248</v>
+      </c>
+      <c r="C57" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="D57" s="40" t="str">
+        <f t="shared" si="19"/>
+        <v>STR_MOB_N_0006</v>
+      </c>
+      <c r="E57" s="40" t="str">
+        <f t="shared" si="20"/>
+        <v>STR_MOB_N_0006_DESC</v>
+      </c>
+      <c r="F57" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G57" s="40">
+        <v>40</v>
+      </c>
+      <c r="H57" s="40">
+        <v>1</v>
+      </c>
+      <c r="I57" s="40">
+        <v>1</v>
+      </c>
+      <c r="J57" s="40">
+        <v>0</v>
+      </c>
+      <c r="K57" s="40">
+        <v>1000</v>
+      </c>
+      <c r="L57" s="40">
+        <v>60</v>
+      </c>
+      <c r="M57" s="40">
+        <v>25</v>
+      </c>
+      <c r="N57" s="40" t="s">
+        <v>391</v>
+      </c>
+      <c r="O57" s="40"/>
+      <c r="P57" s="40"/>
+      <c r="Q57" s="40" t="s">
+        <v>251</v>
+      </c>
+      <c r="R57" s="40"/>
+      <c r="S57" s="40"/>
+      <c r="T57" s="40"/>
+      <c r="U57" s="40"/>
+      <c r="V57" s="40"/>
+      <c r="W57" s="40"/>
+      <c r="X57" s="40"/>
+      <c r="Y57" s="40"/>
+      <c r="Z57" s="40"/>
+      <c r="AA57" s="40"/>
+      <c r="AB57" s="40"/>
+      <c r="AC57" s="40"/>
+    </row>
+    <row r="58" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A58" s="40">
+        <v>22006</v>
+      </c>
+      <c r="B58" s="41" t="s">
+        <v>250</v>
+      </c>
+      <c r="C58" s="42" t="s">
+        <v>237</v>
+      </c>
+      <c r="D58" s="40" t="str">
+        <f t="shared" si="19"/>
+        <v>STR_MOB_N_0007</v>
+      </c>
+      <c r="E58" s="40" t="str">
+        <f t="shared" si="20"/>
+        <v>STR_MOB_N_0007_DESC</v>
+      </c>
+      <c r="F58" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G58" s="40">
+        <v>60</v>
+      </c>
+      <c r="H58" s="40">
+        <v>1</v>
+      </c>
+      <c r="I58" s="40">
+        <v>1</v>
+      </c>
+      <c r="J58" s="40">
+        <v>0</v>
+      </c>
+      <c r="K58" s="40">
+        <v>900</v>
+      </c>
+      <c r="L58" s="40">
+        <v>70</v>
+      </c>
+      <c r="M58" s="40">
+        <v>35</v>
+      </c>
+      <c r="N58" s="40" t="s">
+        <v>392</v>
+      </c>
+      <c r="O58" s="40" t="s">
+        <v>393</v>
+      </c>
+      <c r="P58" s="40"/>
+      <c r="Q58" s="40" t="s">
+        <v>252</v>
+      </c>
+      <c r="R58" s="40"/>
+      <c r="S58" s="40"/>
+      <c r="T58" s="40"/>
+      <c r="U58" s="40"/>
+      <c r="V58" s="40"/>
+      <c r="W58" s="40"/>
+      <c r="X58" s="40"/>
+      <c r="Y58" s="40"/>
+      <c r="Z58" s="40"/>
+      <c r="AA58" s="40"/>
+      <c r="AB58" s="40"/>
+      <c r="AC58" s="40"/>
+    </row>
+    <row r="59" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A59" s="40">
+        <v>22007</v>
+      </c>
+      <c r="B59" s="41" t="s">
+        <v>258</v>
+      </c>
+      <c r="C59" s="42" t="s">
+        <v>238</v>
+      </c>
+      <c r="D59" s="40" t="str">
+        <f t="shared" si="19"/>
+        <v>STR_MOB_N_0008</v>
+      </c>
+      <c r="E59" s="40" t="str">
+        <f t="shared" si="20"/>
+        <v>STR_MOB_N_0008_DESC</v>
+      </c>
+      <c r="F59" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G59" s="40">
+        <v>80</v>
+      </c>
+      <c r="H59" s="40">
+        <v>1</v>
+      </c>
+      <c r="I59" s="40">
+        <v>1</v>
+      </c>
+      <c r="J59" s="40">
+        <v>0</v>
+      </c>
+      <c r="K59" s="40">
+        <v>800</v>
+      </c>
+      <c r="L59" s="40">
+        <v>80</v>
+      </c>
+      <c r="M59" s="40">
+        <v>45</v>
+      </c>
+      <c r="N59" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="O59" s="40"/>
+      <c r="P59" s="40"/>
+      <c r="Q59" s="40" t="s">
+        <v>253</v>
+      </c>
+      <c r="R59" s="40"/>
+      <c r="S59" s="40"/>
+      <c r="T59" s="40"/>
+      <c r="U59" s="40"/>
+      <c r="V59" s="40"/>
+      <c r="W59" s="40"/>
+      <c r="X59" s="40"/>
+      <c r="Y59" s="40"/>
+      <c r="Z59" s="40"/>
+      <c r="AA59" s="40"/>
+      <c r="AB59" s="40"/>
+      <c r="AC59" s="40"/>
+    </row>
+    <row r="60" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A60" s="40">
+        <v>22008</v>
+      </c>
+      <c r="B60" s="41" t="s">
+        <v>259</v>
+      </c>
+      <c r="C60" s="42" t="s">
+        <v>239</v>
+      </c>
+      <c r="D60" s="40" t="str">
+        <f t="shared" si="19"/>
+        <v>STR_MOB_N_0009</v>
+      </c>
+      <c r="E60" s="40" t="str">
+        <f t="shared" si="20"/>
+        <v>STR_MOB_N_0009_DESC</v>
+      </c>
+      <c r="F60" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G60" s="40">
+        <v>1</v>
+      </c>
+      <c r="H60" s="40">
+        <v>1</v>
+      </c>
+      <c r="I60" s="40">
+        <v>1</v>
+      </c>
+      <c r="J60" s="40">
+        <v>0</v>
+      </c>
+      <c r="K60" s="40">
+        <v>1800</v>
+      </c>
+      <c r="L60" s="40">
+        <v>20</v>
+      </c>
+      <c r="M60" s="40">
+        <v>5</v>
+      </c>
+      <c r="N60" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="O60" s="40"/>
+      <c r="P60" s="40"/>
+      <c r="Q60" s="40" t="s">
+        <v>254</v>
+      </c>
+      <c r="R60" s="40"/>
+      <c r="S60" s="40"/>
+      <c r="T60" s="40"/>
+      <c r="U60" s="40"/>
+      <c r="V60" s="40"/>
+      <c r="W60" s="40"/>
+      <c r="X60" s="40"/>
+      <c r="Y60" s="40"/>
+      <c r="Z60" s="40"/>
+      <c r="AA60" s="40"/>
+      <c r="AB60" s="40"/>
+      <c r="AC60" s="40"/>
+    </row>
+    <row r="61" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A61" s="40">
+        <v>22009</v>
+      </c>
+      <c r="B61" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="C61" s="42" t="s">
+        <v>240</v>
+      </c>
+      <c r="D61" s="40" t="str">
+        <f t="shared" si="19"/>
+        <v>STR_MOB_N_0010</v>
+      </c>
+      <c r="E61" s="40" t="str">
+        <f t="shared" si="20"/>
+        <v>STR_MOB_N_0010_DESC</v>
+      </c>
+      <c r="F61" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G61" s="40">
+        <v>50</v>
+      </c>
+      <c r="H61" s="40">
+        <v>50</v>
+      </c>
+      <c r="I61" s="40">
+        <v>3</v>
+      </c>
+      <c r="J61" s="40">
+        <v>0</v>
+      </c>
+      <c r="K61" s="40">
+        <v>1500</v>
+      </c>
+      <c r="L61" s="40">
+        <v>0</v>
+      </c>
+      <c r="M61" s="40">
+        <v>70</v>
+      </c>
+      <c r="N61" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="O61" s="40"/>
+      <c r="P61" s="40"/>
+      <c r="Q61" s="40" t="s">
+        <v>255</v>
+      </c>
+      <c r="R61" s="40"/>
+      <c r="S61" s="40" t="s">
+        <v>285</v>
+      </c>
+      <c r="T61" s="40"/>
+      <c r="U61" s="40"/>
+      <c r="V61" s="40"/>
+      <c r="W61" s="40"/>
+      <c r="X61" s="40"/>
+      <c r="Y61" s="40"/>
+      <c r="Z61" s="40"/>
+      <c r="AA61" s="40"/>
+      <c r="AB61" s="40"/>
+      <c r="AC61" s="40"/>
+    </row>
+    <row r="62" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A62" s="40">
+        <v>22010</v>
+      </c>
+      <c r="B62" s="41" t="s">
+        <v>260</v>
+      </c>
+      <c r="C62" s="42" t="s">
+        <v>241</v>
+      </c>
+      <c r="D62" s="40" t="str">
+        <f t="shared" si="19"/>
+        <v>STR_MOB_N_0011</v>
+      </c>
+      <c r="E62" s="40" t="str">
+        <f t="shared" si="20"/>
+        <v>STR_MOB_N_0011_DESC</v>
+      </c>
+      <c r="F62" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G62" s="40">
+        <v>90</v>
+      </c>
+      <c r="H62" s="40">
+        <v>150</v>
+      </c>
+      <c r="I62" s="40">
+        <v>5</v>
+      </c>
+      <c r="J62" s="40">
+        <v>0</v>
+      </c>
+      <c r="K62" s="40">
+        <v>1200</v>
+      </c>
+      <c r="L62" s="40">
+        <v>45</v>
+      </c>
+      <c r="M62" s="40">
+        <v>250</v>
+      </c>
+      <c r="N62" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="O62" s="40"/>
+      <c r="P62" s="40"/>
+      <c r="Q62" s="40" t="s">
+        <v>256</v>
+      </c>
+      <c r="R62" s="40"/>
+      <c r="S62" s="40" t="s">
+        <v>400</v>
+      </c>
+      <c r="T62" s="40"/>
+      <c r="U62" s="40"/>
+      <c r="V62" s="40"/>
+      <c r="W62" s="40"/>
+      <c r="X62" s="40"/>
+      <c r="Y62" s="40"/>
+      <c r="Z62" s="40"/>
+      <c r="AA62" s="40"/>
+      <c r="AB62" s="40"/>
+      <c r="AC62" s="40"/>
+    </row>
+    <row r="63" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A63" s="40">
+        <v>22011</v>
+      </c>
+      <c r="B63" s="41" t="s">
+        <v>261</v>
+      </c>
+      <c r="C63" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="D63" s="40" t="str">
+        <f t="shared" si="19"/>
+        <v>STR_MOB_N_0012</v>
+      </c>
+      <c r="E63" s="40" t="str">
+        <f t="shared" si="20"/>
+        <v>STR_MOB_N_0012_DESC</v>
+      </c>
+      <c r="F63" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G63" s="40">
+        <v>120</v>
+      </c>
+      <c r="H63" s="40">
+        <v>80</v>
+      </c>
+      <c r="I63" s="40">
+        <v>1</v>
+      </c>
+      <c r="J63" s="40">
+        <v>0</v>
+      </c>
+      <c r="K63" s="40">
+        <v>1000</v>
+      </c>
+      <c r="L63" s="40">
+        <v>53</v>
+      </c>
+      <c r="M63" s="40">
+        <v>200</v>
+      </c>
+      <c r="N63" s="40" t="s">
+        <v>396</v>
+      </c>
+      <c r="O63" s="40" t="s">
+        <v>397</v>
+      </c>
+      <c r="P63" s="40"/>
+      <c r="Q63" s="40" t="s">
+        <v>257</v>
+      </c>
+      <c r="R63" s="40"/>
+      <c r="S63" s="40" t="s">
+        <v>285</v>
+      </c>
+      <c r="T63" s="40"/>
+      <c r="U63" s="40"/>
+      <c r="V63" s="40"/>
+      <c r="W63" s="40"/>
+      <c r="X63" s="40"/>
+      <c r="Y63" s="40"/>
+      <c r="Z63" s="40"/>
+      <c r="AA63" s="40"/>
+      <c r="AB63" s="40"/>
+      <c r="AC63" s="40"/>
+    </row>
+    <row r="64" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A64" s="40">
+        <v>22012</v>
+      </c>
+      <c r="B64" s="41" t="s">
+        <v>317</v>
+      </c>
+      <c r="C64" s="42" t="s">
+        <v>318</v>
+      </c>
+      <c r="D64" s="40" t="str">
+        <f t="shared" si="19"/>
+        <v>STR_MOB_N_0013</v>
+      </c>
+      <c r="E64" s="40" t="str">
+        <f t="shared" si="20"/>
+        <v>STR_MOB_N_0013_DESC</v>
+      </c>
+      <c r="F64" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G64" s="40">
+        <v>25</v>
+      </c>
+      <c r="H64" s="40">
+        <v>1</v>
+      </c>
+      <c r="I64" s="40">
+        <v>1</v>
+      </c>
+      <c r="J64" s="40">
+        <v>0</v>
+      </c>
+      <c r="K64" s="40">
+        <v>1500</v>
+      </c>
+      <c r="L64" s="40">
+        <v>20</v>
+      </c>
+      <c r="M64" s="40">
+        <v>1</v>
+      </c>
+      <c r="N64" s="40" t="s">
+        <v>398</v>
+      </c>
+      <c r="O64" s="40"/>
+      <c r="P64" s="40"/>
+      <c r="Q64" s="40" t="s">
+        <v>319</v>
+      </c>
+      <c r="R64" s="40"/>
+      <c r="S64" s="40"/>
+      <c r="T64" s="40"/>
+      <c r="U64" s="40"/>
+      <c r="V64" s="40"/>
+      <c r="W64" s="40"/>
+      <c r="X64" s="40"/>
+      <c r="Y64" s="40"/>
+      <c r="Z64" s="40"/>
+      <c r="AA64" s="40"/>
+      <c r="AB64" s="40"/>
+      <c r="AC64" s="40"/>
+    </row>
+    <row r="65" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A65" s="40">
+        <v>22013</v>
+      </c>
+      <c r="B65" s="41" t="s">
+        <v>320</v>
+      </c>
+      <c r="C65" s="42" t="s">
+        <v>321</v>
+      </c>
+      <c r="D65" s="40" t="str">
+        <f t="shared" ref="D65" si="21">"STR_"&amp;UPPER(C65)</f>
+        <v>STR_MOB_N_0014</v>
+      </c>
+      <c r="E65" s="40" t="str">
+        <f t="shared" ref="E65" si="22">D65&amp;"_DESC"</f>
+        <v>STR_MOB_N_0014_DESC</v>
+      </c>
+      <c r="F65" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G65" s="40">
+        <v>20</v>
+      </c>
+      <c r="H65" s="40">
+        <v>60</v>
+      </c>
+      <c r="I65" s="40">
+        <v>3</v>
+      </c>
+      <c r="J65" s="40">
+        <v>0</v>
+      </c>
+      <c r="K65" s="40">
+        <v>1500</v>
+      </c>
+      <c r="L65" s="40">
+        <v>15</v>
+      </c>
+      <c r="M65" s="40">
+        <v>70</v>
+      </c>
+      <c r="N65" s="40" t="s">
+        <v>399</v>
+      </c>
+      <c r="O65" s="40"/>
+      <c r="P65" s="40"/>
+      <c r="Q65" s="40" t="s">
+        <v>322</v>
+      </c>
+      <c r="R65" s="40"/>
+      <c r="S65" s="40" t="s">
+        <v>285</v>
+      </c>
+      <c r="T65" s="40"/>
+      <c r="U65" s="40"/>
+      <c r="V65" s="40"/>
+      <c r="W65" s="40"/>
+      <c r="X65" s="40"/>
+      <c r="Y65" s="40"/>
+      <c r="Z65" s="40"/>
+      <c r="AA65" s="40"/>
+      <c r="AB65" s="40"/>
+      <c r="AC65" s="40"/>
+    </row>
+    <row r="66" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A66" s="40">
+        <v>22015</v>
+      </c>
+      <c r="B66" s="41" t="s">
+        <v>457</v>
+      </c>
+      <c r="C66" s="42" t="s">
+        <v>458</v>
+      </c>
+      <c r="D66" s="40" t="str">
+        <f t="shared" ref="D66" si="23">"STR_"&amp;UPPER(C66)</f>
+        <v>STR_MOB_N_0015</v>
+      </c>
+      <c r="E66" s="40" t="str">
+        <f t="shared" ref="E66" si="24">D66&amp;"_DESC"</f>
+        <v>STR_MOB_N_0015_DESC</v>
+      </c>
+      <c r="F66" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G66" s="40">
+        <v>60</v>
+      </c>
+      <c r="H66" s="40">
+        <v>1</v>
+      </c>
+      <c r="I66" s="40">
+        <v>1</v>
+      </c>
+      <c r="J66" s="40">
+        <v>0</v>
+      </c>
+      <c r="K66" s="40">
+        <v>1100</v>
+      </c>
+      <c r="L66" s="40">
+        <v>35</v>
+      </c>
+      <c r="M66" s="40">
+        <v>80</v>
+      </c>
+      <c r="N66" s="40" t="s">
+        <v>399</v>
+      </c>
+      <c r="O66" s="40"/>
+      <c r="P66" s="40"/>
+      <c r="Q66" s="40" t="s">
+        <v>459</v>
+      </c>
+      <c r="R66" s="40"/>
+      <c r="S66" s="40" t="s">
+        <v>285</v>
+      </c>
+      <c r="T66" s="40"/>
+      <c r="U66" s="40"/>
+      <c r="V66" s="40"/>
+      <c r="W66" s="40"/>
+      <c r="X66" s="40"/>
+      <c r="Y66" s="40"/>
+      <c r="Z66" s="40"/>
+      <c r="AA66" s="40"/>
+      <c r="AB66" s="40"/>
+      <c r="AC66" s="40"/>
+    </row>
+    <row r="67" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A67" s="33">
+        <v>25000</v>
+      </c>
+      <c r="B67" s="34" t="s">
+        <v>386</v>
+      </c>
+      <c r="C67" s="35" t="s">
+        <v>204</v>
+      </c>
+      <c r="D67" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="E67" s="33" t="str">
+        <f t="shared" si="14"/>
+        <v>STR_BOX_N_0001_DESC</v>
+      </c>
+      <c r="F67" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G67" s="33">
+        <v>0</v>
+      </c>
+      <c r="H67" s="33">
+        <v>0</v>
+      </c>
+      <c r="I67" s="33">
+        <v>1</v>
+      </c>
+      <c r="J67" s="33">
+        <v>0</v>
+      </c>
+      <c r="K67" s="33">
+        <v>0</v>
+      </c>
+      <c r="L67" s="33">
+        <v>0</v>
+      </c>
+      <c r="M67" s="33">
+        <v>0</v>
+      </c>
+      <c r="N67" s="33" t="s">
+        <v>205</v>
+      </c>
+      <c r="O67" s="33"/>
+      <c r="P67" s="33"/>
+      <c r="Q67" s="36" t="s">
+        <v>327</v>
+      </c>
+      <c r="T67" s="33"/>
+      <c r="U67" s="33"/>
+      <c r="V67" s="33"/>
+      <c r="W67" s="33"/>
+      <c r="X67" s="33"/>
+      <c r="Y67" s="33"/>
+      <c r="Z67" s="33"/>
+      <c r="AA67" s="33"/>
+      <c r="AB67" s="33"/>
+      <c r="AC67" s="33"/>
+    </row>
+    <row r="68" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A68" s="33">
+        <v>25001</v>
+      </c>
+      <c r="B68" s="34" t="s">
+        <v>387</v>
+      </c>
+      <c r="C68" s="35" t="s">
+        <v>323</v>
+      </c>
+      <c r="D68" s="33" t="s">
+        <v>324</v>
+      </c>
+      <c r="E68" s="33" t="str">
+        <f t="shared" ref="E68:E72" si="25">D68&amp;"_DESC"</f>
+        <v>STR_BOX_N_0002_DESC</v>
+      </c>
+      <c r="F68" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G68" s="33">
+        <v>0</v>
+      </c>
+      <c r="H68" s="33">
+        <v>0</v>
+      </c>
+      <c r="I68" s="33">
+        <v>1</v>
+      </c>
+      <c r="J68" s="33">
+        <v>0</v>
+      </c>
+      <c r="K68" s="33">
+        <v>0</v>
+      </c>
+      <c r="L68" s="33">
+        <v>0</v>
+      </c>
+      <c r="M68" s="33">
+        <v>0</v>
+      </c>
+      <c r="N68" s="33" t="s">
+        <v>388</v>
+      </c>
+      <c r="O68" s="33"/>
+      <c r="P68" s="33"/>
+      <c r="Q68" s="36" t="s">
+        <v>327</v>
+      </c>
+      <c r="T68" s="33"/>
+      <c r="U68" s="33"/>
+      <c r="V68" s="33"/>
+      <c r="W68" s="33"/>
+      <c r="X68" s="33"/>
+      <c r="Y68" s="33"/>
+      <c r="Z68" s="33"/>
+      <c r="AA68" s="33"/>
+      <c r="AB68" s="33"/>
+      <c r="AC68" s="33"/>
+    </row>
+    <row r="69" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A69" s="33">
+        <v>25002</v>
+      </c>
+      <c r="B69" s="34" t="s">
+        <v>389</v>
+      </c>
+      <c r="C69" s="35" t="s">
+        <v>325</v>
+      </c>
+      <c r="D69" s="33" t="s">
+        <v>326</v>
+      </c>
+      <c r="E69" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>STR_BOX_N_0003_DESC</v>
+      </c>
+      <c r="F69" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G69" s="33">
+        <v>0</v>
+      </c>
+      <c r="H69" s="33">
+        <v>0</v>
+      </c>
+      <c r="I69" s="33">
+        <v>1</v>
+      </c>
+      <c r="J69" s="33">
+        <v>0</v>
+      </c>
+      <c r="K69" s="33">
+        <v>0</v>
+      </c>
+      <c r="L69" s="33">
+        <v>0</v>
+      </c>
+      <c r="M69" s="33">
+        <v>0</v>
+      </c>
+      <c r="N69" s="33" t="s">
+        <v>390</v>
+      </c>
+      <c r="O69" s="33"/>
+      <c r="P69" s="33"/>
+      <c r="Q69" s="36" t="s">
+        <v>327</v>
+      </c>
+      <c r="T69" s="33"/>
+      <c r="U69" s="33"/>
+      <c r="V69" s="33"/>
+      <c r="W69" s="33"/>
+      <c r="X69" s="33"/>
+      <c r="Y69" s="33"/>
+      <c r="Z69" s="33"/>
+      <c r="AA69" s="33"/>
+      <c r="AB69" s="33"/>
+      <c r="AC69" s="33"/>
+    </row>
+    <row r="70" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A70" s="33">
+        <v>25003</v>
+      </c>
+      <c r="B70" s="34" t="s">
+        <v>429</v>
+      </c>
+      <c r="C70" s="35" t="s">
+        <v>430</v>
+      </c>
+      <c r="D70" s="33" t="s">
+        <v>431</v>
+      </c>
+      <c r="E70" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>STR_BOX_N_0004_DESC</v>
+      </c>
+      <c r="F70" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G70" s="33">
+        <v>0</v>
+      </c>
+      <c r="H70" s="33">
+        <v>0</v>
+      </c>
+      <c r="I70" s="33">
+        <v>1</v>
+      </c>
+      <c r="J70" s="33">
+        <v>0</v>
+      </c>
+      <c r="K70" s="33">
+        <v>0</v>
+      </c>
+      <c r="L70" s="33">
+        <v>0</v>
+      </c>
+      <c r="M70" s="33">
+        <v>0</v>
+      </c>
+      <c r="N70" s="33" t="s">
+        <v>205</v>
+      </c>
+      <c r="O70" s="33"/>
+      <c r="P70" s="33"/>
+      <c r="Q70" s="36" t="s">
+        <v>327</v>
+      </c>
+      <c r="T70" s="33"/>
+      <c r="U70" s="33"/>
+      <c r="V70" s="33"/>
+      <c r="W70" s="33"/>
+      <c r="X70" s="33"/>
+      <c r="Y70" s="33"/>
+      <c r="Z70" s="33"/>
+      <c r="AA70" s="33"/>
+      <c r="AB70" s="33"/>
+      <c r="AC70" s="33"/>
+    </row>
+    <row r="71" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A71" s="33">
+        <v>25004</v>
+      </c>
+      <c r="B71" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="C71" s="35" t="s">
+        <v>438</v>
+      </c>
+      <c r="D71" s="33" t="s">
+        <v>440</v>
+      </c>
+      <c r="E71" s="33" t="str">
+        <f t="shared" ref="E71" si="26">D71&amp;"_DESC"</f>
+        <v>STR_OBJ_N_0001_DESC</v>
+      </c>
+      <c r="F71" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G71" s="33">
+        <v>0</v>
+      </c>
+      <c r="H71" s="33">
+        <v>0</v>
+      </c>
+      <c r="I71" s="33">
+        <v>1</v>
+      </c>
+      <c r="J71" s="33">
+        <v>0</v>
+      </c>
+      <c r="K71" s="33">
+        <v>0</v>
+      </c>
+      <c r="L71" s="33">
+        <v>0</v>
+      </c>
+      <c r="M71" s="33">
+        <v>0</v>
+      </c>
+      <c r="N71" s="33" t="s">
+        <v>205</v>
+      </c>
+      <c r="O71" s="33"/>
+      <c r="P71" s="33"/>
+      <c r="Q71" s="36" t="s">
+        <v>441</v>
+      </c>
+      <c r="T71" s="33"/>
+      <c r="U71" s="33"/>
+      <c r="V71" s="33"/>
+      <c r="W71" s="33"/>
+      <c r="X71" s="33"/>
+      <c r="Y71" s="33"/>
+      <c r="Z71" s="33"/>
+      <c r="AA71" s="33"/>
+      <c r="AB71" s="33"/>
+      <c r="AC71" s="33"/>
+    </row>
+    <row r="72" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A72" s="40">
+        <v>26000</v>
+      </c>
+      <c r="B72" s="41" t="s">
+        <v>328</v>
+      </c>
+      <c r="C72" s="42" t="s">
+        <v>329</v>
+      </c>
+      <c r="D72" s="40" t="s">
+        <v>223</v>
+      </c>
+      <c r="E72" s="40" t="str">
+        <f t="shared" si="25"/>
+        <v>STR_BOX_N_0001_DESC</v>
+      </c>
+      <c r="F72" s="40" t="s">
+        <v>330</v>
+      </c>
+      <c r="G72" s="40">
+        <v>300</v>
+      </c>
+      <c r="H72" s="40">
+        <v>0</v>
+      </c>
+      <c r="I72" s="40">
+        <v>1</v>
+      </c>
+      <c r="J72" s="40">
+        <v>0</v>
+      </c>
+      <c r="K72" s="40">
+        <v>0</v>
+      </c>
+      <c r="L72" s="40">
+        <v>0</v>
+      </c>
+      <c r="M72" s="40">
+        <v>0</v>
+      </c>
+      <c r="N72" s="40"/>
+      <c r="O72" s="40"/>
+      <c r="P72" s="40"/>
+      <c r="Q72" s="40" t="s">
+        <v>377</v>
+      </c>
+      <c r="R72" s="40"/>
+      <c r="S72" s="40"/>
+      <c r="T72" s="40"/>
+      <c r="U72" s="40"/>
+      <c r="V72" s="40"/>
+      <c r="W72" s="40"/>
+      <c r="X72" s="40"/>
+      <c r="Y72" s="40"/>
+      <c r="Z72" s="40"/>
+      <c r="AA72" s="40"/>
+      <c r="AB72" s="40"/>
+      <c r="AC72" s="40"/>
+    </row>
+    <row r="73" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A73" s="40">
+        <v>26001</v>
+      </c>
+      <c r="B73" s="41" t="s">
+        <v>331</v>
+      </c>
+      <c r="C73" s="42" t="s">
+        <v>332</v>
+      </c>
+      <c r="D73" s="40" t="s">
+        <v>333</v>
+      </c>
+      <c r="E73" s="40" t="str">
+        <f t="shared" ref="E73:E77" si="27">D73&amp;"_DESC"</f>
+        <v>STR_TRAP_N_0001_DESC</v>
+      </c>
+      <c r="F73" s="40" t="s">
+        <v>330</v>
+      </c>
+      <c r="G73" s="40">
+        <v>300</v>
+      </c>
+      <c r="H73" s="40">
+        <v>0</v>
+      </c>
+      <c r="I73" s="40">
+        <v>1</v>
+      </c>
+      <c r="J73" s="40">
+        <v>0</v>
+      </c>
+      <c r="K73" s="40">
+        <v>2000</v>
+      </c>
+      <c r="L73" s="40">
+        <v>0</v>
+      </c>
+      <c r="M73" s="40">
+        <v>0</v>
+      </c>
+      <c r="N73" s="40"/>
+      <c r="O73" s="40"/>
+      <c r="P73" s="40"/>
+      <c r="Q73" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="R73" s="40"/>
+      <c r="S73" s="40"/>
+      <c r="T73" s="40"/>
+      <c r="U73" s="40"/>
+      <c r="V73" s="40"/>
+      <c r="W73" s="40"/>
+      <c r="X73" s="40"/>
+      <c r="Y73" s="40"/>
+      <c r="Z73" s="40"/>
+      <c r="AA73" s="40"/>
+      <c r="AB73" s="40"/>
+      <c r="AC73" s="40"/>
+    </row>
+    <row r="74" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A74" s="40">
+        <v>26002</v>
+      </c>
+      <c r="B74" s="41" t="s">
+        <v>334</v>
+      </c>
+      <c r="C74" s="42" t="s">
+        <v>335</v>
+      </c>
+      <c r="D74" s="40" t="s">
+        <v>336</v>
+      </c>
+      <c r="E74" s="40" t="str">
+        <f t="shared" si="27"/>
+        <v>STR_TRAP_N_0002_DESC</v>
+      </c>
+      <c r="F74" s="40" t="s">
+        <v>330</v>
+      </c>
+      <c r="G74" s="40">
+        <v>0</v>
+      </c>
+      <c r="H74" s="40">
+        <v>0</v>
+      </c>
+      <c r="I74" s="40">
+        <v>1</v>
+      </c>
+      <c r="J74" s="40">
+        <v>0</v>
+      </c>
+      <c r="K74" s="40">
+        <v>0</v>
+      </c>
+      <c r="L74" s="40">
+        <v>0</v>
+      </c>
+      <c r="M74" s="40">
+        <v>0</v>
+      </c>
+      <c r="N74" s="40"/>
+      <c r="O74" s="40"/>
+      <c r="P74" s="40"/>
+      <c r="Q74" s="40" t="s">
+        <v>338</v>
+      </c>
+      <c r="R74" s="40"/>
+      <c r="S74" s="40"/>
+      <c r="T74" s="40"/>
+      <c r="U74" s="40"/>
+      <c r="V74" s="40"/>
+      <c r="W74" s="40"/>
+      <c r="X74" s="40"/>
+      <c r="Y74" s="40"/>
+      <c r="Z74" s="40"/>
+      <c r="AA74" s="40"/>
+      <c r="AB74" s="40"/>
+      <c r="AC74" s="40"/>
+    </row>
+    <row r="75" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A75" s="40">
+        <v>26003</v>
+      </c>
+      <c r="B75" s="41" t="s">
+        <v>345</v>
+      </c>
+      <c r="C75" s="42" t="s">
+        <v>343</v>
+      </c>
+      <c r="D75" s="40" t="s">
+        <v>344</v>
+      </c>
+      <c r="E75" s="40" t="str">
+        <f t="shared" ref="E75" si="28">D75&amp;"_DESC"</f>
+        <v>STR_TRAP_N_0003_DESC</v>
+      </c>
+      <c r="F75" s="40" t="s">
+        <v>330</v>
+      </c>
+      <c r="G75" s="40">
+        <v>0</v>
+      </c>
+      <c r="H75" s="40">
+        <v>0</v>
+      </c>
+      <c r="I75" s="40">
+        <v>1</v>
+      </c>
+      <c r="J75" s="40">
+        <v>0</v>
+      </c>
+      <c r="K75" s="40">
+        <v>0</v>
+      </c>
+      <c r="L75" s="40">
+        <v>0</v>
+      </c>
+      <c r="M75" s="40">
+        <v>0</v>
+      </c>
+      <c r="N75" s="40"/>
+      <c r="O75" s="40"/>
+      <c r="P75" s="40"/>
+      <c r="Q75" s="40" t="s">
+        <v>346</v>
+      </c>
+      <c r="R75" s="40"/>
+      <c r="S75" s="40"/>
+      <c r="T75" s="40"/>
+      <c r="U75" s="40"/>
+      <c r="V75" s="40"/>
+      <c r="W75" s="40"/>
+      <c r="X75" s="40"/>
+      <c r="Y75" s="40"/>
+      <c r="Z75" s="40"/>
+      <c r="AA75" s="40"/>
+      <c r="AB75" s="40"/>
+      <c r="AC75" s="40"/>
+    </row>
+    <row r="76" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A76" s="40">
+        <v>26004</v>
+      </c>
+      <c r="B76" s="41" t="s">
+        <v>442</v>
+      </c>
+      <c r="C76" s="42" t="s">
+        <v>329</v>
+      </c>
+      <c r="D76" s="40" t="s">
+        <v>439</v>
+      </c>
+      <c r="E76" s="40" t="str">
+        <f t="shared" ref="E76" si="29">D76&amp;"_DESC"</f>
+        <v>STR_OBJ_N_0001_DESC</v>
+      </c>
+      <c r="F76" s="40" t="s">
+        <v>330</v>
+      </c>
+      <c r="G76" s="40">
+        <v>300</v>
+      </c>
+      <c r="H76" s="40">
+        <v>0</v>
+      </c>
+      <c r="I76" s="40">
+        <v>1</v>
+      </c>
+      <c r="J76" s="40">
+        <v>0</v>
+      </c>
+      <c r="K76" s="40">
+        <v>0</v>
+      </c>
+      <c r="L76" s="40">
+        <v>0</v>
+      </c>
+      <c r="M76" s="40">
+        <v>0</v>
+      </c>
+      <c r="N76" s="40"/>
+      <c r="O76" s="40"/>
+      <c r="P76" s="40"/>
+      <c r="Q76" s="40" t="s">
+        <v>443</v>
+      </c>
+      <c r="R76" s="40"/>
+      <c r="S76" s="40"/>
+      <c r="T76" s="40"/>
+      <c r="U76" s="40"/>
+      <c r="V76" s="40"/>
+      <c r="W76" s="40"/>
+      <c r="X76" s="40"/>
+      <c r="Y76" s="40"/>
+      <c r="Z76" s="40"/>
+      <c r="AA76" s="40"/>
+      <c r="AB76" s="40"/>
+      <c r="AC76" s="40"/>
+    </row>
+    <row r="77" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A77" s="33">
         <v>27000</v>
       </c>
-      <c r="B53" s="34" t="s">
+      <c r="B77" s="34" t="s">
         <v>339</v>
       </c>
-      <c r="C53" s="35" t="s">
+      <c r="C77" s="35" t="s">
         <v>340</v>
       </c>
-      <c r="D53" s="33" t="s">
+      <c r="D77" s="33" t="s">
         <v>341</v>
       </c>
-      <c r="E53" s="33" t="str">
-        <f t="shared" si="24"/>
+      <c r="E77" s="33" t="str">
+        <f t="shared" si="27"/>
         <v>STR_DOOR_N_0001_DESC</v>
       </c>
-      <c r="F53" s="33" t="s">
+      <c r="F77" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="G53" s="33">
-        <v>0</v>
-      </c>
-      <c r="H53" s="33">
-        <v>0</v>
-      </c>
-      <c r="I53" s="33">
+      <c r="G77" s="33">
+        <v>0</v>
+      </c>
+      <c r="H77" s="33">
+        <v>0</v>
+      </c>
+      <c r="I77" s="33">
         <v>1</v>
       </c>
-      <c r="J53" s="33">
-        <v>0</v>
-      </c>
-      <c r="K53" s="33">
-        <v>0</v>
-      </c>
-      <c r="L53" s="33">
-        <v>0</v>
-      </c>
-      <c r="M53" s="33">
-        <v>0</v>
-      </c>
-      <c r="N53" s="33"/>
-      <c r="O53" s="33"/>
-      <c r="P53" s="33"/>
-      <c r="Q53" s="36" t="s">
+      <c r="J77" s="33">
+        <v>0</v>
+      </c>
+      <c r="K77" s="33">
+        <v>0</v>
+      </c>
+      <c r="L77" s="33">
+        <v>0</v>
+      </c>
+      <c r="M77" s="33">
+        <v>0</v>
+      </c>
+      <c r="N77" s="33"/>
+      <c r="O77" s="33"/>
+      <c r="P77" s="33"/>
+      <c r="Q77" s="36" t="s">
         <v>342</v>
       </c>
-      <c r="T53" s="33"/>
-      <c r="U53" s="33"/>
-      <c r="V53" s="33"/>
-      <c r="W53" s="33"/>
-      <c r="X53" s="33"/>
-      <c r="Y53" s="33"/>
-      <c r="Z53" s="33"/>
-      <c r="AA53" s="33"/>
-      <c r="AB53" s="33"/>
-      <c r="AC53" s="33"/>
-    </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A54" s="33"/>
-      <c r="D54" s="33"/>
-      <c r="E54" s="33"/>
-      <c r="M54" s="33"/>
-      <c r="N54" s="33"/>
-      <c r="O54" s="33"/>
-      <c r="P54" s="33"/>
-      <c r="T54" s="33"/>
-      <c r="U54" s="33"/>
-      <c r="V54" s="33"/>
-      <c r="W54" s="33"/>
-      <c r="X54" s="33"/>
-      <c r="Y54" s="33"/>
-      <c r="Z54" s="33"/>
-      <c r="AA54" s="33"/>
-      <c r="AB54" s="33"/>
-      <c r="AC54" s="33"/>
-    </row>
-    <row r="55" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A55" s="33"/>
-      <c r="B55" s="34"/>
-      <c r="D55" s="33"/>
-      <c r="E55" s="33"/>
-      <c r="M55" s="33"/>
-      <c r="N55" s="33"/>
-      <c r="O55" s="33"/>
-      <c r="P55" s="33"/>
-      <c r="T55" s="33"/>
-      <c r="U55" s="33"/>
-      <c r="V55" s="33"/>
-      <c r="W55" s="33"/>
-      <c r="X55" s="33"/>
-      <c r="Y55" s="33"/>
-      <c r="Z55" s="33"/>
-      <c r="AA55" s="33"/>
-      <c r="AB55" s="33"/>
-      <c r="AC55" s="33"/>
-    </row>
-    <row r="56" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A56" s="33"/>
-      <c r="D56" s="33"/>
-      <c r="E56" s="33"/>
-      <c r="M56" s="33"/>
-      <c r="N56" s="33"/>
-      <c r="O56" s="33"/>
-      <c r="P56" s="33"/>
-      <c r="T56" s="33"/>
-      <c r="U56" s="33"/>
-      <c r="V56" s="33"/>
-      <c r="W56" s="33"/>
-      <c r="X56" s="33"/>
-      <c r="Y56" s="33"/>
-      <c r="Z56" s="33"/>
-      <c r="AA56" s="33"/>
-      <c r="AB56" s="33"/>
-      <c r="AC56" s="33"/>
-    </row>
-    <row r="57" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A57" s="33"/>
-      <c r="D57" s="33"/>
-      <c r="E57" s="33"/>
-      <c r="M57" s="33"/>
-      <c r="N57" s="33"/>
-      <c r="O57" s="33"/>
-      <c r="P57" s="33"/>
-      <c r="T57" s="33"/>
-      <c r="U57" s="33"/>
-      <c r="V57" s="33"/>
-      <c r="W57" s="33"/>
-      <c r="X57" s="33"/>
-      <c r="Y57" s="33"/>
-      <c r="Z57" s="33"/>
-      <c r="AA57" s="33"/>
-      <c r="AB57" s="33"/>
-      <c r="AC57" s="33"/>
-    </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A58" s="33"/>
-      <c r="D58" s="33"/>
-      <c r="E58" s="33"/>
-      <c r="M58" s="33"/>
-      <c r="N58" s="33"/>
-      <c r="O58" s="33"/>
-      <c r="P58" s="33"/>
-      <c r="T58" s="33"/>
-      <c r="U58" s="33"/>
-      <c r="V58" s="33"/>
-      <c r="W58" s="33"/>
-      <c r="X58" s="33"/>
-      <c r="Y58" s="33"/>
-      <c r="Z58" s="33"/>
-      <c r="AA58" s="33"/>
-      <c r="AB58" s="33"/>
-      <c r="AC58" s="33"/>
-    </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A59" s="33"/>
-      <c r="D59" s="33"/>
-      <c r="E59" s="33"/>
-      <c r="M59" s="33"/>
-      <c r="N59" s="33"/>
-      <c r="O59" s="33"/>
-      <c r="P59" s="33"/>
-      <c r="T59" s="33"/>
-      <c r="U59" s="33"/>
-      <c r="V59" s="33"/>
-      <c r="W59" s="33"/>
-      <c r="X59" s="33"/>
-      <c r="Y59" s="33"/>
-      <c r="Z59" s="33"/>
-      <c r="AA59" s="33"/>
-      <c r="AB59" s="33"/>
-      <c r="AC59" s="33"/>
+      <c r="T77" s="33"/>
+      <c r="U77" s="33"/>
+      <c r="V77" s="33"/>
+      <c r="W77" s="33"/>
+      <c r="X77" s="33"/>
+      <c r="Y77" s="33"/>
+      <c r="Z77" s="33"/>
+      <c r="AA77" s="33"/>
+      <c r="AB77" s="33"/>
+      <c r="AC77" s="33"/>
+    </row>
+    <row r="78" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A78" s="33"/>
+      <c r="D78" s="33"/>
+      <c r="E78" s="33"/>
+      <c r="M78" s="33"/>
+      <c r="N78" s="33"/>
+      <c r="O78" s="33"/>
+      <c r="P78" s="33"/>
+      <c r="T78" s="33"/>
+      <c r="U78" s="33"/>
+      <c r="V78" s="33"/>
+      <c r="W78" s="33"/>
+      <c r="X78" s="33"/>
+      <c r="Y78" s="33"/>
+      <c r="Z78" s="33"/>
+      <c r="AA78" s="33"/>
+      <c r="AB78" s="33"/>
+      <c r="AC78" s="33"/>
+    </row>
+    <row r="79" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A79" s="33"/>
+      <c r="B79" s="34"/>
+      <c r="D79" s="33"/>
+      <c r="E79" s="33"/>
+      <c r="M79" s="33"/>
+      <c r="N79" s="33"/>
+      <c r="O79" s="33"/>
+      <c r="P79" s="33"/>
+      <c r="T79" s="33"/>
+      <c r="U79" s="33"/>
+      <c r="V79" s="33"/>
+      <c r="W79" s="33"/>
+      <c r="X79" s="33"/>
+      <c r="Y79" s="33"/>
+      <c r="Z79" s="33"/>
+      <c r="AA79" s="33"/>
+      <c r="AB79" s="33"/>
+      <c r="AC79" s="33"/>
+    </row>
+    <row r="80" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A80" s="33"/>
+      <c r="D80" s="33"/>
+      <c r="E80" s="33"/>
+      <c r="M80" s="33"/>
+      <c r="N80" s="33"/>
+      <c r="O80" s="33"/>
+      <c r="P80" s="33"/>
+      <c r="T80" s="33"/>
+      <c r="U80" s="33"/>
+      <c r="V80" s="33"/>
+      <c r="W80" s="33"/>
+      <c r="X80" s="33"/>
+      <c r="Y80" s="33"/>
+      <c r="Z80" s="33"/>
+      <c r="AA80" s="33"/>
+      <c r="AB80" s="33"/>
+      <c r="AC80" s="33"/>
+    </row>
+    <row r="81" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A81" s="33"/>
+      <c r="D81" s="33"/>
+      <c r="E81" s="33"/>
+      <c r="M81" s="33"/>
+      <c r="N81" s="33"/>
+      <c r="O81" s="33"/>
+      <c r="P81" s="33"/>
+      <c r="T81" s="33"/>
+      <c r="U81" s="33"/>
+      <c r="V81" s="33"/>
+      <c r="W81" s="33"/>
+      <c r="X81" s="33"/>
+      <c r="Y81" s="33"/>
+      <c r="Z81" s="33"/>
+      <c r="AA81" s="33"/>
+      <c r="AB81" s="33"/>
+      <c r="AC81" s="33"/>
+    </row>
+    <row r="82" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A82" s="33"/>
+      <c r="D82" s="33"/>
+      <c r="E82" s="33"/>
+      <c r="M82" s="33"/>
+      <c r="N82" s="33"/>
+      <c r="O82" s="33"/>
+      <c r="P82" s="33"/>
+      <c r="T82" s="33"/>
+      <c r="U82" s="33"/>
+      <c r="V82" s="33"/>
+      <c r="W82" s="33"/>
+      <c r="X82" s="33"/>
+      <c r="Y82" s="33"/>
+      <c r="Z82" s="33"/>
+      <c r="AA82" s="33"/>
+      <c r="AB82" s="33"/>
+      <c r="AC82" s="33"/>
+    </row>
+    <row r="83" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A83" s="33"/>
+      <c r="D83" s="33"/>
+      <c r="E83" s="33"/>
+      <c r="M83" s="33"/>
+      <c r="N83" s="33"/>
+      <c r="O83" s="33"/>
+      <c r="P83" s="33"/>
+      <c r="T83" s="33"/>
+      <c r="U83" s="33"/>
+      <c r="V83" s="33"/>
+      <c r="W83" s="33"/>
+      <c r="X83" s="33"/>
+      <c r="Y83" s="33"/>
+      <c r="Z83" s="33"/>
+      <c r="AA83" s="33"/>
+      <c r="AB83" s="33"/>
+      <c r="AC83" s="33"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:U2"/>
@@ -9030,7 +11050,7 @@
           <x14:formula1>
             <xm:f>Type!$A$2:$A$20</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F53</xm:sqref>
+          <xm:sqref>F2:F77</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/30_table/01_테스트버전/Table_Data_Npc.xlsx
+++ b/30_table/01_테스트버전/Table_Data_Npc.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="551">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1908,6 +1908,48 @@
   </si>
   <si>
     <t>STR_STORY_NPC_20050_04</t>
+  </si>
+  <si>
+    <t>비석_59000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_n_0051</t>
+  </si>
+  <si>
+    <t>STR_NPC_N_0051</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20051_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20051_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20051_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20051_04</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20051_05</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20051_06</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20051_07</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20051_08</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20051_09</t>
+  </si>
+  <si>
+    <t>npc_0022</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -5905,7 +5947,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AC83"/>
+  <dimension ref="A1:AC84"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" style="36" bestFit="1" customWidth="1"/>
@@ -7890,7 +7932,7 @@
         <v>348</v>
       </c>
       <c r="E30" s="33" t="str">
-        <f>D30&amp;"_DESC"</f>
+        <f t="shared" ref="E30:E52" si="13">D30&amp;"_DESC"</f>
         <v>STR_NPC_N_0026_DESC</v>
       </c>
       <c r="F30" s="33" t="s">
@@ -7952,7 +7994,7 @@
         <v>380</v>
       </c>
       <c r="E31" s="33" t="str">
-        <f>D31&amp;"_DESC"</f>
+        <f t="shared" si="13"/>
         <v>STR_NPC_N_0030_DESC</v>
       </c>
       <c r="F31" s="33" t="s">
@@ -8018,7 +8060,7 @@
         <v>403</v>
       </c>
       <c r="E32" s="33" t="str">
-        <f>D32&amp;"_DESC"</f>
+        <f t="shared" si="13"/>
         <v>STR_NPC_N_0031_DESC</v>
       </c>
       <c r="F32" s="33" t="s">
@@ -8084,7 +8126,7 @@
         <v>403</v>
       </c>
       <c r="E33" s="33" t="str">
-        <f>D33&amp;"_DESC"</f>
+        <f t="shared" si="13"/>
         <v>STR_NPC_N_0031_DESC</v>
       </c>
       <c r="F33" s="33" t="s">
@@ -8148,7 +8190,7 @@
         <v>414</v>
       </c>
       <c r="E34" s="33" t="str">
-        <f>D34&amp;"_DESC"</f>
+        <f t="shared" si="13"/>
         <v>STR_NPC_N_0033_DESC</v>
       </c>
       <c r="F34" s="33" t="s">
@@ -8216,7 +8258,7 @@
         <v>414</v>
       </c>
       <c r="E35" s="33" t="str">
-        <f>D35&amp;"_DESC"</f>
+        <f t="shared" si="13"/>
         <v>STR_NPC_N_0033_DESC</v>
       </c>
       <c r="F35" s="33" t="s">
@@ -8280,7 +8322,7 @@
         <v>419</v>
       </c>
       <c r="E36" s="33" t="str">
-        <f>D36&amp;"_DESC"</f>
+        <f t="shared" si="13"/>
         <v>STR_NPC_N_0035_DESC</v>
       </c>
       <c r="F36" s="33" t="s">
@@ -8346,7 +8388,7 @@
         <v>419</v>
       </c>
       <c r="E37" s="33" t="str">
-        <f>D37&amp;"_DESC"</f>
+        <f t="shared" si="13"/>
         <v>STR_NPC_N_0035_DESC</v>
       </c>
       <c r="F37" s="33" t="s">
@@ -8410,7 +8452,7 @@
         <v>414</v>
       </c>
       <c r="E38" s="33" t="str">
-        <f>D38&amp;"_DESC"</f>
+        <f t="shared" si="13"/>
         <v>STR_NPC_N_0033_DESC</v>
       </c>
       <c r="F38" s="33" t="s">
@@ -8478,7 +8520,7 @@
         <v>434</v>
       </c>
       <c r="E39" s="33" t="str">
-        <f>D39&amp;"_DESC"</f>
+        <f t="shared" si="13"/>
         <v>STR_NPC_N_0038_DESC</v>
       </c>
       <c r="F39" s="33" t="s">
@@ -8546,7 +8588,7 @@
         <v>434</v>
       </c>
       <c r="E40" s="33" t="str">
-        <f>D40&amp;"_DESC"</f>
+        <f t="shared" si="13"/>
         <v>STR_NPC_N_0038_DESC</v>
       </c>
       <c r="F40" s="33" t="s">
@@ -8606,7 +8648,7 @@
         <v>434</v>
       </c>
       <c r="E41" s="33" t="str">
-        <f>D41&amp;"_DESC"</f>
+        <f t="shared" si="13"/>
         <v>STR_NPC_N_0038_DESC</v>
       </c>
       <c r="F41" s="33" t="s">
@@ -8668,7 +8710,7 @@
         <v>456</v>
       </c>
       <c r="E42" s="33" t="str">
-        <f>D42&amp;"_DESC"</f>
+        <f t="shared" si="13"/>
         <v>STR_NPC_N_0041_DESC</v>
       </c>
       <c r="F42" s="33" t="s">
@@ -8736,7 +8778,7 @@
         <v>456</v>
       </c>
       <c r="E43" s="33" t="str">
-        <f>D43&amp;"_DESC"</f>
+        <f t="shared" si="13"/>
         <v>STR_NPC_N_0041_DESC</v>
       </c>
       <c r="F43" s="33" t="s">
@@ -8802,7 +8844,7 @@
         <v>456</v>
       </c>
       <c r="E44" s="33" t="str">
-        <f>D44&amp;"_DESC"</f>
+        <f t="shared" si="13"/>
         <v>STR_NPC_N_0041_DESC</v>
       </c>
       <c r="F44" s="33" t="s">
@@ -8864,7 +8906,7 @@
         <v>462</v>
       </c>
       <c r="E45" s="33" t="str">
-        <f>D45&amp;"_DESC"</f>
+        <f t="shared" si="13"/>
         <v>STR_NPC_N_0044_DESC</v>
       </c>
       <c r="F45" s="33" t="s">
@@ -8926,7 +8968,7 @@
         <v>456</v>
       </c>
       <c r="E46" s="33" t="str">
-        <f>D46&amp;"_DESC"</f>
+        <f t="shared" si="13"/>
         <v>STR_NPC_N_0041_DESC</v>
       </c>
       <c r="F46" s="33" t="s">
@@ -8988,7 +9030,7 @@
         <v>456</v>
       </c>
       <c r="E47" s="33" t="str">
-        <f>D47&amp;"_DESC"</f>
+        <f t="shared" si="13"/>
         <v>STR_NPC_N_0041_DESC</v>
       </c>
       <c r="F47" s="33" t="s">
@@ -9050,7 +9092,7 @@
         <v>456</v>
       </c>
       <c r="E48" s="33" t="str">
-        <f>D48&amp;"_DESC"</f>
+        <f t="shared" si="13"/>
         <v>STR_NPC_N_0041_DESC</v>
       </c>
       <c r="F48" s="33" t="s">
@@ -9116,7 +9158,7 @@
         <v>478</v>
       </c>
       <c r="E49" s="33" t="str">
-        <f>D49&amp;"_DESC"</f>
+        <f t="shared" si="13"/>
         <v>STR_NPC_N_0048_DESC</v>
       </c>
       <c r="F49" s="33" t="s">
@@ -9184,7 +9226,7 @@
         <v>414</v>
       </c>
       <c r="E50" s="33" t="str">
-        <f>D50&amp;"_DESC"</f>
+        <f t="shared" si="13"/>
         <v>STR_NPC_N_0033_DESC</v>
       </c>
       <c r="F50" s="33" t="s">
@@ -9254,7 +9296,7 @@
         <v>485</v>
       </c>
       <c r="E51" s="33" t="str">
-        <f>D51&amp;"_DESC"</f>
+        <f t="shared" si="13"/>
         <v>STR_NPC_N_0050_DESC</v>
       </c>
       <c r="F51" s="33" t="s">
@@ -9307,91 +9349,104 @@
       <c r="AC51" s="33"/>
     </row>
     <row r="52" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A52" s="40">
-        <v>22000</v>
-      </c>
-      <c r="B52" s="41" t="s">
-        <v>247</v>
-      </c>
-      <c r="C52" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="D52" s="40" t="str">
-        <f t="shared" ref="D52:D53" si="13">"STR_"&amp;UPPER(C52)</f>
-        <v>STR_MOB_N_0001</v>
-      </c>
-      <c r="E52" s="40" t="str">
-        <f t="shared" ref="E52:E67" si="14">D52&amp;"_DESC"</f>
-        <v>STR_MOB_N_0001_DESC</v>
-      </c>
-      <c r="F52" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G52" s="40">
-        <v>10</v>
-      </c>
-      <c r="H52" s="40">
+      <c r="A52" s="33">
+        <v>20051</v>
+      </c>
+      <c r="B52" s="34" t="s">
+        <v>538</v>
+      </c>
+      <c r="C52" s="35" t="s">
+        <v>539</v>
+      </c>
+      <c r="D52" s="33" t="s">
+        <v>540</v>
+      </c>
+      <c r="E52" s="33" t="str">
+        <f t="shared" si="13"/>
+        <v>STR_NPC_N_0051_DESC</v>
+      </c>
+      <c r="F52" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G52" s="33">
+        <v>0</v>
+      </c>
+      <c r="H52" s="33">
+        <v>0</v>
+      </c>
+      <c r="I52" s="33">
         <v>1</v>
       </c>
-      <c r="I52" s="40">
-        <v>1</v>
-      </c>
-      <c r="J52" s="40">
-        <v>0</v>
-      </c>
-      <c r="K52" s="40">
-        <v>1200</v>
-      </c>
-      <c r="L52" s="40">
-        <v>30</v>
-      </c>
-      <c r="M52" s="40">
-        <v>20</v>
-      </c>
-      <c r="N52" s="40" t="s">
-        <v>225</v>
-      </c>
-      <c r="O52" s="40"/>
-      <c r="P52" s="40"/>
-      <c r="Q52" s="40" t="s">
-        <v>226</v>
-      </c>
-      <c r="R52" s="40"/>
-      <c r="S52" s="40"/>
-      <c r="T52" s="40"/>
-      <c r="U52" s="40"/>
-      <c r="V52" s="40"/>
-      <c r="W52" s="40"/>
-      <c r="X52" s="40"/>
-      <c r="Y52" s="40"/>
-      <c r="Z52" s="40"/>
-      <c r="AA52" s="40"/>
-      <c r="AB52" s="40"/>
-      <c r="AC52" s="40"/>
+      <c r="J52" s="33">
+        <v>0</v>
+      </c>
+      <c r="K52" s="33">
+        <v>0</v>
+      </c>
+      <c r="L52" s="33">
+        <v>0</v>
+      </c>
+      <c r="M52" s="33">
+        <v>0</v>
+      </c>
+      <c r="N52" s="33"/>
+      <c r="O52" s="33"/>
+      <c r="P52" s="33"/>
+      <c r="Q52" s="36" t="s">
+        <v>550</v>
+      </c>
+      <c r="T52" s="33" t="s">
+        <v>541</v>
+      </c>
+      <c r="U52" s="33" t="s">
+        <v>542</v>
+      </c>
+      <c r="V52" s="33" t="s">
+        <v>543</v>
+      </c>
+      <c r="W52" s="33" t="s">
+        <v>544</v>
+      </c>
+      <c r="X52" s="33" t="s">
+        <v>545</v>
+      </c>
+      <c r="Y52" s="33" t="s">
+        <v>546</v>
+      </c>
+      <c r="Z52" s="33" t="s">
+        <v>547</v>
+      </c>
+      <c r="AA52" s="33" t="s">
+        <v>548</v>
+      </c>
+      <c r="AB52" s="33" t="s">
+        <v>549</v>
+      </c>
+      <c r="AC52" s="33"/>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A53" s="40">
-        <v>22001</v>
-      </c>
-      <c r="B53" s="40" t="s">
-        <v>137</v>
-      </c>
-      <c r="C53" s="41" t="s">
-        <v>138</v>
+        <v>22000</v>
+      </c>
+      <c r="B53" s="41" t="s">
+        <v>247</v>
+      </c>
+      <c r="C53" s="42" t="s">
+        <v>100</v>
       </c>
       <c r="D53" s="40" t="str">
-        <f t="shared" si="13"/>
-        <v>STR_MOB_N_0002</v>
+        <f t="shared" ref="D53:D54" si="14">"STR_"&amp;UPPER(C53)</f>
+        <v>STR_MOB_N_0001</v>
       </c>
       <c r="E53" s="40" t="str">
-        <f t="shared" si="14"/>
-        <v>STR_MOB_N_0002_DESC</v>
+        <f t="shared" ref="E53:E68" si="15">D53&amp;"_DESC"</f>
+        <v>STR_MOB_N_0001_DESC</v>
       </c>
       <c r="F53" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G53" s="40">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H53" s="40">
         <v>1</v>
@@ -9403,19 +9458,21 @@
         <v>0</v>
       </c>
       <c r="K53" s="40">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="L53" s="40">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M53" s="40">
-        <v>10</v>
-      </c>
-      <c r="N53" s="40"/>
+        <v>20</v>
+      </c>
+      <c r="N53" s="40" t="s">
+        <v>225</v>
+      </c>
       <c r="O53" s="40"/>
       <c r="P53" s="40"/>
       <c r="Q53" s="40" t="s">
-        <v>139</v>
+        <v>226</v>
       </c>
       <c r="R53" s="40"/>
       <c r="S53" s="40"/>
@@ -9432,27 +9489,27 @@
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A54" s="40">
-        <v>22002</v>
-      </c>
-      <c r="B54" s="41" t="s">
-        <v>249</v>
-      </c>
-      <c r="C54" s="42" t="s">
-        <v>286</v>
+        <v>22001</v>
+      </c>
+      <c r="B54" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="C54" s="41" t="s">
+        <v>138</v>
       </c>
       <c r="D54" s="40" t="str">
-        <f t="shared" ref="D54" si="15">"STR_"&amp;UPPER(C54)</f>
-        <v>STR_MOB_N_0003</v>
+        <f t="shared" si="14"/>
+        <v>STR_MOB_N_0002</v>
       </c>
       <c r="E54" s="40" t="str">
-        <f t="shared" ref="E54" si="16">D54&amp;"_DESC"</f>
-        <v>STR_MOB_N_0003_DESC</v>
+        <f t="shared" si="15"/>
+        <v>STR_MOB_N_0002_DESC</v>
       </c>
       <c r="F54" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G54" s="40">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H54" s="40">
         <v>1</v>
@@ -9464,21 +9521,19 @@
         <v>0</v>
       </c>
       <c r="K54" s="40">
-        <v>1500</v>
+        <v>2400</v>
       </c>
       <c r="L54" s="40">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M54" s="40">
-        <v>30</v>
-      </c>
-      <c r="N54" s="40" t="s">
-        <v>224</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="N54" s="40"/>
       <c r="O54" s="40"/>
       <c r="P54" s="40"/>
       <c r="Q54" s="40" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="R54" s="40"/>
       <c r="S54" s="40"/>
@@ -9495,27 +9550,27 @@
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A55" s="40">
-        <v>22003</v>
+        <v>22002</v>
       </c>
       <c r="B55" s="41" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="C55" s="42" t="s">
-        <v>234</v>
+        <v>286</v>
       </c>
       <c r="D55" s="40" t="str">
-        <f t="shared" ref="D55" si="17">"STR_"&amp;UPPER(C55)</f>
-        <v>STR_MOB_N_0004</v>
+        <f t="shared" ref="D55" si="16">"STR_"&amp;UPPER(C55)</f>
+        <v>STR_MOB_N_0003</v>
       </c>
       <c r="E55" s="40" t="str">
-        <f t="shared" ref="E55" si="18">D55&amp;"_DESC"</f>
-        <v>STR_MOB_N_0004_DESC</v>
+        <f t="shared" ref="E55" si="17">D55&amp;"_DESC"</f>
+        <v>STR_MOB_N_0003_DESC</v>
       </c>
       <c r="F55" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G55" s="40">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="H55" s="40">
         <v>1</v>
@@ -9530,20 +9585,18 @@
         <v>1500</v>
       </c>
       <c r="L55" s="40">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="M55" s="40">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="N55" s="40" t="s">
-        <v>394</v>
-      </c>
-      <c r="O55" s="40" t="s">
-        <v>395</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="O55" s="40"/>
       <c r="P55" s="40"/>
       <c r="Q55" s="40" t="s">
-        <v>244</v>
+        <v>102</v>
       </c>
       <c r="R55" s="40"/>
       <c r="S55" s="40"/>
@@ -9560,27 +9613,27 @@
     </row>
     <row r="56" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A56" s="40">
-        <v>22004</v>
+        <v>22003</v>
       </c>
       <c r="B56" s="41" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C56" s="42" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D56" s="40" t="str">
-        <f t="shared" ref="D56:D64" si="19">"STR_"&amp;UPPER(C56)</f>
-        <v>STR_MOB_N_0005</v>
+        <f t="shared" ref="D56" si="18">"STR_"&amp;UPPER(C56)</f>
+        <v>STR_MOB_N_0004</v>
       </c>
       <c r="E56" s="40" t="str">
-        <f t="shared" ref="E56:E64" si="20">D56&amp;"_DESC"</f>
-        <v>STR_MOB_N_0005_DESC</v>
+        <f t="shared" ref="E56" si="19">D56&amp;"_DESC"</f>
+        <v>STR_MOB_N_0004_DESC</v>
       </c>
       <c r="F56" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G56" s="40">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H56" s="40">
         <v>1</v>
@@ -9592,21 +9645,23 @@
         <v>0</v>
       </c>
       <c r="K56" s="40">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="L56" s="40">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="M56" s="40">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="N56" s="40" t="s">
-        <v>224</v>
-      </c>
-      <c r="O56" s="40"/>
+        <v>394</v>
+      </c>
+      <c r="O56" s="40" t="s">
+        <v>395</v>
+      </c>
       <c r="P56" s="40"/>
       <c r="Q56" s="40" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="R56" s="40"/>
       <c r="S56" s="40"/>
@@ -9623,27 +9678,27 @@
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A57" s="40">
-        <v>22005</v>
+        <v>22004</v>
       </c>
       <c r="B57" s="41" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C57" s="42" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D57" s="40" t="str">
-        <f t="shared" si="19"/>
-        <v>STR_MOB_N_0006</v>
+        <f t="shared" ref="D57:D65" si="20">"STR_"&amp;UPPER(C57)</f>
+        <v>STR_MOB_N_0005</v>
       </c>
       <c r="E57" s="40" t="str">
-        <f t="shared" si="20"/>
-        <v>STR_MOB_N_0006_DESC</v>
+        <f t="shared" ref="E57:E65" si="21">D57&amp;"_DESC"</f>
+        <v>STR_MOB_N_0005_DESC</v>
       </c>
       <c r="F57" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G57" s="40">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="H57" s="40">
         <v>1</v>
@@ -9655,21 +9710,21 @@
         <v>0</v>
       </c>
       <c r="K57" s="40">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="L57" s="40">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="M57" s="40">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="N57" s="40" t="s">
-        <v>391</v>
+        <v>224</v>
       </c>
       <c r="O57" s="40"/>
       <c r="P57" s="40"/>
       <c r="Q57" s="40" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="R57" s="40"/>
       <c r="S57" s="40"/>
@@ -9686,27 +9741,27 @@
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A58" s="40">
-        <v>22006</v>
+        <v>22005</v>
       </c>
       <c r="B58" s="41" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C58" s="42" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D58" s="40" t="str">
-        <f t="shared" si="19"/>
-        <v>STR_MOB_N_0007</v>
+        <f t="shared" si="20"/>
+        <v>STR_MOB_N_0006</v>
       </c>
       <c r="E58" s="40" t="str">
-        <f t="shared" si="20"/>
-        <v>STR_MOB_N_0007_DESC</v>
+        <f t="shared" si="21"/>
+        <v>STR_MOB_N_0006_DESC</v>
       </c>
       <c r="F58" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G58" s="40">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H58" s="40">
         <v>1</v>
@@ -9718,23 +9773,21 @@
         <v>0</v>
       </c>
       <c r="K58" s="40">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="L58" s="40">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M58" s="40">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N58" s="40" t="s">
-        <v>392</v>
-      </c>
-      <c r="O58" s="40" t="s">
-        <v>393</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="O58" s="40"/>
       <c r="P58" s="40"/>
       <c r="Q58" s="40" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="R58" s="40"/>
       <c r="S58" s="40"/>
@@ -9751,27 +9804,27 @@
     </row>
     <row r="59" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A59" s="40">
-        <v>22007</v>
+        <v>22006</v>
       </c>
       <c r="B59" s="41" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="C59" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D59" s="40" t="str">
-        <f t="shared" si="19"/>
-        <v>STR_MOB_N_0008</v>
+        <f t="shared" si="20"/>
+        <v>STR_MOB_N_0007</v>
       </c>
       <c r="E59" s="40" t="str">
-        <f t="shared" si="20"/>
-        <v>STR_MOB_N_0008_DESC</v>
+        <f t="shared" si="21"/>
+        <v>STR_MOB_N_0007_DESC</v>
       </c>
       <c r="F59" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G59" s="40">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H59" s="40">
         <v>1</v>
@@ -9783,21 +9836,23 @@
         <v>0</v>
       </c>
       <c r="K59" s="40">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="L59" s="40">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="M59" s="40">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="N59" s="40" t="s">
-        <v>224</v>
-      </c>
-      <c r="O59" s="40"/>
+        <v>392</v>
+      </c>
+      <c r="O59" s="40" t="s">
+        <v>393</v>
+      </c>
       <c r="P59" s="40"/>
       <c r="Q59" s="40" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="R59" s="40"/>
       <c r="S59" s="40"/>
@@ -9814,27 +9869,27 @@
     </row>
     <row r="60" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A60" s="40">
-        <v>22008</v>
+        <v>22007</v>
       </c>
       <c r="B60" s="41" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C60" s="42" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D60" s="40" t="str">
-        <f t="shared" si="19"/>
-        <v>STR_MOB_N_0009</v>
+        <f t="shared" si="20"/>
+        <v>STR_MOB_N_0008</v>
       </c>
       <c r="E60" s="40" t="str">
-        <f t="shared" si="20"/>
-        <v>STR_MOB_N_0009_DESC</v>
+        <f t="shared" si="21"/>
+        <v>STR_MOB_N_0008_DESC</v>
       </c>
       <c r="F60" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G60" s="40">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="H60" s="40">
         <v>1</v>
@@ -9846,13 +9901,13 @@
         <v>0</v>
       </c>
       <c r="K60" s="40">
-        <v>1800</v>
+        <v>800</v>
       </c>
       <c r="L60" s="40">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="M60" s="40">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="N60" s="40" t="s">
         <v>224</v>
@@ -9860,7 +9915,7 @@
       <c r="O60" s="40"/>
       <c r="P60" s="40"/>
       <c r="Q60" s="40" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="R60" s="40"/>
       <c r="S60" s="40"/>
@@ -9877,45 +9932,45 @@
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A61" s="40">
-        <v>22009</v>
+        <v>22008</v>
       </c>
       <c r="B61" s="41" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C61" s="42" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D61" s="40" t="str">
-        <f t="shared" si="19"/>
-        <v>STR_MOB_N_0010</v>
+        <f t="shared" si="20"/>
+        <v>STR_MOB_N_0009</v>
       </c>
       <c r="E61" s="40" t="str">
-        <f t="shared" si="20"/>
-        <v>STR_MOB_N_0010_DESC</v>
+        <f t="shared" si="21"/>
+        <v>STR_MOB_N_0009_DESC</v>
       </c>
       <c r="F61" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G61" s="40">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H61" s="40">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I61" s="40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J61" s="40">
         <v>0</v>
       </c>
       <c r="K61" s="40">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="L61" s="40">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M61" s="40">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="N61" s="40" t="s">
         <v>224</v>
@@ -9923,12 +9978,10 @@
       <c r="O61" s="40"/>
       <c r="P61" s="40"/>
       <c r="Q61" s="40" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="R61" s="40"/>
-      <c r="S61" s="40" t="s">
-        <v>285</v>
-      </c>
+      <c r="S61" s="40"/>
       <c r="T61" s="40"/>
       <c r="U61" s="40"/>
       <c r="V61" s="40"/>
@@ -9942,45 +9995,45 @@
     </row>
     <row r="62" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A62" s="40">
-        <v>22010</v>
+        <v>22009</v>
       </c>
       <c r="B62" s="41" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C62" s="42" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D62" s="40" t="str">
-        <f t="shared" si="19"/>
-        <v>STR_MOB_N_0011</v>
+        <f t="shared" si="20"/>
+        <v>STR_MOB_N_0010</v>
       </c>
       <c r="E62" s="40" t="str">
-        <f t="shared" si="20"/>
-        <v>STR_MOB_N_0011_DESC</v>
+        <f t="shared" si="21"/>
+        <v>STR_MOB_N_0010_DESC</v>
       </c>
       <c r="F62" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G62" s="40">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="H62" s="40">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="I62" s="40">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J62" s="40">
         <v>0</v>
       </c>
       <c r="K62" s="40">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="L62" s="40">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M62" s="40">
-        <v>250</v>
+        <v>70</v>
       </c>
       <c r="N62" s="40" t="s">
         <v>224</v>
@@ -9988,11 +10041,11 @@
       <c r="O62" s="40"/>
       <c r="P62" s="40"/>
       <c r="Q62" s="40" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="R62" s="40"/>
       <c r="S62" s="40" t="s">
-        <v>400</v>
+        <v>285</v>
       </c>
       <c r="T62" s="40"/>
       <c r="U62" s="40"/>
@@ -10007,59 +10060,57 @@
     </row>
     <row r="63" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A63" s="40">
-        <v>22011</v>
+        <v>22010</v>
       </c>
       <c r="B63" s="41" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C63" s="42" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D63" s="40" t="str">
-        <f t="shared" si="19"/>
-        <v>STR_MOB_N_0012</v>
+        <f t="shared" si="20"/>
+        <v>STR_MOB_N_0011</v>
       </c>
       <c r="E63" s="40" t="str">
-        <f t="shared" si="20"/>
-        <v>STR_MOB_N_0012_DESC</v>
+        <f t="shared" si="21"/>
+        <v>STR_MOB_N_0011_DESC</v>
       </c>
       <c r="F63" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G63" s="40">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="H63" s="40">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="I63" s="40">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J63" s="40">
         <v>0</v>
       </c>
       <c r="K63" s="40">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="L63" s="40">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="M63" s="40">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="N63" s="40" t="s">
-        <v>396</v>
-      </c>
-      <c r="O63" s="40" t="s">
-        <v>397</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="O63" s="40"/>
       <c r="P63" s="40"/>
       <c r="Q63" s="40" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="R63" s="40"/>
       <c r="S63" s="40" t="s">
-        <v>285</v>
+        <v>400</v>
       </c>
       <c r="T63" s="40"/>
       <c r="U63" s="40"/>
@@ -10074,30 +10125,30 @@
     </row>
     <row r="64" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A64" s="40">
-        <v>22012</v>
+        <v>22011</v>
       </c>
       <c r="B64" s="41" t="s">
-        <v>317</v>
+        <v>261</v>
       </c>
       <c r="C64" s="42" t="s">
-        <v>318</v>
+        <v>242</v>
       </c>
       <c r="D64" s="40" t="str">
-        <f t="shared" si="19"/>
-        <v>STR_MOB_N_0013</v>
+        <f t="shared" si="20"/>
+        <v>STR_MOB_N_0012</v>
       </c>
       <c r="E64" s="40" t="str">
-        <f t="shared" si="20"/>
-        <v>STR_MOB_N_0013_DESC</v>
+        <f t="shared" si="21"/>
+        <v>STR_MOB_N_0012_DESC</v>
       </c>
       <c r="F64" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G64" s="40">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="H64" s="40">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="I64" s="40">
         <v>1</v>
@@ -10106,24 +10157,28 @@
         <v>0</v>
       </c>
       <c r="K64" s="40">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="L64" s="40">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="M64" s="40">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="N64" s="40" t="s">
-        <v>398</v>
-      </c>
-      <c r="O64" s="40"/>
+        <v>396</v>
+      </c>
+      <c r="O64" s="40" t="s">
+        <v>397</v>
+      </c>
       <c r="P64" s="40"/>
       <c r="Q64" s="40" t="s">
-        <v>319</v>
+        <v>257</v>
       </c>
       <c r="R64" s="40"/>
-      <c r="S64" s="40"/>
+      <c r="S64" s="40" t="s">
+        <v>285</v>
+      </c>
       <c r="T64" s="40"/>
       <c r="U64" s="40"/>
       <c r="V64" s="40"/>
@@ -10137,33 +10192,33 @@
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A65" s="40">
-        <v>22013</v>
+        <v>22012</v>
       </c>
       <c r="B65" s="41" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C65" s="42" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D65" s="40" t="str">
-        <f t="shared" ref="D65" si="21">"STR_"&amp;UPPER(C65)</f>
-        <v>STR_MOB_N_0014</v>
+        <f t="shared" si="20"/>
+        <v>STR_MOB_N_0013</v>
       </c>
       <c r="E65" s="40" t="str">
-        <f t="shared" ref="E65" si="22">D65&amp;"_DESC"</f>
-        <v>STR_MOB_N_0014_DESC</v>
+        <f t="shared" si="21"/>
+        <v>STR_MOB_N_0013_DESC</v>
       </c>
       <c r="F65" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G65" s="40">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H65" s="40">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="I65" s="40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J65" s="40">
         <v>0</v>
@@ -10172,23 +10227,21 @@
         <v>1500</v>
       </c>
       <c r="L65" s="40">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="M65" s="40">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="N65" s="40" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="O65" s="40"/>
       <c r="P65" s="40"/>
       <c r="Q65" s="40" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="R65" s="40"/>
-      <c r="S65" s="40" t="s">
-        <v>285</v>
-      </c>
+      <c r="S65" s="40"/>
       <c r="T65" s="40"/>
       <c r="U65" s="40"/>
       <c r="V65" s="40"/>
@@ -10202,45 +10255,45 @@
     </row>
     <row r="66" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A66" s="40">
-        <v>22015</v>
+        <v>22013</v>
       </c>
       <c r="B66" s="41" t="s">
-        <v>457</v>
+        <v>320</v>
       </c>
       <c r="C66" s="42" t="s">
-        <v>458</v>
+        <v>321</v>
       </c>
       <c r="D66" s="40" t="str">
-        <f t="shared" ref="D66" si="23">"STR_"&amp;UPPER(C66)</f>
-        <v>STR_MOB_N_0015</v>
+        <f t="shared" ref="D66" si="22">"STR_"&amp;UPPER(C66)</f>
+        <v>STR_MOB_N_0014</v>
       </c>
       <c r="E66" s="40" t="str">
-        <f t="shared" ref="E66" si="24">D66&amp;"_DESC"</f>
-        <v>STR_MOB_N_0015_DESC</v>
+        <f t="shared" ref="E66" si="23">D66&amp;"_DESC"</f>
+        <v>STR_MOB_N_0014_DESC</v>
       </c>
       <c r="F66" s="40" t="s">
         <v>101</v>
       </c>
       <c r="G66" s="40">
+        <v>20</v>
+      </c>
+      <c r="H66" s="40">
         <v>60</v>
       </c>
-      <c r="H66" s="40">
-        <v>1</v>
-      </c>
       <c r="I66" s="40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J66" s="40">
         <v>0</v>
       </c>
       <c r="K66" s="40">
-        <v>1100</v>
+        <v>1500</v>
       </c>
       <c r="L66" s="40">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="M66" s="40">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="N66" s="40" t="s">
         <v>399</v>
@@ -10248,7 +10301,7 @@
       <c r="O66" s="40"/>
       <c r="P66" s="40"/>
       <c r="Q66" s="40" t="s">
-        <v>459</v>
+        <v>322</v>
       </c>
       <c r="R66" s="40"/>
       <c r="S66" s="40" t="s">
@@ -10266,81 +10319,86 @@
       <c r="AC66" s="40"/>
     </row>
     <row r="67" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A67" s="33">
-        <v>25000</v>
-      </c>
-      <c r="B67" s="34" t="s">
-        <v>386</v>
-      </c>
-      <c r="C67" s="35" t="s">
-        <v>204</v>
-      </c>
-      <c r="D67" s="33" t="s">
-        <v>223</v>
-      </c>
-      <c r="E67" s="33" t="str">
-        <f t="shared" si="14"/>
-        <v>STR_BOX_N_0001_DESC</v>
-      </c>
-      <c r="F67" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="G67" s="33">
-        <v>0</v>
-      </c>
-      <c r="H67" s="33">
-        <v>0</v>
-      </c>
-      <c r="I67" s="33">
+      <c r="A67" s="40">
+        <v>22015</v>
+      </c>
+      <c r="B67" s="41" t="s">
+        <v>457</v>
+      </c>
+      <c r="C67" s="42" t="s">
+        <v>458</v>
+      </c>
+      <c r="D67" s="40" t="str">
+        <f t="shared" ref="D67" si="24">"STR_"&amp;UPPER(C67)</f>
+        <v>STR_MOB_N_0015</v>
+      </c>
+      <c r="E67" s="40" t="str">
+        <f t="shared" ref="E67" si="25">D67&amp;"_DESC"</f>
+        <v>STR_MOB_N_0015_DESC</v>
+      </c>
+      <c r="F67" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G67" s="40">
+        <v>60</v>
+      </c>
+      <c r="H67" s="40">
         <v>1</v>
       </c>
-      <c r="J67" s="33">
-        <v>0</v>
-      </c>
-      <c r="K67" s="33">
-        <v>0</v>
-      </c>
-      <c r="L67" s="33">
-        <v>0</v>
-      </c>
-      <c r="M67" s="33">
-        <v>0</v>
-      </c>
-      <c r="N67" s="33" t="s">
-        <v>205</v>
-      </c>
-      <c r="O67" s="33"/>
-      <c r="P67" s="33"/>
-      <c r="Q67" s="36" t="s">
-        <v>327</v>
-      </c>
-      <c r="T67" s="33"/>
-      <c r="U67" s="33"/>
-      <c r="V67" s="33"/>
-      <c r="W67" s="33"/>
-      <c r="X67" s="33"/>
-      <c r="Y67" s="33"/>
-      <c r="Z67" s="33"/>
-      <c r="AA67" s="33"/>
-      <c r="AB67" s="33"/>
-      <c r="AC67" s="33"/>
+      <c r="I67" s="40">
+        <v>1</v>
+      </c>
+      <c r="J67" s="40">
+        <v>0</v>
+      </c>
+      <c r="K67" s="40">
+        <v>1100</v>
+      </c>
+      <c r="L67" s="40">
+        <v>35</v>
+      </c>
+      <c r="M67" s="40">
+        <v>80</v>
+      </c>
+      <c r="N67" s="40" t="s">
+        <v>399</v>
+      </c>
+      <c r="O67" s="40"/>
+      <c r="P67" s="40"/>
+      <c r="Q67" s="40" t="s">
+        <v>459</v>
+      </c>
+      <c r="R67" s="40"/>
+      <c r="S67" s="40" t="s">
+        <v>285</v>
+      </c>
+      <c r="T67" s="40"/>
+      <c r="U67" s="40"/>
+      <c r="V67" s="40"/>
+      <c r="W67" s="40"/>
+      <c r="X67" s="40"/>
+      <c r="Y67" s="40"/>
+      <c r="Z67" s="40"/>
+      <c r="AA67" s="40"/>
+      <c r="AB67" s="40"/>
+      <c r="AC67" s="40"/>
     </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A68" s="33">
-        <v>25001</v>
+        <v>25000</v>
       </c>
       <c r="B68" s="34" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C68" s="35" t="s">
-        <v>323</v>
+        <v>204</v>
       </c>
       <c r="D68" s="33" t="s">
-        <v>324</v>
+        <v>223</v>
       </c>
       <c r="E68" s="33" t="str">
-        <f t="shared" ref="E68:E72" si="25">D68&amp;"_DESC"</f>
-        <v>STR_BOX_N_0002_DESC</v>
+        <f t="shared" si="15"/>
+        <v>STR_BOX_N_0001_DESC</v>
       </c>
       <c r="F68" s="33" t="s">
         <v>88</v>
@@ -10367,7 +10425,7 @@
         <v>0</v>
       </c>
       <c r="N68" s="33" t="s">
-        <v>388</v>
+        <v>205</v>
       </c>
       <c r="O68" s="33"/>
       <c r="P68" s="33"/>
@@ -10387,20 +10445,20 @@
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A69" s="33">
-        <v>25002</v>
+        <v>25001</v>
       </c>
       <c r="B69" s="34" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C69" s="35" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D69" s="33" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E69" s="33" t="str">
-        <f t="shared" si="25"/>
-        <v>STR_BOX_N_0003_DESC</v>
+        <f t="shared" ref="E69:E73" si="26">D69&amp;"_DESC"</f>
+        <v>STR_BOX_N_0002_DESC</v>
       </c>
       <c r="F69" s="33" t="s">
         <v>88</v>
@@ -10427,7 +10485,7 @@
         <v>0</v>
       </c>
       <c r="N69" s="33" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="O69" s="33"/>
       <c r="P69" s="33"/>
@@ -10447,20 +10505,20 @@
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A70" s="33">
-        <v>25003</v>
+        <v>25002</v>
       </c>
       <c r="B70" s="34" t="s">
-        <v>429</v>
+        <v>389</v>
       </c>
       <c r="C70" s="35" t="s">
-        <v>430</v>
+        <v>325</v>
       </c>
       <c r="D70" s="33" t="s">
-        <v>431</v>
+        <v>326</v>
       </c>
       <c r="E70" s="33" t="str">
-        <f t="shared" si="25"/>
-        <v>STR_BOX_N_0004_DESC</v>
+        <f t="shared" si="26"/>
+        <v>STR_BOX_N_0003_DESC</v>
       </c>
       <c r="F70" s="33" t="s">
         <v>88</v>
@@ -10487,7 +10545,7 @@
         <v>0</v>
       </c>
       <c r="N70" s="33" t="s">
-        <v>205</v>
+        <v>390</v>
       </c>
       <c r="O70" s="33"/>
       <c r="P70" s="33"/>
@@ -10507,20 +10565,20 @@
     </row>
     <row r="71" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A71" s="33">
-        <v>25004</v>
+        <v>25003</v>
       </c>
       <c r="B71" s="34" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C71" s="35" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="D71" s="33" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="E71" s="33" t="str">
-        <f t="shared" ref="E71" si="26">D71&amp;"_DESC"</f>
-        <v>STR_OBJ_N_0001_DESC</v>
+        <f t="shared" si="26"/>
+        <v>STR_BOX_N_0004_DESC</v>
       </c>
       <c r="F71" s="33" t="s">
         <v>88</v>
@@ -10552,7 +10610,7 @@
       <c r="O71" s="33"/>
       <c r="P71" s="33"/>
       <c r="Q71" s="36" t="s">
-        <v>441</v>
+        <v>327</v>
       </c>
       <c r="T71" s="33"/>
       <c r="U71" s="33"/>
@@ -10566,81 +10624,81 @@
       <c r="AC71" s="33"/>
     </row>
     <row r="72" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A72" s="40">
-        <v>26000</v>
-      </c>
-      <c r="B72" s="41" t="s">
-        <v>328</v>
-      </c>
-      <c r="C72" s="42" t="s">
-        <v>329</v>
-      </c>
-      <c r="D72" s="40" t="s">
-        <v>223</v>
-      </c>
-      <c r="E72" s="40" t="str">
-        <f t="shared" si="25"/>
-        <v>STR_BOX_N_0001_DESC</v>
-      </c>
-      <c r="F72" s="40" t="s">
-        <v>330</v>
-      </c>
-      <c r="G72" s="40">
-        <v>300</v>
-      </c>
-      <c r="H72" s="40">
-        <v>0</v>
-      </c>
-      <c r="I72" s="40">
+      <c r="A72" s="33">
+        <v>25004</v>
+      </c>
+      <c r="B72" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="C72" s="35" t="s">
+        <v>438</v>
+      </c>
+      <c r="D72" s="33" t="s">
+        <v>440</v>
+      </c>
+      <c r="E72" s="33" t="str">
+        <f t="shared" ref="E72" si="27">D72&amp;"_DESC"</f>
+        <v>STR_OBJ_N_0001_DESC</v>
+      </c>
+      <c r="F72" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G72" s="33">
+        <v>0</v>
+      </c>
+      <c r="H72" s="33">
+        <v>0</v>
+      </c>
+      <c r="I72" s="33">
         <v>1</v>
       </c>
-      <c r="J72" s="40">
-        <v>0</v>
-      </c>
-      <c r="K72" s="40">
-        <v>0</v>
-      </c>
-      <c r="L72" s="40">
-        <v>0</v>
-      </c>
-      <c r="M72" s="40">
-        <v>0</v>
-      </c>
-      <c r="N72" s="40"/>
-      <c r="O72" s="40"/>
-      <c r="P72" s="40"/>
-      <c r="Q72" s="40" t="s">
-        <v>377</v>
-      </c>
-      <c r="R72" s="40"/>
-      <c r="S72" s="40"/>
-      <c r="T72" s="40"/>
-      <c r="U72" s="40"/>
-      <c r="V72" s="40"/>
-      <c r="W72" s="40"/>
-      <c r="X72" s="40"/>
-      <c r="Y72" s="40"/>
-      <c r="Z72" s="40"/>
-      <c r="AA72" s="40"/>
-      <c r="AB72" s="40"/>
-      <c r="AC72" s="40"/>
+      <c r="J72" s="33">
+        <v>0</v>
+      </c>
+      <c r="K72" s="33">
+        <v>0</v>
+      </c>
+      <c r="L72" s="33">
+        <v>0</v>
+      </c>
+      <c r="M72" s="33">
+        <v>0</v>
+      </c>
+      <c r="N72" s="33" t="s">
+        <v>205</v>
+      </c>
+      <c r="O72" s="33"/>
+      <c r="P72" s="33"/>
+      <c r="Q72" s="36" t="s">
+        <v>441</v>
+      </c>
+      <c r="T72" s="33"/>
+      <c r="U72" s="33"/>
+      <c r="V72" s="33"/>
+      <c r="W72" s="33"/>
+      <c r="X72" s="33"/>
+      <c r="Y72" s="33"/>
+      <c r="Z72" s="33"/>
+      <c r="AA72" s="33"/>
+      <c r="AB72" s="33"/>
+      <c r="AC72" s="33"/>
     </row>
     <row r="73" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A73" s="40">
-        <v>26001</v>
+        <v>26000</v>
       </c>
       <c r="B73" s="41" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C73" s="42" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D73" s="40" t="s">
-        <v>333</v>
+        <v>223</v>
       </c>
       <c r="E73" s="40" t="str">
-        <f t="shared" ref="E73:E77" si="27">D73&amp;"_DESC"</f>
-        <v>STR_TRAP_N_0001_DESC</v>
+        <f t="shared" si="26"/>
+        <v>STR_BOX_N_0001_DESC</v>
       </c>
       <c r="F73" s="40" t="s">
         <v>330</v>
@@ -10658,7 +10716,7 @@
         <v>0</v>
       </c>
       <c r="K73" s="40">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="L73" s="40">
         <v>0</v>
@@ -10670,7 +10728,7 @@
       <c r="O73" s="40"/>
       <c r="P73" s="40"/>
       <c r="Q73" s="40" t="s">
-        <v>337</v>
+        <v>377</v>
       </c>
       <c r="R73" s="40"/>
       <c r="S73" s="40"/>
@@ -10687,26 +10745,26 @@
     </row>
     <row r="74" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A74" s="40">
-        <v>26002</v>
+        <v>26001</v>
       </c>
       <c r="B74" s="41" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C74" s="42" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D74" s="40" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E74" s="40" t="str">
-        <f t="shared" si="27"/>
-        <v>STR_TRAP_N_0002_DESC</v>
+        <f t="shared" ref="E74:E78" si="28">D74&amp;"_DESC"</f>
+        <v>STR_TRAP_N_0001_DESC</v>
       </c>
       <c r="F74" s="40" t="s">
         <v>330</v>
       </c>
       <c r="G74" s="40">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H74" s="40">
         <v>0</v>
@@ -10718,7 +10776,7 @@
         <v>0</v>
       </c>
       <c r="K74" s="40">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="L74" s="40">
         <v>0</v>
@@ -10730,7 +10788,7 @@
       <c r="O74" s="40"/>
       <c r="P74" s="40"/>
       <c r="Q74" s="40" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="R74" s="40"/>
       <c r="S74" s="40"/>
@@ -10747,20 +10805,20 @@
     </row>
     <row r="75" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A75" s="40">
-        <v>26003</v>
+        <v>26002</v>
       </c>
       <c r="B75" s="41" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="C75" s="42" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="D75" s="40" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="E75" s="40" t="str">
-        <f t="shared" ref="E75" si="28">D75&amp;"_DESC"</f>
-        <v>STR_TRAP_N_0003_DESC</v>
+        <f t="shared" si="28"/>
+        <v>STR_TRAP_N_0002_DESC</v>
       </c>
       <c r="F75" s="40" t="s">
         <v>330</v>
@@ -10790,7 +10848,7 @@
       <c r="O75" s="40"/>
       <c r="P75" s="40"/>
       <c r="Q75" s="40" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="R75" s="40"/>
       <c r="S75" s="40"/>
@@ -10807,26 +10865,26 @@
     </row>
     <row r="76" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A76" s="40">
-        <v>26004</v>
+        <v>26003</v>
       </c>
       <c r="B76" s="41" t="s">
-        <v>442</v>
+        <v>345</v>
       </c>
       <c r="C76" s="42" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="D76" s="40" t="s">
-        <v>439</v>
+        <v>344</v>
       </c>
       <c r="E76" s="40" t="str">
         <f t="shared" ref="E76" si="29">D76&amp;"_DESC"</f>
-        <v>STR_OBJ_N_0001_DESC</v>
+        <v>STR_TRAP_N_0003_DESC</v>
       </c>
       <c r="F76" s="40" t="s">
         <v>330</v>
       </c>
       <c r="G76" s="40">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H76" s="40">
         <v>0</v>
@@ -10850,7 +10908,7 @@
       <c r="O76" s="40"/>
       <c r="P76" s="40"/>
       <c r="Q76" s="40" t="s">
-        <v>443</v>
+        <v>346</v>
       </c>
       <c r="R76" s="40"/>
       <c r="S76" s="40"/>
@@ -10866,71 +10924,112 @@
       <c r="AC76" s="40"/>
     </row>
     <row r="77" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A77" s="33">
+      <c r="A77" s="40">
+        <v>26004</v>
+      </c>
+      <c r="B77" s="41" t="s">
+        <v>442</v>
+      </c>
+      <c r="C77" s="42" t="s">
+        <v>329</v>
+      </c>
+      <c r="D77" s="40" t="s">
+        <v>439</v>
+      </c>
+      <c r="E77" s="40" t="str">
+        <f t="shared" ref="E77" si="30">D77&amp;"_DESC"</f>
+        <v>STR_OBJ_N_0001_DESC</v>
+      </c>
+      <c r="F77" s="40" t="s">
+        <v>330</v>
+      </c>
+      <c r="G77" s="40">
+        <v>300</v>
+      </c>
+      <c r="H77" s="40">
+        <v>0</v>
+      </c>
+      <c r="I77" s="40">
+        <v>1</v>
+      </c>
+      <c r="J77" s="40">
+        <v>0</v>
+      </c>
+      <c r="K77" s="40">
+        <v>0</v>
+      </c>
+      <c r="L77" s="40">
+        <v>0</v>
+      </c>
+      <c r="M77" s="40">
+        <v>0</v>
+      </c>
+      <c r="N77" s="40"/>
+      <c r="O77" s="40"/>
+      <c r="P77" s="40"/>
+      <c r="Q77" s="40" t="s">
+        <v>443</v>
+      </c>
+      <c r="R77" s="40"/>
+      <c r="S77" s="40"/>
+      <c r="T77" s="40"/>
+      <c r="U77" s="40"/>
+      <c r="V77" s="40"/>
+      <c r="W77" s="40"/>
+      <c r="X77" s="40"/>
+      <c r="Y77" s="40"/>
+      <c r="Z77" s="40"/>
+      <c r="AA77" s="40"/>
+      <c r="AB77" s="40"/>
+      <c r="AC77" s="40"/>
+    </row>
+    <row r="78" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A78" s="33">
         <v>27000</v>
       </c>
-      <c r="B77" s="34" t="s">
+      <c r="B78" s="34" t="s">
         <v>339</v>
       </c>
-      <c r="C77" s="35" t="s">
+      <c r="C78" s="35" t="s">
         <v>340</v>
       </c>
-      <c r="D77" s="33" t="s">
+      <c r="D78" s="33" t="s">
         <v>341</v>
       </c>
-      <c r="E77" s="33" t="str">
-        <f t="shared" si="27"/>
+      <c r="E78" s="33" t="str">
+        <f t="shared" si="28"/>
         <v>STR_DOOR_N_0001_DESC</v>
       </c>
-      <c r="F77" s="33" t="s">
+      <c r="F78" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="G77" s="33">
-        <v>0</v>
-      </c>
-      <c r="H77" s="33">
-        <v>0</v>
-      </c>
-      <c r="I77" s="33">
+      <c r="G78" s="33">
+        <v>0</v>
+      </c>
+      <c r="H78" s="33">
+        <v>0</v>
+      </c>
+      <c r="I78" s="33">
         <v>1</v>
       </c>
-      <c r="J77" s="33">
-        <v>0</v>
-      </c>
-      <c r="K77" s="33">
-        <v>0</v>
-      </c>
-      <c r="L77" s="33">
-        <v>0</v>
-      </c>
-      <c r="M77" s="33">
-        <v>0</v>
-      </c>
-      <c r="N77" s="33"/>
-      <c r="O77" s="33"/>
-      <c r="P77" s="33"/>
-      <c r="Q77" s="36" t="s">
-        <v>342</v>
-      </c>
-      <c r="T77" s="33"/>
-      <c r="U77" s="33"/>
-      <c r="V77" s="33"/>
-      <c r="W77" s="33"/>
-      <c r="X77" s="33"/>
-      <c r="Y77" s="33"/>
-      <c r="Z77" s="33"/>
-      <c r="AA77" s="33"/>
-      <c r="AB77" s="33"/>
-      <c r="AC77" s="33"/>
-    </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A78" s="33"/>
-      <c r="D78" s="33"/>
-      <c r="E78" s="33"/>
-      <c r="M78" s="33"/>
+      <c r="J78" s="33">
+        <v>0</v>
+      </c>
+      <c r="K78" s="33">
+        <v>0</v>
+      </c>
+      <c r="L78" s="33">
+        <v>0</v>
+      </c>
+      <c r="M78" s="33">
+        <v>0</v>
+      </c>
       <c r="N78" s="33"/>
       <c r="O78" s="33"/>
       <c r="P78" s="33"/>
+      <c r="Q78" s="36" t="s">
+        <v>342</v>
+      </c>
       <c r="T78" s="33"/>
       <c r="U78" s="33"/>
       <c r="V78" s="33"/>
@@ -10944,7 +11043,6 @@
     </row>
     <row r="79" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A79" s="33"/>
-      <c r="B79" s="34"/>
       <c r="D79" s="33"/>
       <c r="E79" s="33"/>
       <c r="M79" s="33"/>
@@ -10964,6 +11062,7 @@
     </row>
     <row r="80" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A80" s="33"/>
+      <c r="B80" s="34"/>
       <c r="D80" s="33"/>
       <c r="E80" s="33"/>
       <c r="M80" s="33"/>
@@ -11038,6 +11137,25 @@
       <c r="AB83" s="33"/>
       <c r="AC83" s="33"/>
     </row>
+    <row r="84" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A84" s="33"/>
+      <c r="D84" s="33"/>
+      <c r="E84" s="33"/>
+      <c r="M84" s="33"/>
+      <c r="N84" s="33"/>
+      <c r="O84" s="33"/>
+      <c r="P84" s="33"/>
+      <c r="T84" s="33"/>
+      <c r="U84" s="33"/>
+      <c r="V84" s="33"/>
+      <c r="W84" s="33"/>
+      <c r="X84" s="33"/>
+      <c r="Y84" s="33"/>
+      <c r="Z84" s="33"/>
+      <c r="AA84" s="33"/>
+      <c r="AB84" s="33"/>
+      <c r="AC84" s="33"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:U2"/>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -11050,7 +11168,7 @@
           <x14:formula1>
             <xm:f>Type!$A$2:$A$20</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F77</xm:sqref>
+          <xm:sqref>F2:F78</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
